--- a/exports/lote2_questoes_autorais.xlsx
+++ b/exports/lote2_questoes_autorais.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em uma via aérea estreitada, a velocidade linear do gás aumenta e o fluxo torna-se &lt;strong&gt;turbulento&lt;/strong&gt;. Nesse regime, a resistência depende da &lt;strong&gt;densidade&lt;/strong&gt; do gás; já no fluxo laminar, descrito pela lei de Hagen-Poiseuille, o determinante é a viscosidade. O número de Reynolds, que prevê a transição para turbulência, é diretamente proporcional à densidade e à velocidade do gás e inversamente proporcional à viscosidade.&lt;/p&gt;&lt;p&gt;O hélio tem densidade cerca de sete vezes menor que a do nitrogênio. Ao substituir o nitrogênio, reduz o número de Reynolds, favorece a reconversão para regime laminar e diminui o trabalho respiratório imposto pela obstrução. O ganho é maior nas obstruções de vias aéreas &lt;em&gt;centrais&lt;/em&gt; — subglótica, laríngea ou traqueal —, onde as velocidades são elevadas. A limitação prática é a fração inspirada de oxigênio: quanto mais O&lt;sub&gt;2&lt;/sub&gt; na mistura, menor o teor de hélio e menor o efeito, de modo que misturas com menos de 60% a 70% de hélio perdem utilidade clínica. É medida de ponte, que não trata a causa da obstrução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a viscosidade do hélio é discretamente maior que a do ar e, no fluxo laminar, viscosidade maior aumenta a resistência; (C) o hélio é apenas veículo, não altera a difusão do oxigênio pela membrana alveolocapilar; (D) o hélio é biologicamente inerte, sem ação broncodilatadora ou anti-inflamatória.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em uma via aérea estreitada, a velocidade linear do gás aumenta e o fluxo torna-se &lt;strong&gt;turbulento&lt;/strong&gt;. Nesse regime, a resistência depende da &lt;strong&gt;densidade&lt;/strong&gt; do gás; já no fluxo laminar, descrito pela lei de Hagen-Poiseuille, o determinante é a viscosidade. O número de Reynolds, que prevê a transição para turbulência, é diretamente proporcional à densidade e à velocidade do gás e inversamente proporcional à viscosidade.&lt;/p&gt;&lt;p&gt;O hélio tem densidade cerca de sete vezes menor que a do nitrogênio. Ao substituir o nitrogênio, reduz o número de Reynolds, favorece a reconversão para regime laminar e diminui o trabalho respiratório imposto pela obstrução. O ganho é maior nas obstruções de vias aéreas &lt;em&gt;centrais&lt;/em&gt; (subglótica, laríngea ou traqueal), onde as velocidades são elevadas. A limitação prática é a fração inspirada de oxigênio: quanto mais O&lt;sub&gt;2&lt;/sub&gt; na mistura, menor o teor de hélio e menor o efeito, de modo que misturas com menos de 60% a 70% de hélio perdem utilidade clínica. É medida de ponte, que não trata a causa da obstrução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a viscosidade do hélio é discretamente maior que a do ar e, no fluxo laminar, viscosidade maior aumenta a resistência; (C) o hélio é apenas veículo, não altera a difusão do oxigênio pela membrana alveolocapilar; (D) o hélio é biologicamente inerte, sem ação broncodilatadora ou anti-inflamatória.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As técnicas de &lt;strong&gt;diluição de gás inerte&lt;/strong&gt; (hélio) e de &lt;strong&gt;lavagem de nitrogênio&lt;/strong&gt; quantificam apenas o volume de gás que se comunica livremente com as vias aéreas e que, portanto, pode ser alcançado pelo traçador durante a manobra. Em doenças com aprisionamento aéreo — enfisema bolhoso, asma grave, bronquiectasias — parte do gás está em unidades muito lentas ou seladas e escapa da medida, resultando em subestimação da CRF.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;pletismografia corporal&lt;/strong&gt; baseia-se na lei de Boyle: com a via aérea ocluída, o paciente faz esforços respiratórios e a relação entre variação de pressão na boca e variação de volume da cabine permite calcular todo o &lt;em&gt;gás torácico&lt;/em&gt;, comunicante ou não. Por isso mede valores maiores nessas doenças. A diferença entre os dois métodos é, na prática, uma estimativa do volume aprisionado, e sua magnitude tem valor clínico na avaliação do enfisema.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a diluição subestima, e não superestima, o volume nessas condições, e o erro não decorre do espaço morto anatômico; (B) a pletismografia é justamente o método que capta o gás aprisionado na obstrução; (D) a pletismografia mede o gás torácico total, não apenas o volume renovado por ciclo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As técnicas de &lt;strong&gt;diluição de gás inerte&lt;/strong&gt; (hélio) e de &lt;strong&gt;lavagem de nitrogênio&lt;/strong&gt; quantificam apenas o volume de gás que se comunica livremente com as vias aéreas e que, portanto, pode ser alcançado pelo traçador durante a manobra. Em doenças com aprisionamento aéreo (enfisema bolhoso, asma grave, bronquiectasias), parte do gás está em unidades muito lentas ou seladas e escapa da medida, resultando em subestimação da CRF.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;pletismografia corporal&lt;/strong&gt; baseia-se na lei de Boyle: com a via aérea ocluída, o paciente faz esforços respiratórios e a relação entre variação de pressão na boca e variação de volume da cabine permite calcular todo o &lt;em&gt;gás torácico&lt;/em&gt;, comunicante ou não. Por isso mede valores maiores nessas doenças. A diferença entre os dois métodos é, na prática, uma estimativa do volume aprisionado, e sua magnitude tem valor clínico na avaliação do enfisema.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a diluição subestima, e não superestima, o volume nessas condições, e o erro não decorre do espaço morto anatômico; (B) a pletismografia é justamente o método que capta o gás aprisionado na obstrução; (D) a pletismografia mede o gás torácico total, não apenas o volume renovado por ciclo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A leitura da espirometria começa pela &lt;strong&gt;relação VEF1/CVF&lt;/strong&gt;. Quando essa relação está reduzida (habitualmente abaixo de 0,70 ou abaixo do limite inferior da normalidade), define-se distúrbio &lt;strong&gt;obstrutivo&lt;/strong&gt;: o VEF1 cai desproporcionalmente à CVF porque o esvaziamento é lento. Quando a relação está normal ou aumentada e a CVF está reduzida, suspeita-se de distúrbio &lt;strong&gt;restritivo&lt;/strong&gt;, mas a confirmação exige medida da &lt;strong&gt;capacidade pulmonar total&lt;/strong&gt; por diluição ou pletismografia — a CVF isolada pode cair por aprisionamento aéreo.&lt;/p&gt;&lt;p&gt;No caso, a relação de 0,89 afasta obstrução, e a capacidade pulmonar total de 61% do previsto confirma a restrição, quadro compatível com doença pulmonar intersticial. O VEF1 reduzido é apenas consequência da CVF menor, não de limitação ao fluxo. Na alça fluxo-volume, a restrição produz curva de morfologia preservada, porém miniaturizada e deslocada para volumes menores.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o VEF1 absoluto reduzido não define obstrução — o critério é a relação VEF1/CVF; (B) padrão misto exige relação reduzida somada à queda da capacidade pulmonar total, e aqui a relação está preservada; (C) a normalidade da relação não exclui doença, e a queda da capacidade pulmonar total documenta restrição significativa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A leitura da espirometria começa pela &lt;strong&gt;relação VEF1/CVF&lt;/strong&gt;. Quando essa relação está reduzida (habitualmente abaixo de 0,70 ou abaixo do limite inferior da normalidade), define-se distúrbio &lt;strong&gt;obstrutivo&lt;/strong&gt;: o VEF1 cai desproporcionalmente à CVF porque o esvaziamento é lento. Quando a relação está normal ou aumentada e a CVF está reduzida, suspeita-se de distúrbio &lt;strong&gt;restritivo&lt;/strong&gt;, mas a confirmação exige medida da &lt;strong&gt;capacidade pulmonar total&lt;/strong&gt; por diluição ou pletismografia; a CVF isolada pode cair por aprisionamento aéreo.&lt;/p&gt;&lt;p&gt;No caso, a relação de 0,89 afasta obstrução, e a capacidade pulmonar total de 61% do previsto confirma a restrição, quadro compatível com doença pulmonar intersticial. O VEF1 reduzido é apenas consequência da CVF menor, não de limitação ao fluxo. Na alça fluxo-volume, a restrição produz curva de morfologia preservada, porém miniaturizada e deslocada para volumes menores.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o VEF1 absoluto reduzido não define obstrução: o critério é a relação VEF1/CVF; (B) padrão misto exige relação reduzida somada à queda da capacidade pulmonar total, e aqui a relação está preservada; (C) a normalidade da relação não exclui doença, e a queda da capacidade pulmonar total documenta restrição significativa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;capacidade de fechamento&lt;/strong&gt; é o volume pulmonar a partir do qual as pequenas vias aéreas das regiões dependentes começam a colapsar durante a expiração. Ela aumenta progressivamente com a idade, por perda de tecido elástico e menor tração radial sobre as vias aéreas. Em ortostatismo, tende a ultrapassar a CRF por volta dos 65 a 70 anos; em decúbito dorsal, onde a CRF é menor, isso ocorre bem antes, próximo dos 45 anos.&lt;/p&gt;&lt;p&gt;Quando a capacidade de fechamento excede a CRF, unidades alveolares fecham dentro da respiração corrente e passam a ser perfundidas sem serem adequadamente ventiladas, criando áreas de baixa relação ventilação-perfusão e verdadeiro shunt. O resultado é hipoxemia com gradiente alveoloarterial alargado, sem alteração de complacência, de pressões de via aérea ou de capnografia — exatamente o quadro descrito. A anestesia geral agrava o problema ao reduzir ainda mais a CRF.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o espaço morto adicional eleva a PaCO&lt;sub&gt;2&lt;/sub&gt;, mas não produz hipoxemia relevante com FiO&lt;sub&gt;2&lt;/sub&gt; de 0,4; (C) a queda de difusão com a idade raramente causa hipoxemia em repouso e não explica o caso; (D) a hipoventilação cursaria com capnografia alterada e PaCO&lt;sub&gt;2&lt;/sub&gt; elevada, ausentes aqui.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;capacidade de fechamento&lt;/strong&gt; é o volume pulmonar a partir do qual as pequenas vias aéreas das regiões dependentes começam a colapsar durante a expiração. Ela aumenta progressivamente com a idade, por perda de tecido elástico e menor tração radial sobre as vias aéreas. Em ortostatismo, tende a ultrapassar a CRF por volta dos 65 a 70 anos; em decúbito dorsal, onde a CRF é menor, isso ocorre bem antes, próximo dos 45 anos.&lt;/p&gt;&lt;p&gt;Quando a capacidade de fechamento excede a CRF, unidades alveolares fecham dentro da respiração corrente e passam a ser perfundidas sem serem adequadamente ventiladas, criando áreas de baixa relação ventilação-perfusão e verdadeiro shunt. O resultado é hipoxemia com gradiente alveoloarterial alargado, sem alteração de complacência, de pressões de via aérea ou de capnografia: exatamente o quadro descrito. A anestesia geral agrava o problema ao reduzir ainda mais a CRF.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o espaço morto adicional eleva a PaCO&lt;sub&gt;2&lt;/sub&gt;, mas não produz hipoxemia relevante com FiO&lt;sub&gt;2&lt;/sub&gt; de 0,4; (C) a queda de difusão com a idade raramente causa hipoxemia em repouso e não explica o caso; (D) a hipoventilação cursaria com capnografia alterada e PaCO&lt;sub&gt;2&lt;/sub&gt; elevada, ausentes aqui.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O trabalho respiratório tem dois componentes. O &lt;strong&gt;trabalho elástico&lt;/strong&gt; é o gasto para distender pulmão e caixa torácica e cresce com volumes correntes maiores. O &lt;strong&gt;trabalho resistivo&lt;/strong&gt; é o gasto para vencer a resistência ao fluxo e cresce com a velocidade do fluxo, portanto com frequências respiratórias mais altas.&lt;/p&gt;&lt;p&gt;Existe, para cada mecânica pulmonar, uma frequência que minimiza o trabalho total. Nas doenças &lt;em&gt;obstrutivas&lt;/em&gt;, em que a resistência domina, esse ponto ótimo desloca-se para frequências baixas e volumes correntes maiores, com tempo expiratório prolongado — padrão lento e profundo, que ainda ajuda a limitar o aprisionamento aéreo e a auto-PEEP. Nas doenças &lt;em&gt;restritivas&lt;/em&gt;, em que a elastância domina, ocorre o oposto: o padrão espontâneo é rápido e superficial. Reconhecer essa lógica orienta também a programação do ventilador nesses pacientes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os componentes: nas obstrutivas predomina o trabalho resistivo, e frequências baixas atuam justamente sobre ele; (C) volumes correntes maiores reduzem a &lt;em&gt;fração&lt;/em&gt; de espaço morto por ciclo, mas isso não diminui o trabalho elástico, que na verdade aumenta; (D) a complacência é maior, e não mínima, na faixa de volumes próxima à CRF, e volumes altos afastam o paciente dessa faixa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O trabalho respiratório tem dois componentes. O &lt;strong&gt;trabalho elástico&lt;/strong&gt; é o gasto para distender pulmão e caixa torácica e cresce com volumes correntes maiores. O &lt;strong&gt;trabalho resistivo&lt;/strong&gt; é o gasto para vencer a resistência ao fluxo e cresce com a velocidade do fluxo, portanto com frequências respiratórias mais altas.&lt;/p&gt;&lt;p&gt;Existe, para cada mecânica pulmonar, uma frequência que minimiza o trabalho total. Nas doenças &lt;em&gt;obstrutivas&lt;/em&gt;, em que a resistência domina, esse ponto ótimo desloca-se para frequências baixas e volumes correntes maiores, com tempo expiratório prolongado, num padrão lento e profundo que ainda ajuda a limitar o aprisionamento aéreo e a auto-PEEP. Nas doenças &lt;em&gt;restritivas&lt;/em&gt;, em que a elastância domina, ocorre o oposto: o padrão espontâneo é rápido e superficial. Reconhecer essa lógica orienta também a programação do ventilador nesses pacientes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os componentes: nas obstrutivas predomina o trabalho resistivo, e frequências baixas atuam justamente sobre ele; (C) volumes correntes maiores reduzem a &lt;em&gt;fração&lt;/em&gt; de espaço morto por ciclo, mas isso não diminui o trabalho elástico, que na verdade aumenta; (D) a complacência é maior, e não mínima, na faixa de volumes próxima à CRF, e volumes altos afastam o paciente dessa faixa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;vasoconstrição pulmonar hipóxica&lt;/strong&gt; é um mecanismo de autorregulação que desvia o fluxo sanguíneo das regiões mal ventiladas para as bem ventiladas, limitando o shunt. Vasodilatadores sistêmicos — nitroprussiato, nitroglicerina, alguns inodilatadores — atingem indistintamente todo o leito pulmonar, inclusive o das áreas hipoventiladas, atenuando esse reflexo e piorando a oxigenação, além de causarem hipotensão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;óxido nítrico inalado&lt;/strong&gt; resolve o problema pela via de administração: alcança apenas os alvéolos &lt;em&gt;ventilados&lt;/em&gt; e dilata seletivamente os capilares adjacentes, redistribuindo o fluxo para as unidades que efetivamente trocam gás. Ao atingir o sangue, é rapidamente ligado e inativado pela hemoglobina, formando metemoglobina e nitrato, de modo que não produz vasodilatação sistêmica. As doses habituais situam-se entre 5 e 40 ppm. O efeito é melhora da oxigenação e redução da resistência vascular pulmonar, útil também na falência ventricular direita, embora sem benefício demonstrado sobre mortalidade na SDRA. Exigem-se monitorização de metemoglobina e de dióxido de nitrogênio e desmame gradual, pelo risco de hipertensão pulmonar de rebote.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o óxido nítrico dilata, não intensifica a vasoconstrição hipóxica; (B) não tem ação inotrópica direta, e a melhora do desempenho ventricular direito decorre da redução da pós-carga; (D) vasodilatadores intravenosos inibem a vasoconstrição pulmonar hipóxica e tendem a piorar a relação ventilação-perfusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;vasoconstrição pulmonar hipóxica&lt;/strong&gt; é um mecanismo de autorregulação que desvia o fluxo sanguíneo das regiões mal ventiladas para as bem ventiladas, limitando o shunt. Vasodilatadores sistêmicos (nitroprussiato, nitroglicerina, alguns inodilatadores) atingem indistintamente todo o leito pulmonar, inclusive o das áreas hipoventiladas, atenuando esse reflexo e piorando a oxigenação, além de causarem hipotensão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;óxido nítrico inalado&lt;/strong&gt; resolve o problema pela via de administração: alcança apenas os alvéolos &lt;em&gt;ventilados&lt;/em&gt; e dilata seletivamente os capilares adjacentes, redistribuindo o fluxo para as unidades que efetivamente trocam gás. Ao atingir o sangue, é rapidamente ligado e inativado pela hemoglobina, formando metemoglobina e nitrato, de modo que não produz vasodilatação sistêmica. As doses habituais situam-se entre 5 e 40 ppm. O efeito é melhora da oxigenação e redução da resistência vascular pulmonar, útil também na falência ventricular direita, embora sem benefício demonstrado sobre mortalidade na SDRA. Exigem-se monitorização de metemoglobina e de dióxido de nitrogênio e desmame gradual, pelo risco de hipertensão pulmonar de rebote.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o óxido nítrico dilata, não intensifica a vasoconstrição hipóxica; (B) não tem ação inotrópica direta, e a melhora do desempenho ventricular direito decorre da redução da pós-carga; (D) vasodilatadores intravenosos inibem a vasoconstrição pulmonar hipóxica e tendem a piorar a relação ventilação-perfusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;espaço morto fisiológico&lt;/strong&gt; é a soma do &lt;strong&gt;anatômico&lt;/strong&gt; — vias aéreas de condução, cerca de 2 mL/kg — com o &lt;strong&gt;alveolar&lt;/strong&gt;, formado por alvéolos ventilados e não perfundidos. No indivíduo hígido, o espaço morto alveolar é desprezível e a diferença entre PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; fica em torno de 2 a 5 mmHg.&lt;/p&gt;&lt;p&gt;Quando ocorre obstrução súbita da perfusão de um território ventilado — embolia trombótica, gasosa, gordurosa ou de cimento ósseo —, esse território passa a devolver gás praticamente sem CO&lt;sub&gt;2&lt;/sub&gt;, que dilui o gás expirado. O resultado é queda abrupta do EtCO&lt;sub&gt;2&lt;/sub&gt; com PaCO&lt;sub&gt;2&lt;/sub&gt; estável ou elevada, ou seja, &lt;em&gt;alargamento do gradiente&lt;/em&gt;. A associação com hipotensão, taquicardia e pressões de via aérea normais em artroplastia de quadril aponta para embolia, e a conduta inclui suporte hemodinâmico, oxigênio a 100%, comunicação com a equipe cirúrgica e investigação com ecocardiografia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na hipoventilação, PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; sobem juntas, sem alargar o gradiente; (C) o deslocamento do tubo altera pouco o espaço morto e não explica hipotensão nem gradiente de 28 mmHg; (D) o shunt compromete a oxigenação e tem efeito pequeno sobre o gradiente de dióxido de carbono.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;espaço morto fisiológico&lt;/strong&gt; é a soma do &lt;strong&gt;anatômico&lt;/strong&gt; (vias aéreas de condução, cerca de 2 mL/kg) com o &lt;strong&gt;alveolar&lt;/strong&gt;, formado por alvéolos ventilados e não perfundidos. No indivíduo hígido, o espaço morto alveolar é desprezível e a diferença entre PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; fica em torno de 2 a 5 mmHg.&lt;/p&gt;&lt;p&gt;Quando ocorre obstrução súbita da perfusão de um território ventilado (embolia trombótica, gasosa, gordurosa ou de cimento ósseo), esse território passa a devolver gás praticamente sem CO&lt;sub&gt;2&lt;/sub&gt;, que dilui o gás expirado. O resultado é queda abrupta do EtCO&lt;sub&gt;2&lt;/sub&gt; com PaCO&lt;sub&gt;2&lt;/sub&gt; estável ou elevada, ou seja, &lt;em&gt;alargamento do gradiente&lt;/em&gt;. A associação com hipotensão, taquicardia e pressões de via aérea normais em artroplastia de quadril aponta para embolia, e a conduta inclui suporte hemodinâmico, oxigênio a 100%, comunicação com a equipe cirúrgica e investigação com ecocardiografia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na hipoventilação, PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; sobem juntas, sem alargar o gradiente; (C) o deslocamento do tubo altera pouco o espaço morto e não explica hipotensão nem gradiente de 28 mmHg; (D) o shunt compromete a oxigenação e tem efeito pequeno sobre o gradiente de dióxido de carbono.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;P50&lt;/strong&gt; é a pressão parcial de oxigênio na qual a hemoglobina está 50% saturada e vale cerca de 26 a 27 mmHg no adulto normal. Valores &lt;em&gt;maiores&lt;/em&gt; indicam desvio à direita, com menor afinidade e maior liberação de oxigênio aos tecidos; valores &lt;em&gt;menores&lt;/em&gt; indicam desvio à esquerda, com maior afinidade e menor entrega periférica.&lt;/p&gt;&lt;p&gt;Deslocam a curva para a direita: acidose, hipercapnia, hipertermia e aumento do 2,3-DPG. Deslocam para a esquerda: alcalose, hipocapnia, hipotermia, queda do 2,3-DPG, carboxi-hemoglobina, metemoglobina e hemoglobina fetal. No sangue estocado, o 2,3-DPG cai progressivamente, podendo tornar-se muito baixo ao fim do armazenamento; a transfusão maciça soma a isso a hipotermia e a alcalose metabólica decorrente do metabolismo hepático do citrato em bicarbonato. Os três fatores empurram a curva para a esquerda, dificultando a liberação de oxigênio nos tecidos apesar de saturação arterial adequada — o que ajuda a explicar lactato persistente. A regeneração do 2,3-DPG ocorre ao longo de 12 a 24 horas após a transfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o 2,3-DPG diminui, e não aumenta, durante a estocagem; (B) a hipotermia desvia a curva para a esquerda e reduz a P50; (D) a alcalose desloca a curva para a esquerda, pelo efeito Bohr, dificultando a extração tecidual.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;P50&lt;/strong&gt; é a pressão parcial de oxigênio na qual a hemoglobina está 50% saturada e vale cerca de 26 a 27 mmHg no adulto normal. Valores &lt;em&gt;maiores&lt;/em&gt; indicam desvio à direita, com menor afinidade e maior liberação de oxigênio aos tecidos; valores &lt;em&gt;menores&lt;/em&gt; indicam desvio à esquerda, com maior afinidade e menor entrega periférica.&lt;/p&gt;&lt;p&gt;Deslocam a curva para a direita: acidose, hipercapnia, hipertermia e aumento do 2,3-DPG. Deslocam para a esquerda: alcalose, hipocapnia, hipotermia, queda do 2,3-DPG, carboxi-hemoglobina, metemoglobina e hemoglobina fetal. No sangue estocado, o 2,3-DPG cai progressivamente, podendo tornar-se muito baixo ao fim do armazenamento; a transfusão maciça soma a isso a hipotermia e a alcalose metabólica decorrente do metabolismo hepático do citrato em bicarbonato. Os três fatores empurram a curva para a esquerda, dificultando a liberação de oxigênio nos tecidos apesar de saturação arterial adequada, o que ajuda a explicar lactato persistente. A regeneração do 2,3-DPG ocorre ao longo de 12 a 24 horas após a transfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o 2,3-DPG diminui, e não aumenta, durante a estocagem; (B) a hipotermia desvia a curva para a esquerda e reduz a P50; (D) a alcalose desloca a curva para a esquerda, pelo efeito Bohr, dificultando a extração tecidual.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt; é descrita por uma reta que relaciona ventilação-minuto e PaCO&lt;sub&gt;2&lt;/sub&gt;. Interessam dois parâmetros: a &lt;strong&gt;inclinação&lt;/strong&gt;, cerca de 2 a 3 L/min para cada mmHg de elevação da PaCO&lt;sub&gt;2&lt;/sub&gt; no adulto acordado, e o &lt;strong&gt;limiar apneico&lt;/strong&gt;, valor de PaCO&lt;sub&gt;2&lt;/sub&gt; abaixo do qual cessa o estímulo ventilatório.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;opioides&lt;/strong&gt; deslocam essa curva para a &lt;em&gt;direita&lt;/em&gt; e reduzem sua inclinação: para qualquer PaCO&lt;sub&gt;2&lt;/sub&gt;, a ventilação resultante é menor, e é necessária uma PaCO&lt;sub&gt;2&lt;/sub&gt; mais alta para deflagrar o mesmo estímulo, ou seja, o limiar apneico sobe. Clinicamente, isso se manifesta como bradipneia com volume corrente relativamente preservado e hipercapnia tolerada sem despertar espontâneo — exatamente o padrão descrito. Sono, idade avançada, apneia obstrutiva e associação com benzodiazepínicos ou anestésicos residuais potencializam o efeito. O manejo inclui estímulo, oxigênio suplementar, vigilância prolongada e, se houver depressão importante, titulação cuidadosa de naloxona.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o oposto do efeito opioide, característico de estados de aumento do estímulo ventilatório; (C) os opioides reduzem a inclinação, não a preservam, e o limiar apneico sobe; (D) a depressão seletiva da resposta hipóxica com preservação da resposta ao CO&lt;sub&gt;2&lt;/sub&gt; é característica dos anestésicos inalatórios em concentrações subanestésicas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt; é descrita por uma reta que relaciona ventilação-minuto e PaCO&lt;sub&gt;2&lt;/sub&gt;. Interessam dois parâmetros: a &lt;strong&gt;inclinação&lt;/strong&gt;, cerca de 2 a 3 L/min para cada mmHg de elevação da PaCO&lt;sub&gt;2&lt;/sub&gt; no adulto acordado, e o &lt;strong&gt;limiar apneico&lt;/strong&gt;, valor de PaCO&lt;sub&gt;2&lt;/sub&gt; abaixo do qual cessa o estímulo ventilatório.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;opioides&lt;/strong&gt; deslocam essa curva para a &lt;em&gt;direita&lt;/em&gt; e reduzem sua inclinação: para qualquer PaCO&lt;sub&gt;2&lt;/sub&gt;, a ventilação resultante é menor, e é necessária uma PaCO&lt;sub&gt;2&lt;/sub&gt; mais alta para deflagrar o mesmo estímulo, ou seja, o limiar apneico sobe. Clinicamente, isso se manifesta como bradipneia com volume corrente relativamente preservado e hipercapnia tolerada sem despertar espontâneo, exatamente o padrão descrito. Sono, idade avançada, apneia obstrutiva e associação com benzodiazepínicos ou anestésicos residuais potencializam o efeito. O manejo inclui estímulo, oxigênio suplementar, vigilância prolongada e, se houver depressão importante, titulação cuidadosa de naloxona.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o oposto do efeito opioide, característico de estados de aumento do estímulo ventilatório; (C) os opioides reduzem a inclinação, não a preservam, e o limiar apneico sobe; (D) a depressão seletiva da resposta hipóxica com preservação da resposta ao CO&lt;sub&gt;2&lt;/sub&gt; é característica dos anestésicos inalatórios em concentrações subanestésicas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;auto-PEEP&lt;/strong&gt; ocorre quando o tempo expiratório é insuficiente para esvaziar os pulmões, situação típica da limitação ao fluxo expiratório. O gás aprisionado mantém pressão alveolar positiva ao fim da expiração, e o paciente precisa gerar um esforço capaz de vencer &lt;em&gt;toda&lt;/em&gt; essa pressão antes que a via aérea proximal registre queda suficiente para disparar o ventilador. Com auto-PEEP de 10 e PEEP aplicada de 3 cmH&lt;sub&gt;2&lt;/sub&gt;O, o esforço necessário é de aproximadamente 7 cmH&lt;sub&gt;2&lt;/sub&gt;O somados à sensibilidade programada — daí os &lt;strong&gt;esforços ineficazes&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Aplicar PEEP externa em torno de 75% a 85% da auto-PEEP funciona como contrapressão que reduz o gradiente a ser vencido, sem aumentar de forma significativa o volume pulmonar expiratório final, porque nesses pacientes o ponto de limitação de fluxo se comporta como resistor de Starling. Medidas complementares essenciais são prolongar o tempo expiratório (reduzindo a frequência ou aumentando o fluxo inspiratório), tratar o broncoespasmo e evitar volumes correntes excessivos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) sensibilidade muito ávida não resolve o obstáculo principal, que é a auto-PEEP, e favorece autodisparo; (B) PEEP acima da auto-PEEP aumenta a hiperinsuflação, a pressão de platô e o comprometimento hemodinâmico; (D) aumentar a frequência encurta ainda mais o tempo expiratório e agrava o aprisionamento aéreo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;auto-PEEP&lt;/strong&gt; ocorre quando o tempo expiratório é insuficiente para esvaziar os pulmões, situação típica da limitação ao fluxo expiratório. O gás aprisionado mantém pressão alveolar positiva ao fim da expiração, e o paciente precisa gerar um esforço capaz de vencer &lt;em&gt;toda&lt;/em&gt; essa pressão antes que a via aérea proximal registre queda suficiente para disparar o ventilador. Com auto-PEEP de 10 e PEEP aplicada de 3 cmH&lt;sub&gt;2&lt;/sub&gt;O, o esforço necessário é de aproximadamente 7 cmH&lt;sub&gt;2&lt;/sub&gt;O somados à sensibilidade programada; daí os &lt;strong&gt;esforços ineficazes&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Aplicar PEEP externa em torno de 75% a 85% da auto-PEEP funciona como contrapressão que reduz o gradiente a ser vencido, sem aumentar de forma significativa o volume pulmonar expiratório final, porque nesses pacientes o ponto de limitação de fluxo se comporta como resistor de Starling. Medidas complementares essenciais são prolongar o tempo expiratório (reduzindo a frequência ou aumentando o fluxo inspiratório), tratar o broncoespasmo e evitar volumes correntes excessivos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) sensibilidade muito ávida não resolve o obstáculo principal, que é a auto-PEEP, e favorece autodisparo; (B) PEEP acima da auto-PEEP aumenta a hiperinsuflação, a pressão de platô e o comprometimento hemodinâmico; (D) aumentar a frequência encurta ainda mais o tempo expiratório e agrava o aprisionamento aéreo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em qualquer modo ventilatório, o que se programa determina qual variável fica &lt;em&gt;fixa&lt;/em&gt; e qual se torna &lt;strong&gt;dependente&lt;/strong&gt; da mecânica respiratória. Na ventilação &lt;strong&gt;controlada a volume&lt;/strong&gt;, o volume corrente é garantido e a pressão de via aérea varia com resistência e complacência. Na ventilação &lt;strong&gt;controlada a pressão&lt;/strong&gt;, ocorre o inverso: a pressão é limitada e constante, e o volume corrente resulta da complacência, da resistência e do tempo inspiratório disponível.&lt;/p&gt;&lt;p&gt;Pneumoperitônio e Trendelenburg reduzem de forma abrupta a complacência do sistema respiratório, sobretudo por rigidez da parede toracoabdominal. Com a mesma pressão motriz de 15 cmH&lt;sub&gt;2&lt;/sub&gt;O, o volume entregue cai — no caso, de 480 para 330 mL, o que corresponde a queda da complacência de 32 para 22 mL/cmH&lt;sub&gt;2&lt;/sub&gt;O. O volume-minuto cai de 5,8 para 4,0 L/min, a ventilação alveolar diminui e a PaCO&lt;sub&gt;2&lt;/sub&gt; sobe. A conduta é reavaliar a pressão inspiratória e a frequência, otimizar a PEEP e monitorizar volume corrente e capnografia continuamente após cada mudança de posição ou de pressão intra-abdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) queda de resistência aumentaria o volume entregue, não o contrário; (C) em vazamento significativo o volume expirado cai com queda da pressão sustentada e alarmes específicos, o que não corresponde ao quadro; (D) nenhum modo a pressão garante volume corrente, justamente por ser variável dependente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em qualquer modo ventilatório, o que se programa determina qual variável fica &lt;em&gt;fixa&lt;/em&gt; e qual se torna &lt;strong&gt;dependente&lt;/strong&gt; da mecânica respiratória. Na ventilação &lt;strong&gt;controlada a volume&lt;/strong&gt;, o volume corrente é garantido e a pressão de via aérea varia com resistência e complacência. Na ventilação &lt;strong&gt;controlada a pressão&lt;/strong&gt;, ocorre o inverso: a pressão é limitada e constante, e o volume corrente resulta da complacência, da resistência e do tempo inspiratório disponível.&lt;/p&gt;&lt;p&gt;Pneumoperitônio e Trendelenburg reduzem de forma abrupta a complacência do sistema respiratório, sobretudo por rigidez da parede toracoabdominal. Com a mesma pressão motriz de 15 cmH&lt;sub&gt;2&lt;/sub&gt;O, o volume entregue cai: no caso, de 480 para 330 mL, o que corresponde a queda da complacência de 32 para 22 mL/cmH&lt;sub&gt;2&lt;/sub&gt;O. O volume-minuto cai de 5,8 para 4,0 L/min, a ventilação alveolar diminui e a PaCO&lt;sub&gt;2&lt;/sub&gt; sobe. A conduta é reavaliar a pressão inspiratória e a frequência, otimizar a PEEP e monitorizar volume corrente e capnografia continuamente após cada mudança de posição ou de pressão intra-abdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) queda de resistência aumentaria o volume entregue, não o contrário; (C) em vazamento significativo o volume expirado cai com queda da pressão sustentada e alarmes específicos, o que não corresponde ao quadro; (D) nenhum modo a pressão garante volume corrente, justamente por ser variável dependente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A ventilação com pressão positiva inverte o regime de pressões do tórax. Na respiração espontânea, a pressão intratorácica negativa durante a inspiração favorece o &lt;strong&gt;retorno venoso&lt;/strong&gt;. Sob pressão positiva, a pressão intratorácica média torna-se positiva, eleva a pressão do átrio direito e reduz o gradiente entre a pressão sistêmica média de enchimento e o átrio direito, que é o motor do retorno venoso. O efeito é tanto maior quanto menor a volemia, quanto maior a PEEP e quanto maior a pressão média de via aérea.&lt;/p&gt;&lt;p&gt;No politraumatizado, a hipovolemia costuma estar mascarada pela descarga adrenérgica; a sedação para intubação retira esse tônus simpático e a pressão positiva completa o quadro, produzindo hipotensão logo após a conexão ao ventilador. Deve-se sempre excluir pneumotórax hipertensivo — aqui afastado pela ausculta e pelo deslizamento pleural preservado — e auto-PEEP. O manejo consiste em reposição volêmica, redução transitória da pressão média de via aérea e vasopressor conforme a resposta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a pressão positiva &lt;em&gt;reduz&lt;/em&gt; a pós-carga do ventrículo esquerdo, ao diminuir sua pressão transmural; (B) a hipocapnia produz vasoconstrição cerebral e não vasoplegia sistêmica relevante; (C) a hipercapnia aguda tende a elevar o débito cardíaco por estímulo simpático, não a deprimi-lo nesse contexto.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A ventilação com pressão positiva inverte o regime de pressões do tórax. Na respiração espontânea, a pressão intratorácica negativa durante a inspiração favorece o &lt;strong&gt;retorno venoso&lt;/strong&gt;. Sob pressão positiva, a pressão intratorácica média torna-se positiva, eleva a pressão do átrio direito e reduz o gradiente entre a pressão sistêmica média de enchimento e o átrio direito, que é o motor do retorno venoso. O efeito é tanto maior quanto menor a volemia, quanto maior a PEEP e quanto maior a pressão média de via aérea.&lt;/p&gt;&lt;p&gt;No politraumatizado, a hipovolemia costuma estar mascarada pela descarga adrenérgica; a sedação para intubação retira esse tônus simpático e a pressão positiva completa o quadro, produzindo hipotensão logo após a conexão ao ventilador. Deve-se sempre excluir pneumotórax hipertensivo (aqui afastado pela ausculta e pelo deslizamento pleural preservado) e auto-PEEP. O manejo consiste em reposição volêmica, redução transitória da pressão média de via aérea e vasopressor conforme a resposta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a pressão positiva &lt;em&gt;reduz&lt;/em&gt; a pós-carga do ventrículo esquerdo, ao diminuir sua pressão transmural; (B) a hipocapnia produz vasoconstrição cerebral e não vasoplegia sistêmica relevante; (C) a hipercapnia aguda tende a elevar o débito cardíaco por estímulo simpático, não a deprimi-lo nesse contexto.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha entre tubo de duplo lúmen esquerdo e direito é anatômica. O &lt;strong&gt;brônquio principal esquerdo&lt;/strong&gt; mede cerca de 4,5 a 5 cm antes de se dividir, o que oferece ampla margem para acomodar o balonete brônquico sem obstruir lobos. O &lt;strong&gt;brônquio principal direito&lt;/strong&gt; mede apenas 1,5 a 2 cm, e o orifício do lobo superior direito emerge muito precocemente, podendo em alguns pacientes originar-se da própria traqueia. Qualquer deslocamento de poucos milímetros de um tubo direito oclui esse orifício, produzindo hipoxemia e atelectasia lobar.&lt;/p&gt;&lt;p&gt;Por isso, o tubo esquerdo é a escolha padrão mesmo para cirurgias do lado direito: o pulmão a ser operado é simplesmente deixado colapsar por meio do clampeamento do lúmen correspondente. Reservam-se os tubos direitos para situações em que o brônquio principal esquerdo não pode ser cateterizado ou será seccionado — pneumonectomia esquerda, lesão ou tumor do brônquio principal esquerdo, estenose ou distorção anatômica local. Como alternativa, o bloqueador brônquico é útil em via aérea difícil, intubação já estabelecida ou necessidade de ventilação prolongada no pós-operatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o brônquio direito é o de maior calibre, e não o esquerdo; (B) não há ventilação seletiva do lobo superior direito por meio de um tubo esquerdo; (D) o tubo direito é aceitável e indicado em situações específicas, não sendo contraindicação absoluta.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha entre tubo de duplo lúmen esquerdo e direito é anatômica. O &lt;strong&gt;brônquio principal esquerdo&lt;/strong&gt; mede cerca de 4,5 a 5 cm antes de se dividir, o que oferece ampla margem para acomodar o balonete brônquico sem obstruir lobos. O &lt;strong&gt;brônquio principal direito&lt;/strong&gt; mede apenas 1,5 a 2 cm, e o orifício do lobo superior direito emerge muito precocemente, podendo em alguns pacientes originar-se da própria traqueia. Qualquer deslocamento de poucos milímetros de um tubo direito oclui esse orifício, produzindo hipoxemia e atelectasia lobar.&lt;/p&gt;&lt;p&gt;Por isso, o tubo esquerdo é a escolha padrão mesmo para cirurgias do lado direito: o pulmão a ser operado é simplesmente deixado colapsar por meio do clampeamento do lúmen correspondente. Reservam-se os tubos direitos para situações em que o brônquio principal esquerdo não pode ser cateterizado ou será seccionado: pneumonectomia esquerda, lesão ou tumor do brônquio principal esquerdo, estenose ou distorção anatômica local. Como alternativa, o bloqueador brônquico é útil em via aérea difícil, intubação já estabelecida ou necessidade de ventilação prolongada no pós-operatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o brônquio direito é o de maior calibre, e não o esquerdo; (B) não há ventilação seletiva do lobo superior direito por meio de um tubo esquerdo; (D) o tubo direito é aceitável e indicado em situações específicas, não sendo contraindicação absoluta.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A dor após toracotomia é intensa, tem componente somático e visceral e interfere diretamente na capacidade de tossir e respirar profundamente, com risco de atelectasia, retenção de secreções e pneumonia. A analgesia regional é, por isso, parte central da estratégia perioperatória.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;peridural torácica&lt;/strong&gt; contínua foi durante décadas o padrão de referência. O &lt;strong&gt;bloqueio paravertebral&lt;/strong&gt; torácico, realizado por referências anatômicas ou sob ultrassonografia, deposita anestésico local no espaço onde emergem os nervos espinhais, produzindo bloqueio essencialmente &lt;em&gt;unilateral&lt;/em&gt; de vários dermátomos. As evidências acumuladas mostram eficácia analgésica comparável à da peridural, com perfil de efeitos adversos mais favorável: menos hipotensão, por bloqueio simpático restrito a um lado, menos retenção urinária, menos náusea e menor risco de complicações relacionadas ao neuroeixo, incluindo hematoma epidural — vantagem relevante quando há tromboprofilaxia. Ambas as técnicas permitem cateter e infusão contínua. Bloqueios do plano do serrátil e do eretor da espinha são alternativas quando as duas primeiras não são viáveis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio paravertebral também reduz complicações pulmonares e é alternativa estabelecida; (B) a analgesia é comparável e a manutenção por cateter é rotineira; (D) a peridural torácica produz bloqueio simpático bilateral, com hipotensão que pode ser mal tolerada na disfunção ventricular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A dor após toracotomia é intensa, tem componente somático e visceral e interfere diretamente na capacidade de tossir e respirar profundamente, com risco de atelectasia, retenção de secreções e pneumonia. A analgesia regional é, por isso, parte central da estratégia perioperatória.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;peridural torácica&lt;/strong&gt; contínua foi durante décadas o padrão de referência. O &lt;strong&gt;bloqueio paravertebral&lt;/strong&gt; torácico, realizado por referências anatômicas ou sob ultrassonografia, deposita anestésico local no espaço onde emergem os nervos espinhais, produzindo bloqueio essencialmente &lt;em&gt;unilateral&lt;/em&gt; de vários dermátomos. As evidências acumuladas mostram eficácia analgésica comparável à da peridural, com perfil de efeitos adversos mais favorável: menos hipotensão, por bloqueio simpático restrito a um lado, menos retenção urinária, menos náusea e menor risco de complicações relacionadas ao neuroeixo, incluindo hematoma epidural, vantagem relevante quando há tromboprofilaxia. Ambas as técnicas permitem cateter e infusão contínua. Bloqueios do plano do serrátil e do eretor da espinha são alternativas quando as duas primeiras não são viáveis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio paravertebral também reduz complicações pulmonares e é alternativa estabelecida; (B) a analgesia é comparável e a manutenção por cateter é rotineira; (D) a peridural torácica produz bloqueio simpático bilateral, com hipotensão que pode ser mal tolerada na disfunção ventricular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A máscara laríngea de primeira geração forma um selo perilaríngeo de baixa pressão. A &lt;strong&gt;pressão de selo&lt;/strong&gt; situa-se tipicamente em torno de 20 cmH2O, raramente ultrapassando 25 a 30 cmH2O. A ventilação com pressão positiva por meio desse dispositivo é viável, desde que a &lt;strong&gt;pressão de pico permaneça abaixo da pressão de selo&lt;/strong&gt;; acima desse limiar, o gás escapa pela via de menor resistência e insufla o estômago, o que reduz a complacência, favorece regurgitação e compromete a ventilação alveolar.&lt;/p&gt;&lt;p&gt;A conduta correta é reduzir o volume corrente (aceitando 6 a 7 mL/kg de peso predito), limitar a pressão inspiratória, reposicionar o dispositivo e, se o vazamento persistir com hipoventilação, converter para tubo traqueal, que garante via aérea selada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hiperinsuflação do balonete é contraproducente — o volume máximo do número 4 é da ordem de 30 mL e o excesso distorce a cúpula, &lt;em&gt;piora&lt;/em&gt; o selo e eleva a pressão sobre a mucosa faríngea, com risco de lesão neural. (B) a insuflação gástrica reduz a complacência toracopulmonar, eleva o risco de regurgitação e perpetua a hipoventilação, não sendo aceitável. (D) o aumento do tamanho pode melhorar discretamente o selo, mas dispositivos de primeira geração não alcançam pressões de selo próximas de 40 cmH2O; esse patamar é característico de dispositivos de segunda geração com dreno esofágico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A máscara laríngea de primeira geração forma um selo perilaríngeo de baixa pressão. A &lt;strong&gt;pressão de selo&lt;/strong&gt; situa-se tipicamente em torno de 20 cmH2O, raramente ultrapassando 25 a 30 cmH2O. A ventilação com pressão positiva por meio desse dispositivo é viável, desde que a &lt;strong&gt;pressão de pico permaneça abaixo da pressão de selo&lt;/strong&gt;; acima desse limiar, o gás escapa pela via de menor resistência e insufla o estômago, o que reduz a complacência, favorece regurgitação e compromete a ventilação alveolar.&lt;/p&gt;&lt;p&gt;A conduta correta é reduzir o volume corrente (aceitando 6 a 7 mL/kg de peso predito), limitar a pressão inspiratória, reposicionar o dispositivo e, se o vazamento persistir com hipoventilação, converter para tubo traqueal, que garante via aérea selada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hiperinsuflação do balonete é contraproducente: o volume máximo do número 4 é da ordem de 30 mL e o excesso distorce a cúpula, &lt;em&gt;piora&lt;/em&gt; o selo e eleva a pressão sobre a mucosa faríngea, com risco de lesão neural. (B) a insuflação gástrica reduz a complacência toracopulmonar, eleva o risco de regurgitação e perpetua a hipoventilação, não sendo aceitável. (D) o aumento do tamanho pode melhorar discretamente o selo, mas dispositivos de primeira geração não alcançam pressões de selo próximas de 40 cmH2O; esse patamar é característico de dispositivos de segunda geração com dreno esofágico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pré-oxigenação não é sinônimo de hiperoxigenação do sangue: seu objetivo é a &lt;strong&gt;desnitrogenação&lt;/strong&gt;. Em ar ambiente, a capacidade residual funcional (cerca de 2,5 L no adulto) contém aproximadamente 500 mL de oxigênio e o restante de nitrogênio. Ventilando com FiO2 de 1,0, o nitrogênio é progressivamente eliminado e a CRF passa a conter em torno de 2.000 a 2.500 mL de oxigênio — um reservatório de onde o sangue capilar pulmonar continua a captar gás mesmo sem fluxo ventilatório.&lt;/p&gt;&lt;p&gt;O alvo prático é uma &lt;strong&gt;fração expirada de oxigênio igual ou superior a 0,90&lt;/strong&gt;, obtida com três minutos de volume corrente sob máscara bem vedada ou com oito respirações de capacidade vital em 60 segundos. Alcançado esse patamar, o adulto hígido tolera cerca de oito minutos de apneia antes de dessaturar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o oxigênio dissolvido no plasma, mesmo com PaO&lt;sub&gt;2&lt;/sub&gt; elevada, corresponde a poucos mililitros por decilitro e contribui de forma marginal para o conteúdo total. (C) a hemoglobina já está praticamente saturada em ar ambiente, de modo que a pré-oxigenação acrescenta pouquíssimo oxigênio ligado; a elevação da saturação venosa é consequência, não mecanismo. (D) a hiperóxia não reduz o consumo metabólico de oxigênio, que permanece em torno de 3 a 4 mL/kg/min durante a apneia e é justamente o que consome o reservatório alveolar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pré-oxigenação não é sinônimo de hiperoxigenação do sangue: seu objetivo é a &lt;strong&gt;desnitrogenação&lt;/strong&gt;. Em ar ambiente, a capacidade residual funcional (cerca de 2,5 L no adulto) contém aproximadamente 500 mL de oxigênio e o restante de nitrogênio. Ventilando com FiO2 de 1,0, o nitrogênio é progressivamente eliminado e a CRF passa a conter em torno de 2.000 a 2.500 mL de oxigênio, um reservatório de onde o sangue capilar pulmonar continua a captar gás mesmo sem fluxo ventilatório.&lt;/p&gt;&lt;p&gt;O alvo prático é uma &lt;strong&gt;fração expirada de oxigênio igual ou superior a 0,90&lt;/strong&gt;, obtida com três minutos de volume corrente sob máscara bem vedada ou com oito respirações de capacidade vital em 60 segundos. Alcançado esse patamar, o adulto hígido tolera cerca de oito minutos de apneia antes de dessaturar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o oxigênio dissolvido no plasma, mesmo com PaO&lt;sub&gt;2&lt;/sub&gt; elevada, corresponde a poucos mililitros por decilitro e contribui de forma marginal para o conteúdo total. (C) a hemoglobina já está praticamente saturada em ar ambiente, de modo que a pré-oxigenação acrescenta pouquíssimo oxigênio ligado; a elevação da saturação venosa é consequência, não mecanismo. (D) a hiperóxia não reduz o consumo metabólico de oxigênio, que permanece em torno de 3 a 4 mL/kg/min durante a apneia e é justamente o que consome o reservatório alveolar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os preditores independentes de ventilação difícil sob máscara facial são reunidos em mnemônicos consagrados e incluem &lt;strong&gt;barba, obesidade, ausência de dentes, idade avançada, história de ronco ou apneia obstrutiva&lt;/strong&gt;, limitação da protrusão mandibular e Mallampati elevado. A presença de dois ou mais eleva substancialmente a probabilidade de ventilação difícil.&lt;/p&gt;&lt;p&gt;Desses fatores, apenas um é imediatamente modificável na sala: a barba. A interposição de pelos impede a vedação do coxim da máscara contra a pele. Recobrir a área com &lt;strong&gt;filme adesivo transparente&lt;/strong&gt;, recortando uma janela para boca e narinas, ou aplicar gel hidrossolúvel sobre os pelos, restaura a vedação. Tricotomia prévia é a alternativa definitiva quando há tempo hábil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a idade é fator não modificável; a cânula orofaríngea auxilia a desobstrução por queda da língua, mas não altera o preditor nem garante vedação. (B) o índice de massa corporal não é corrigível no intraoperatório — o que se faz é otimizar posição em rampa e usar pressão positiva, e a escolha do modo ventilatório não neutraliza o risco de ventilação difícil sob máscara. (D) a pressão positiva contínua melhora a pré-oxigenação e retarda a dessaturação, porém a apneia obstrutiva do sono permanece como preditor de colapso de via aérea superior após a perda do tônus muscular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os preditores independentes de ventilação difícil sob máscara facial são reunidos em mnemônicos consagrados e incluem &lt;strong&gt;barba, obesidade, ausência de dentes, idade avançada, história de ronco ou apneia obstrutiva&lt;/strong&gt;, limitação da protrusão mandibular e Mallampati elevado. A presença de dois ou mais eleva substancialmente a probabilidade de ventilação difícil.&lt;/p&gt;&lt;p&gt;Desses fatores, apenas um é imediatamente modificável na sala: a barba. A interposição de pelos impede a vedação do coxim da máscara contra a pele. Recobrir a área com &lt;strong&gt;filme adesivo transparente&lt;/strong&gt;, recortando uma janela para boca e narinas, ou aplicar gel hidrossolúvel sobre os pelos, restaura a vedação. Tricotomia prévia é a alternativa definitiva quando há tempo hábil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a idade é fator não modificável; a cânula orofaríngea auxilia a desobstrução por queda da língua, mas não altera o preditor nem garante vedação. (B) o índice de massa corporal não é corrigível no intraoperatório: o que se faz é otimizar posição em rampa e usar pressão positiva, e a escolha do modo ventilatório não neutraliza o risco de ventilação difícil sob máscara. (D) a pressão positiva contínua melhora a pré-oxigenação e retarda a dessaturação, porém a apneia obstrutiva do sono permanece como preditor de colapso de via aérea superior após a perda do tônus muscular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O laringoespasmo é o fechamento reflexo e sustentado das cordas vocais e das estruturas supraglóticas, desencadeado por estímulo em plano anestésico intermediário — situação clássica na extubação de crianças submetidas a cirurgia de via aérea, em que sangue e secreções irritam a glote.&lt;/p&gt;&lt;p&gt;O manejo é escalonado e deve ser rápido: &lt;strong&gt;remover o estímulo&lt;/strong&gt;, aspirar a orofaringe, ofertar oxigênio a 100% com &lt;strong&gt;pressão positiva contínua&lt;/strong&gt; (10 a 20 cmH2O) mantendo elevação do mento, e aplicar pressão firme bilateral na &lt;strong&gt;incisura do laringoespasmo&lt;/strong&gt; (manobra de Larson), situada entre o processo mastoide, o ramo da mandíbula e a base do crânio. Se o quadro persistir com dessaturação, aprofunda-se com propofol (0,5 a 1 mg/kg) e, na refratariedade, administra-se &lt;strong&gt;suxametônio 0,1 a 0,5 mg/kg por via venosa&lt;/strong&gt; (ou 4 mg/kg por via intramuscular na ausência de acesso), frequentemente com atropina em crianças.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) adrenalina nebulizada trata edema subglótico, não espasmo glótico, e depende de fluxo aéreo inexistente na obstrução completa — aguardar resposta é perda de tempo crítico. (C) a reintubação sem tentativa prévia de resolução conservadora é agressiva, tecnicamente difícil com a glote cerrada e pode traumatizar a via aérea. (D) com a glote fechada não há captação alveolar de sevoflurano, de modo que o aprofundamento inalatório é ineficaz — o aprofundamento deve ser venoso.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O laringoespasmo é o fechamento reflexo e sustentado das cordas vocais e das estruturas supraglóticas, desencadeado por estímulo em plano anestésico intermediário, situação clássica na extubação de crianças submetidas a cirurgia de via aérea, em que sangue e secreções irritam a glote.&lt;/p&gt;&lt;p&gt;O manejo é escalonado e deve ser rápido: &lt;strong&gt;remover o estímulo&lt;/strong&gt;, aspirar a orofaringe, ofertar oxigênio a 100% com &lt;strong&gt;pressão positiva contínua&lt;/strong&gt; (10 a 20 cmH2O) mantendo elevação do mento, e aplicar pressão firme bilateral na &lt;strong&gt;incisura do laringoespasmo&lt;/strong&gt; (manobra de Larson), situada entre o processo mastoide, o ramo da mandíbula e a base do crânio. Se o quadro persistir com dessaturação, aprofunda-se com propofol (0,5 a 1 mg/kg) e, na refratariedade, administra-se &lt;strong&gt;suxametônio 0,1 a 0,5 mg/kg por via venosa&lt;/strong&gt; (ou 4 mg/kg por via intramuscular na ausência de acesso), frequentemente com atropina em crianças.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) adrenalina nebulizada trata edema subglótico, não espasmo glótico, e depende de fluxo aéreo inexistente na obstrução completa; aguardar resposta é perda de tempo crítico. (C) a reintubação sem tentativa prévia de resolução conservadora é agressiva, tecnicamente difícil com a glote cerrada e pode traumatizar a via aérea. (D) com a glote fechada não há captação alveolar de sevoflurano, de modo que o aprofundamento inalatório é ineficaz; o aprofundamento deve ser venoso.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A via aérea do lactente não é uma versão reduzida da do adulto. A &lt;strong&gt;laringe é mais cefálica&lt;/strong&gt;, projetando-se ao nível de C3 a C4 (contra C5 a C6 no adulto), o que aproxima a glote da base da língua e torna a visualização mais angulada. A &lt;strong&gt;epiglote é longa, estreita e em formato de ômega&lt;/strong&gt;, inclinando-se sobre a abertura glótica — daí a preferência tradicional pela &lt;strong&gt;lâmina reta&lt;/strong&gt;, que a eleva diretamente em vez de apenas tracioná-la pela valécula.&lt;/p&gt;&lt;p&gt;Completam o quadro: occipúcio proeminente, língua relativamente grande, região cricóidea e subglótica como zona mais estreita do funil laríngeo na criança pequena, e traqueia curta (poucos centímetros), com margem estreita entre intubação seletiva e extubação acidental.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o ângulo entre base da língua e glote é mais &lt;em&gt;agudo&lt;/em&gt; no lactente, dificultando o alinhamento dos eixos, razão pela qual a lâmina curva é menos favorável nessa idade. (C) a traqueia é proporcionalmente &lt;em&gt;curta&lt;/em&gt;; a flexão cervical aprofunda o tubo e a extensão o retrai, de modo que o risco de intubação seletiva é maior, e não menor. (D) o occipúcio é &lt;em&gt;proeminente&lt;/em&gt;, gerando flexão cervical espontânea em decúbito dorsal — o coxim deve ser colocado sob os ombros, não sob a cabeça.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A via aérea do lactente não é uma versão reduzida da do adulto. A &lt;strong&gt;laringe é mais cefálica&lt;/strong&gt;, projetando-se ao nível de C3 a C4 (contra C5 a C6 no adulto), o que aproxima a glote da base da língua e torna a visualização mais angulada. A &lt;strong&gt;epiglote é longa, estreita e em formato de ômega&lt;/strong&gt;, inclinando-se sobre a abertura glótica; daí a preferência tradicional pela &lt;strong&gt;lâmina reta&lt;/strong&gt;, que a eleva diretamente em vez de apenas tracioná-la pela valécula.&lt;/p&gt;&lt;p&gt;Completam o quadro: occipúcio proeminente, língua relativamente grande, região cricóidea e subglótica como zona mais estreita do funil laríngeo na criança pequena, e traqueia curta (poucos centímetros), com margem estreita entre intubação seletiva e extubação acidental.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o ângulo entre base da língua e glote é mais &lt;em&gt;agudo&lt;/em&gt; no lactente, dificultando o alinhamento dos eixos, razão pela qual a lâmina curva é menos favorável nessa idade. (C) a traqueia é proporcionalmente &lt;em&gt;curta&lt;/em&gt;; a flexão cervical aprofunda o tubo e a extensão o retrai, de modo que o risco de intubação seletiva é maior, e não menor. (D) o occipúcio é &lt;em&gt;proeminente&lt;/em&gt;, gerando flexão cervical espontânea em decúbito dorsal; o coxim deve ser colocado sob os ombros, não sob a cabeça.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O obeso dessatura rapidamente porque a &lt;strong&gt;capacidade residual funcional está reduzida&lt;/strong&gt; pelo aumento da pressão abdominal e da massa da parede torácica, enquanto o consumo de oxigênio está aumentado. O reservatório alveolar é menor e é esvaziado mais depressa.&lt;/p&gt;&lt;p&gt;A estratégia com maior impacto combina três elementos: &lt;strong&gt;posição em rampa&lt;/strong&gt;, alinhando o meato acústico externo à fúrcula esternal, com proclive de 25 a 30 graus, o que descomprime o diafragma e aumenta a CRF; &lt;strong&gt;FiO2 de 1,0&lt;/strong&gt; até fração expirada de oxigênio igual ou superior a 0,90; e &lt;strong&gt;pressão positiva contínua de 8 a 10 cmH2O&lt;/strong&gt;, mantida também como PEEP após a indução, que previne o colapso alveolar dependente. Essa combinação pode dobrar o tempo até a dessaturação em relação à pré-oxigenação convencional em decúbito.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o decúbito dorsal horizontal é justamente a posição que mais reduz a CRF no obeso; prolongar o tempo de pré-oxigenação não compensa a perda de volume pulmonar. (B) o Trendelenburg desloca o conteúdo abdominal em direção cefálica e &lt;em&gt;reduz&lt;/em&gt; ainda mais a capacidade residual funcional, além de aumentar o risco de regurgitação. (C) reduzir a FiO2 diminui a formação de atelectasias, mas às custas de um reservatório alveolar menor — troca desfavorável em paciente com margem de apneia já criticamente curta; o controle da atelectasia se faz com PEEP e recrutamento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O obeso dessatura rapidamente porque a &lt;strong&gt;capacidade residual funcional está reduzida&lt;/strong&gt; pelo aumento da pressão abdominal e da massa da parede torácica, enquanto o consumo de oxigênio está aumentado. O reservatório alveolar é menor e é esvaziado mais depressa.&lt;/p&gt;&lt;p&gt;A estratégia com maior impacto combina três elementos: &lt;strong&gt;posição em rampa&lt;/strong&gt;, alinhando o meato acústico externo à fúrcula esternal, com proclive de 25 a 30 graus, o que descomprime o diafragma e aumenta a CRF; &lt;strong&gt;FiO2 de 1,0&lt;/strong&gt; até fração expirada de oxigênio igual ou superior a 0,90; e &lt;strong&gt;pressão positiva contínua de 8 a 10 cmH2O&lt;/strong&gt;, mantida também como PEEP após a indução, que previne o colapso alveolar dependente. Essa combinação pode dobrar o tempo até a dessaturação em relação à pré-oxigenação convencional em decúbito.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o decúbito dorsal horizontal é justamente a posição que mais reduz a CRF no obeso; prolongar o tempo de pré-oxigenação não compensa a perda de volume pulmonar. (B) o Trendelenburg desloca o conteúdo abdominal em direção cefálica e &lt;em&gt;reduz&lt;/em&gt; ainda mais a capacidade residual funcional, além de aumentar o risco de regurgitação. (C) reduzir a FiO2 diminui a formação de atelectasias, mas às custas de um reservatório alveolar menor, troca desfavorável em paciente com margem de apneia já criticamente curta; o controle da atelectasia se faz com PEEP e recrutamento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A confirmação da posição traqueal é feita pela &lt;strong&gt;capnografia sustentada&lt;/strong&gt;: a presença de CO&lt;sub&gt;2&lt;/sub&gt; expirado com curva característica mantida por pelo menos seis ventilações consecutivas. Esse é o padrão de referência porque nenhum sinal clínico isolado é confiável.&lt;/p&gt;&lt;p&gt;O quadro descrito é a apresentação clássica da &lt;strong&gt;intubação esofágica&lt;/strong&gt;. Ar deglutido durante a ventilação sob máscara, bebidas gaseificadas ou antiácidos deixam CO&lt;sub&gt;2&lt;/sub&gt; no estômago, o que produz algumas insuflações com valores baixos que &lt;strong&gt;se extinguem rapidamente&lt;/strong&gt; por lavagem do reservatório gástrico. Condensação no tubo, expansão torácica e ausculta podem estar todas falsamente presentes, sobretudo após laringoscopia difícil. Diante da dúvida com dessaturação progressiva, retira-se o tubo e reoxigena-se o paciente — a máxima é que, na incerteza, o tubo sai.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) no broncoespasmo a curva de CO&lt;sub&gt;2&lt;/sub&gt; persiste, ainda que com morfologia alterada e ascensão lenta; o desaparecimento completo do traçado não é compatível. (C) a intubação seletiva mantém capnografia normal e cursa com assimetria de ausculta, o que não ocorre aqui. (D) atribuir a ausência de CO&lt;sub&gt;2&lt;/sub&gt; a defeito técnico do monitor em paciente que dessatura é o erro mais perigoso desse cenário; o monitor só deve ser questionado depois de excluída a posição esofágica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A confirmação da posição traqueal é feita pela &lt;strong&gt;capnografia sustentada&lt;/strong&gt;: a presença de CO&lt;sub&gt;2&lt;/sub&gt; expirado com curva característica mantida por pelo menos seis ventilações consecutivas. Esse é o padrão de referência porque nenhum sinal clínico isolado é confiável.&lt;/p&gt;&lt;p&gt;O quadro descrito é a apresentação clássica da &lt;strong&gt;intubação esofágica&lt;/strong&gt;. Ar deglutido durante a ventilação sob máscara, bebidas gaseificadas ou antiácidos deixam CO&lt;sub&gt;2&lt;/sub&gt; no estômago, o que produz algumas insuflações com valores baixos que &lt;strong&gt;se extinguem rapidamente&lt;/strong&gt; por lavagem do reservatório gástrico. Condensação no tubo, expansão torácica e ausculta podem estar todas falsamente presentes, sobretudo após laringoscopia difícil. Diante da dúvida com dessaturação progressiva, retira-se o tubo e reoxigena-se o paciente; a máxima é que, na incerteza, o tubo sai.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) no broncoespasmo a curva de CO&lt;sub&gt;2&lt;/sub&gt; persiste, ainda que com morfologia alterada e ascensão lenta; o desaparecimento completo do traçado não é compatível. (C) a intubação seletiva mantém capnografia normal e cursa com assimetria de ausculta, o que não ocorre aqui. (D) atribuir a ausência de CO&lt;sub&gt;2&lt;/sub&gt; a defeito técnico do monitor em paciente que dessatura é o erro mais perigoso desse cenário; o monitor só deve ser questionado depois de excluída a posição esofágica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O edema pulmonar por pressão negativa é complicação típica de &lt;strong&gt;homens jovens e musculosos&lt;/strong&gt;, capazes de gerar esforço inspiratório muito vigoroso contra uma via aérea ocluída — laringoespasmo, mordedura do tubo ou obstrução por corpo estranho.&lt;/p&gt;&lt;p&gt;O mecanismo é hemodinâmico e mecânico. A inspiração contra glote fechada gera pressões intrapleurais da ordem de -50 a -100 cmH2O. Isso &lt;strong&gt;aumenta o retorno venoso&lt;/strong&gt; ao ventrículo direito, &lt;strong&gt;eleva a pós-carga do ventrículo esquerdo&lt;/strong&gt; pelo aumento da pressão transmural e, sobretudo, torna fortemente negativa a pressão intersticial peribrônquica. O resultado é um &lt;strong&gt;gradiente de pressão transcapilar&lt;/strong&gt; que empurra líquido do capilar para o interstício e o alvéolo. A descarga adrenérgica associada contribui pela redistribuição de volume para o leito pulmonar.&lt;/p&gt;&lt;p&gt;O tratamento é essencialmente de suporte: oxigênio, pressão positiva não invasiva ou reintubação com PEEP quando necessário. A resolução costuma ocorrer em 12 a 48 horas, e o benefício dos diuréticos é questionável, já que o paciente em geral não está hipervolêmico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) não houve regurgitação e a aspiração cursa habitualmente com achados assimétricos e febre, com evolução mais arrastada. (C) trata-se de jovem sem cardiopatia, com pressão arterial normal e sem sinais de disfunção ventricular. (D) a anafilaxia se manifesta minutos após a exposição, com hipotensão, broncoespasmo e sinais cutâneos, ausentes neste caso.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O edema pulmonar por pressão negativa é complicação típica de &lt;strong&gt;homens jovens e musculosos&lt;/strong&gt;, capazes de gerar esforço inspiratório muito vigoroso contra uma via aérea ocluída por laringoespasmo, mordedura do tubo ou obstrução por corpo estranho.&lt;/p&gt;&lt;p&gt;O mecanismo é hemodinâmico e mecânico. A inspiração contra glote fechada gera pressões intrapleurais da ordem de -50 a -100 cmH2O. Isso &lt;strong&gt;aumenta o retorno venoso&lt;/strong&gt; ao ventrículo direito, &lt;strong&gt;eleva a pós-carga do ventrículo esquerdo&lt;/strong&gt; pelo aumento da pressão transmural e, sobretudo, torna fortemente negativa a pressão intersticial peribrônquica. O resultado é um &lt;strong&gt;gradiente de pressão transcapilar&lt;/strong&gt; que empurra líquido do capilar para o interstício e o alvéolo. A descarga adrenérgica associada contribui pela redistribuição de volume para o leito pulmonar.&lt;/p&gt;&lt;p&gt;O tratamento é essencialmente de suporte: oxigênio, pressão positiva não invasiva ou reintubação com PEEP quando necessário. A resolução costuma ocorrer em 12 a 48 horas, e o benefício dos diuréticos é questionável, já que o paciente em geral não está hipervolêmico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) não houve regurgitação e a aspiração cursa habitualmente com achados assimétricos e febre, com evolução mais arrastada. (C) trata-se de jovem sem cardiopatia, com pressão arterial normal e sem sinais de disfunção ventricular. (D) a anafilaxia se manifesta minutos após a exposição, com hipotensão, broncoespasmo e sinais cutâneos, ausentes neste caso.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de hipoxemia perioperatória, o raciocínio deve percorrer as cinco causas clássicas: baixa PiO&lt;sub&gt;2&lt;/sub&gt;, hipoventilação, distúrbio de difusão, desequilíbrio ventilação-perfusão e shunt. A &lt;strong&gt;resposta ao oxigênio suplementar&lt;/strong&gt; é o principal discriminador à beira do leito.&lt;/p&gt;&lt;p&gt;Aqui, a PaCO&lt;sub&gt;2&lt;/sub&gt; normal afasta hipoventilação, e a hipoxemia é &lt;strong&gt;refratária&lt;/strong&gt; ao aumento expressivo da FiO2 — comportamento característico do &lt;strong&gt;shunt verdadeiro&lt;/strong&gt;, em que sangue venoso atravessa unidades sem ventilação alguma e não tem contato com gás alveolar, por mais rico em oxigênio que ele seja. A causa mais frequente no pós-operatório de laparotomia é a &lt;strong&gt;atelectasia em zonas dependentes&lt;/strong&gt;, favorecida por redução da CRF, dor, disfunção diafragmática e ventilação prolongada. O tratamento é recrutamento alveolar: pressão positiva não invasiva, fisioterapia, analgesia adequada e mobilização, e não simplesmente mais oxigênio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipoventilação cursa com &lt;em&gt;hipercapnia&lt;/em&gt;; com PaCO&lt;sub&gt;2&lt;/sub&gt; de 41 mmHg o diagnóstico não se sustenta, e a hipoxemia por hipoventilação corrige facilmente com oxigênio suplementar. (B) o distúrbio de difusão é causa rara de hipoxemia em repouso e, por definição, responde bem ao aumento da FiO2, ao contrário do observado. (D) a baixa PiO&lt;sub&gt;2&lt;/sub&gt; ocorre em altitude ou por erro de mistura de gases no aparelho, situações que não se aplicam a paciente sob máscara com reservatório em sala de recuperação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de hipoxemia perioperatória, o raciocínio deve percorrer as cinco causas clássicas: baixa PiO&lt;sub&gt;2&lt;/sub&gt;, hipoventilação, distúrbio de difusão, desequilíbrio ventilação-perfusão e shunt. A &lt;strong&gt;resposta ao oxigênio suplementar&lt;/strong&gt; é o principal discriminador à beira do leito.&lt;/p&gt;&lt;p&gt;Aqui, a PaCO&lt;sub&gt;2&lt;/sub&gt; normal afasta hipoventilação, e a hipoxemia é &lt;strong&gt;refratária&lt;/strong&gt; ao aumento expressivo da FiO2, comportamento característico do &lt;strong&gt;shunt verdadeiro&lt;/strong&gt;, em que sangue venoso atravessa unidades sem ventilação alguma e não tem contato com gás alveolar, por mais rico em oxigênio que ele seja. A causa mais frequente no pós-operatório de laparotomia é a &lt;strong&gt;atelectasia em zonas dependentes&lt;/strong&gt;, favorecida por redução da CRF, dor, disfunção diafragmática e ventilação prolongada. O tratamento é recrutamento alveolar: pressão positiva não invasiva, fisioterapia, analgesia adequada e mobilização, e não simplesmente mais oxigênio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipoventilação cursa com &lt;em&gt;hipercapnia&lt;/em&gt;; com PaCO&lt;sub&gt;2&lt;/sub&gt; de 41 mmHg o diagnóstico não se sustenta, e a hipoxemia por hipoventilação corrige facilmente com oxigênio suplementar. (B) o distúrbio de difusão é causa rara de hipoxemia em repouso e, por definição, responde bem ao aumento da FiO2, ao contrário do observado. (D) a baixa PiO&lt;sub&gt;2&lt;/sub&gt; ocorre em altitude ou por erro de mistura de gases no aparelho, situações que não se aplicam a paciente sob máscara com reservatório em sala de recuperação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de aspiração presenciada, a prioridade é &lt;strong&gt;evitar que o material seja empurrado para a periferia&lt;/strong&gt; pela pressão positiva. A sequência consagrada é: aspirar a orofaringe, posicionar a mesa em Trendelenburg ou lateralizar a cabeça quando a via aérea ainda não está protegida, &lt;strong&gt;intubar rapidamente&lt;/strong&gt; e aspirar pelo tubo antes de iniciar a ventilação com pressão positiva, desde que o grau de hipoxemia permita esses poucos segundos.&lt;/p&gt;&lt;p&gt;Em seguida, institui-se suporte: oxigênio suplementar titulado, PEEP e ventilação protetora. A lesão inicial é &lt;strong&gt;química&lt;/strong&gt; (síndrome de Mendelson), com gravidade classicamente relacionada a pH inferior a 2,5 e volume superior a 25 mL, e não infecciosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) ventilar sob pressão positiva antes de aspirar dissemina o conteúdo para os brônquios distais e agrava a lesão; essa etapa só se antecipa diante de hipoxemia crítica que não tolera qualquer demora. (B) corticoides não demonstraram benefício na pneumonite aspirativa e podem retardar a resolução; antibiótico não é profilático de rotina, sendo reservado para aspiração de conteúdo francamente contaminado, como na obstrução intestinal estabelecida com material fecaloide, ou para infecção documentada na evolução. (C) a lavagem brônquica com solução salina não é indicada — o dano ácido é praticamente instantâneo, e o líquido instilado apenas redistribui o material e piora a troca gasosa; a aspiração deve ser feita sem instilação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de aspiração presenciada, a prioridade é &lt;strong&gt;evitar que o material seja empurrado para a periferia&lt;/strong&gt; pela pressão positiva. A sequência consagrada é: aspirar a orofaringe, posicionar a mesa em Trendelenburg ou lateralizar a cabeça quando a via aérea ainda não está protegida, &lt;strong&gt;intubar rapidamente&lt;/strong&gt; e aspirar pelo tubo antes de iniciar a ventilação com pressão positiva, desde que o grau de hipoxemia permita esses poucos segundos.&lt;/p&gt;&lt;p&gt;Em seguida, institui-se suporte: oxigênio suplementar titulado, PEEP e ventilação protetora. A lesão inicial é &lt;strong&gt;química&lt;/strong&gt; (síndrome de Mendelson), com gravidade classicamente relacionada a pH inferior a 2,5 e volume superior a 25 mL, e não infecciosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) ventilar sob pressão positiva antes de aspirar dissemina o conteúdo para os brônquios distais e agrava a lesão; essa etapa só se antecipa diante de hipoxemia crítica que não tolera qualquer demora. (B) corticoides não demonstraram benefício na pneumonite aspirativa e podem retardar a resolução; antibiótico não é profilático de rotina, sendo reservado para aspiração de conteúdo francamente contaminado, como na obstrução intestinal estabelecida com material fecaloide, ou para infecção documentada na evolução. (C) a lavagem brônquica com solução salina não é indicada: o dano ácido é praticamente instantâneo, e o líquido instilado apenas redistribui o material e piora a troca gasosa; a aspiração deve ser feita sem instilação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A embolia venosa aérea ocorre quando há gradiente de pressão negativo entre o sítio cirúrgico e o átrio direito — situação típica da posição sentada, em que o campo operatório está acima do coração. O ar aprisionado no trato de saída do ventrículo direito gera obstrução mecânica, aumento do espaço morto e colapso hemodinâmico.&lt;/p&gt;&lt;p&gt;Os métodos de detecção ordenam-se por sensibilidade decrescente: &lt;strong&gt;ecocardiografia transesofágica&lt;/strong&gt; (limiar em torno de 0,02 mL/kg), &lt;strong&gt;Doppler precordial&lt;/strong&gt; (cerca de 0,05 mL/kg), pressão de artéria pulmonar, &lt;strong&gt;nitrogênio expirado&lt;/strong&gt;, &lt;strong&gt;capnografia&lt;/strong&gt;, e por fim os sinais tardios — hipotensão, arritmias, dessaturação e o sopro em roda de moinho.&lt;/p&gt;&lt;p&gt;O manejo imediato inclui avisar o cirurgião e inundar o campo com solução salina, comprimir as veias jugulares, suspender óxido nitroso, ofertar FiO2 de 1,0, posicionar em decúbito lateral esquerdo com cabeceira baixa e aspirar ar por cateter posicionado no átrio direito, além de suporte vasopressor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a capnografia é sensível, de leitura contínua e amplamente disponível, mas detecta volumes maiores que a ecocardiografia transesofágica e o Doppler precordial. (C) a dessaturação é manifestação tardia, que surge quando a repercussão hemodinâmica e de espaço morto já está estabelecida. (D) o sopro em roda de moinho exige volumes grandes de ar, é de percepção subjetiva e frequentemente não é audível em meio ao ruído da sala, tratando-se de sinal tardio e pouco sensível.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A embolia venosa aérea ocorre quando há gradiente de pressão negativo entre o sítio cirúrgico e o átrio direito, situação típica da posição sentada, em que o campo operatório está acima do coração. O ar aprisionado no trato de saída do ventrículo direito gera obstrução mecânica, aumento do espaço morto e colapso hemodinâmico.&lt;/p&gt;&lt;p&gt;Os métodos de detecção ordenam-se por sensibilidade decrescente: &lt;strong&gt;ecocardiografia transesofágica&lt;/strong&gt; (limiar em torno de 0,02 mL/kg), &lt;strong&gt;Doppler precordial&lt;/strong&gt; (cerca de 0,05 mL/kg), pressão de artéria pulmonar, &lt;strong&gt;nitrogênio expirado&lt;/strong&gt;, &lt;strong&gt;capnografia&lt;/strong&gt;, e por fim os sinais tardios: hipotensão, arritmias, dessaturação e o sopro em roda de moinho.&lt;/p&gt;&lt;p&gt;O manejo imediato inclui avisar o cirurgião e inundar o campo com solução salina, comprimir as veias jugulares, suspender óxido nitroso, ofertar FiO2 de 1,0, posicionar em decúbito lateral esquerdo com cabeceira baixa e aspirar ar por cateter posicionado no átrio direito, além de suporte vasopressor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a capnografia é sensível, de leitura contínua e amplamente disponível, mas detecta volumes maiores que a ecocardiografia transesofágica e o Doppler precordial. (C) a dessaturação é manifestação tardia, que surge quando a repercussão hemodinâmica e de espaço morto já está estabelecida. (D) o sopro em roda de moinho exige volumes grandes de ar, é de percepção subjetiva e frequentemente não é audível em meio ao ruído da sala, tratando-se de sinal tardio e pouco sensível.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cefaleia pós-punção dural resulta da perda contínua de líquido cefalorraquidiano pelo orifício dural, com queda da pressão liquórica, tração das estruturas meníngeas sensíveis à dor e vasodilatação compensatória. O caráter &lt;strong&gt;postural&lt;/strong&gt; é o traço definidor: piora em minutos ao sentar ou levantar e alivia em decúbito. Sintomas associados incluem cervicalgia, zumbido, hipoacusia, fotofobia e, ocasionalmente, diplopia por estiramento do sexto par craniano.&lt;/p&gt;&lt;p&gt;O risco é máximo quando a dura-máter é perfurada por agulha calibrosa de ponta cortante, como no caso descrito — a punção acidental com agulha de Tuohy em jovem, mulher e gestante reúne todos os fatores de risco, com incidência que pode ultrapassar 50%.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;tampão sanguíneo peridural&lt;/strong&gt; é o tratamento definitivo: injetam-se 15 a 20 mL de sangue autólogo no espaço peridural, com taxa de sucesso de 70% a 90%. Indica-se em cefaleia intensa, incapacitante ou refratária ao tratamento conservador, habitualmente após 24 a 48 horas do início.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) repouso e hidratação proporcionam alívio sintomático apenas enquanto a paciente permanece deitada e não alteram a incidência nem a história natural do quadro. (C) o quadro é típico e não há sinais de alarme; nova punção lombar agravaria a perda liquórica. (D) corticoides não constituem tratamento de escolha; o arsenal conservador inclui analgésicos, cafeína e hidratação, com o tampão sanguíneo como conduta definitiva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cefaleia pós-punção dural resulta da perda contínua de líquido cefalorraquidiano pelo orifício dural, com queda da pressão liquórica, tração das estruturas meníngeas sensíveis à dor e vasodilatação compensatória. O caráter &lt;strong&gt;postural&lt;/strong&gt; é o traço definidor: piora em minutos ao sentar ou levantar e alivia em decúbito. Sintomas associados incluem cervicalgia, zumbido, hipoacusia, fotofobia e, ocasionalmente, diplopia por estiramento do sexto par craniano.&lt;/p&gt;&lt;p&gt;O risco é máximo quando a dura-máter é perfurada por agulha calibrosa de ponta cortante, como no caso descrito: a punção acidental com agulha de Tuohy em jovem, mulher e gestante reúne todos os fatores de risco, com incidência que pode ultrapassar 50%.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;tampão sanguíneo peridural&lt;/strong&gt; é o tratamento definitivo: injetam-se 15 a 20 mL de sangue autólogo no espaço peridural, com taxa de sucesso de 70% a 90%. Indica-se em cefaleia intensa, incapacitante ou refratária ao tratamento conservador, habitualmente após 24 a 48 horas do início.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) repouso e hidratação proporcionam alívio sintomático apenas enquanto a paciente permanece deitada e não alteram a incidência nem a história natural do quadro. (C) o quadro é típico e não há sinais de alarme; nova punção lombar agravaria a perda liquórica. (D) corticoides não constituem tratamento de escolha; o arsenal conservador inclui analgésicos, cafeína e hidratação, com o tampão sanguíneo como conduta definitiva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipertermia maligna é uma miopatia farmacogenética, de herança autossômica dominante com penetrância variável, ligada com maior frequência a mutações do receptor de rianodina. A exposição ao agente desencadeante provoca liberação descontrolada de cálcio do retículo sarcoplasmático, hipermetabolismo muscular, produção maciça de CO&lt;sub&gt;2&lt;/sub&gt;, acidose, rigidez, rabdomiólise e hipertermia.&lt;/p&gt;&lt;p&gt;Os desencadeantes são apenas dois grupos: &lt;strong&gt;todos os anestésicos inalatórios halogenados&lt;/strong&gt; (halotano, isoflurano, sevoflurano, desflurano) e o &lt;strong&gt;suxametônio&lt;/strong&gt;. Parente de primeiro grau de indivíduo com suscetibilidade comprovada deve ser tratado como suscetível até prova em contrário.&lt;/p&gt;&lt;p&gt;São seguros: &lt;strong&gt;propofol, etomidato, cetamina, opioides, benzodiazepínicos, óxido nitroso, bloqueadores neuromusculares adespolarizantes e todos os anestésicos locais&lt;/strong&gt;. A conduta ideal é anestesia venosa total ou técnica regional, com máquina preparada — vaporizadores removidos ou lacrados, circuito e cal sodada trocados, lavagem com fluxo alto ou uso de filtros de carvão ativado — e dantroleno disponível na dose inicial de 2,5 mg/kg, repetível até cerca de 10 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (B) mantêm halogenado, o desencadeante principal, o que é inaceitável em suscetível, por mais rigorosa que seja a monitorização. (C) o bloqueio do neuroeixo é excelente escolha, mas a justificativa é falsa: anestésicos locais amida, incluindo a bupivacaína, são seguros na hipertermia maligna, e a restrição antiga a esse grupo foi abandonada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipertermia maligna é uma miopatia farmacogenética, de herança autossômica dominante com penetrância variável, ligada com maior frequência a mutações do receptor de rianodina. A exposição ao agente desencadeante provoca liberação descontrolada de cálcio do retículo sarcoplasmático, hipermetabolismo muscular, produção maciça de CO&lt;sub&gt;2&lt;/sub&gt;, acidose, rigidez, rabdomiólise e hipertermia.&lt;/p&gt;&lt;p&gt;Os desencadeantes são apenas dois grupos: &lt;strong&gt;todos os anestésicos inalatórios halogenados&lt;/strong&gt; (halotano, isoflurano, sevoflurano, desflurano) e o &lt;strong&gt;suxametônio&lt;/strong&gt;. Parente de primeiro grau de indivíduo com suscetibilidade comprovada deve ser tratado como suscetível até prova em contrário.&lt;/p&gt;&lt;p&gt;São seguros: &lt;strong&gt;propofol, etomidato, cetamina, opioides, benzodiazepínicos, óxido nitroso, bloqueadores neuromusculares adespolarizantes e todos os anestésicos locais&lt;/strong&gt;. A conduta ideal é anestesia venosa total ou técnica regional, com máquina preparada (vaporizadores removidos ou lacrados, circuito e cal sodada trocados, lavagem com fluxo alto ou uso de filtros de carvão ativado) e dantroleno disponível na dose inicial de 2,5 mg/kg, repetível até cerca de 10 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (B) mantêm halogenado, o desencadeante principal, o que é inaceitável em suscetível, por mais rigorosa que seja a monitorização. (C) o bloqueio do neuroeixo é excelente escolha, mas a justificativa é falsa: anestésicos locais amida, incluindo a bupivacaína, são seguros na hipertermia maligna, e a restrição antiga a esse grupo foi abandonada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A anafilaxia perioperatória combina broncoespasmo, colapso cardiovascular e manifestações cutâneas, sendo os &lt;strong&gt;bloqueadores neuromusculares&lt;/strong&gt; a causa mais frequente no ambiente cirúrgico, seguidos por antibióticos, látex e clorexidina. A hipotensão decorre de vasodilatação intensa somada a extravasamento capilar, com perda de até 35% do volume intravascular em minutos.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;adrenalina é o tratamento de primeira linha&lt;/strong&gt; e não deve ser postergada. Por via venosa, com monitorização em curso, administra-se em &lt;strong&gt;bolus titulados&lt;/strong&gt;: 10 a 50 mcg nos quadros moderados, escalonando para 100 a 200 mcg ou mais no colapso, repetidos a cada um a dois minutos até resposta, com progressão para infusão contínua se necessário. Justifica-se pela ação combinada — alfa-1 revertendo a vasodilatação, beta-1 sustentando o débito e beta-2 promovendo broncodilatação e inibindo a degranulação de mastócitos. A &lt;strong&gt;expansão volêmica vigorosa&lt;/strong&gt; com cristaloide é indissociável do tratamento. Corticoide e anti-histamínico são adjuvantes de segunda linha. A dosagem de triptase sérica, colhida entre uma e duas horas do evento, apoia a confirmação diagnóstica posterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) corticoide tem latência de horas e não trata o colapso agudo; usá-lo como medida inicial é erro clássico. (B) a noradrenalina não é a droga de escolha por carecer de ação beta-2 broncodilatadora e de efeito estabilizador sobre mastócitos, cabendo-lhe papel apenas em choque refratário. (C) o sugamadex encapsula o rocurônio, mas não reverte a cascata já deflagrada de mediadores nem substitui a adrenalina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A anafilaxia perioperatória combina broncoespasmo, colapso cardiovascular e manifestações cutâneas, sendo os &lt;strong&gt;bloqueadores neuromusculares&lt;/strong&gt; a causa mais frequente no ambiente cirúrgico, seguidos por antibióticos, látex e clorexidina. A hipotensão decorre de vasodilatação intensa somada a extravasamento capilar, com perda de até 35% do volume intravascular em minutos.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;adrenalina é o tratamento de primeira linha&lt;/strong&gt; e não deve ser postergada. Por via venosa, com monitorização em curso, administra-se em &lt;strong&gt;bolus titulados&lt;/strong&gt;: 10 a 50 mcg nos quadros moderados, escalonando para 100 a 200 mcg ou mais no colapso, repetidos a cada um a dois minutos até resposta, com progressão para infusão contínua se necessário. Justifica-se pela ação combinada: alfa-1 revertendo a vasodilatação, beta-1 sustentando o débito e beta-2 promovendo broncodilatação e inibindo a degranulação de mastócitos. A &lt;strong&gt;expansão volêmica vigorosa&lt;/strong&gt; com cristaloide é indissociável do tratamento. Corticoide e anti-histamínico são adjuvantes de segunda linha. A dosagem de triptase sérica, colhida entre uma e duas horas do evento, apoia a confirmação diagnóstica posterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) corticoide tem latência de horas e não trata o colapso agudo; usá-lo como medida inicial é erro clássico. (B) a noradrenalina não é a droga de escolha por carecer de ação beta-2 broncodilatadora e de efeito estabilizador sobre mastócitos, cabendo-lhe papel apenas em choque refratário. (C) o sugamadex encapsula o rocurônio, mas não reverte a cascata já deflagrada de mediadores nem substitui a adrenalina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A raquianestesia total ocorre quando dose destinada ao espaço peridural alcança o espaço subaracnóideo — por punção dural não reconhecida ou migração do cateter — e produz bloqueio de extensão cefálica extrema. A gestante é particularmente vulnerável pela redução do volume do espaço peridural, secundária à ingurgitação dos plexos venosos.&lt;/p&gt;&lt;p&gt;A progressão dos sinais é característica e reflete a subida do nível de bloqueio: &lt;strong&gt;dormência em mãos e antebraços&lt;/strong&gt; (raízes C6-C8), &lt;strong&gt;dispneia e voz fraca&lt;/strong&gt; pelo bloqueio da musculatura acessória e intercostal, &lt;strong&gt;hipotensão grave&lt;/strong&gt; por simpatectomia extensa, &lt;strong&gt;bradicardia&lt;/strong&gt; por bloqueio das fibras cardioaceleradoras torácicas altas (T1-T4) e, finalmente, &lt;strong&gt;apneia e perda de consciência&lt;/strong&gt; por comprometimento do frênico e hipoperfusão do tronco encefálico.&lt;/p&gt;&lt;p&gt;O tratamento é de suporte imediato e integralmente reversível se conduzido corretamente: assumir a via aérea com ventilação e oxigênio a 100%, intubar, administrar vasopressor (efedrina, fenilefrina ou adrenalina conforme a gravidade), atropina para a bradicardia, volume, deslocamento uterino à esquerda e manutenção da sedação até a regressão do bloqueio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade sistêmica cursa com pródromos neurológicos, como sabor metálico, zumbido, agitação e convulsão, precedendo o colapso, e não com bloqueio sensitivo ascendente. (B) o bloqueio subdural tem latência mais longa, de 15 a 30 minutos, e bloqueio motor desproporcionalmente pequeno; ademais, nunca se deve apenas aguardar diante de apneia. (D) a síncope vasovagal não produz dormência ascendente, apneia sustentada nem bloqueio motor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A raquianestesia total ocorre quando dose destinada ao espaço peridural alcança o espaço subaracnóideo (por punção dural não reconhecida ou migração do cateter) e produz bloqueio de extensão cefálica extrema. A gestante é particularmente vulnerável pela redução do volume do espaço peridural, secundária à ingurgitação dos plexos venosos.&lt;/p&gt;&lt;p&gt;A progressão dos sinais é característica e reflete a subida do nível de bloqueio: &lt;strong&gt;dormência em mãos e antebraços&lt;/strong&gt; (raízes C6-C8), &lt;strong&gt;dispneia e voz fraca&lt;/strong&gt; pelo bloqueio da musculatura acessória e intercostal, &lt;strong&gt;hipotensão grave&lt;/strong&gt; por simpatectomia extensa, &lt;strong&gt;bradicardia&lt;/strong&gt; por bloqueio das fibras cardioaceleradoras torácicas altas (T1-T4) e, finalmente, &lt;strong&gt;apneia e perda de consciência&lt;/strong&gt; por comprometimento do frênico e hipoperfusão do tronco encefálico.&lt;/p&gt;&lt;p&gt;O tratamento é de suporte imediato e integralmente reversível se conduzido corretamente: assumir a via aérea com ventilação e oxigênio a 100%, intubar, administrar vasopressor (efedrina, fenilefrina ou adrenalina conforme a gravidade), atropina para a bradicardia, volume, deslocamento uterino à esquerda e manutenção da sedação até a regressão do bloqueio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade sistêmica cursa com pródromos neurológicos, como sabor metálico, zumbido, agitação e convulsão, precedendo o colapso, e não com bloqueio sensitivo ascendente. (B) o bloqueio subdural tem latência mais longa, de 15 a 30 minutos, e bloqueio motor desproporcionalmente pequeno; ademais, nunca se deve apenas aguardar diante de apneia. (D) a síncope vasovagal não produz dormência ascendente, apneia sustentada nem bloqueio motor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipoventilação é a principal causa de hipercapnia na sala de recuperação e reúne aqui vários fatores de risco somados: obesidade, opioide titulado por via venosa, dor, possível bloqueio neuromuscular residual e efeito residual dos anestésicos sobre a resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;O ponto central é reconhecer a &lt;strong&gt;limitação da oximetria de pulso como monitor de ventilação&lt;/strong&gt;. A saturação reflete oxigenação, não ventilação. Sob oxigênio suplementar, a pressão alveolar de oxigênio permanece elevada mesmo com hipoventilação acentuada, de modo que a PaCO&lt;sub&gt;2&lt;/sub&gt; pode subir de forma expressiva antes que a saturação caia — o alarme dispara tarde, por vezes já na iminência de apneia. A &lt;strong&gt;capnografia&lt;/strong&gt;, por medir diretamente o CO&lt;sub&gt;2&lt;/sub&gt; expirado e a frequência respiratória, detecta hipoventilação, apneia e obstrução muito antes.&lt;/p&gt;&lt;p&gt;Somam-se a isso medidas gerais: estimulação, elevação da cabeceira, revisão da titulação de opioide, avaliação da curarização residual pelo estimulador de nervo periférico e analgesia multimodal poupadora de opioide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) é justamente o erro conceitual da questão — a oximetria isolada é insensível à hipoventilação sob oxigênio. (B) retirar o oxigênio para &lt;em&gt;provocar&lt;/em&gt; dessaturação como método de vigilância é conduta iatrogênica, que expõe o paciente à hipoxemia em vez de monitorizá-lo. (C) a radiografia pode auxiliar no diagnóstico de atelectasia ou derrame, mas não monitoriza ventilação nem responde à necessidade de vigilância contínua neste momento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipoventilação é a principal causa de hipercapnia na sala de recuperação e reúne aqui vários fatores de risco somados: obesidade, opioide titulado por via venosa, dor, possível bloqueio neuromuscular residual e efeito residual dos anestésicos sobre a resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;O ponto central é reconhecer a &lt;strong&gt;limitação da oximetria de pulso como monitor de ventilação&lt;/strong&gt;. A saturação reflete oxigenação, não ventilação. Sob oxigênio suplementar, a pressão alveolar de oxigênio permanece elevada mesmo com hipoventilação acentuada, de modo que a PaCO&lt;sub&gt;2&lt;/sub&gt; pode subir de forma expressiva antes que a saturação caia; o alarme dispara tarde, por vezes já na iminência de apneia. A &lt;strong&gt;capnografia&lt;/strong&gt;, por medir diretamente o CO&lt;sub&gt;2&lt;/sub&gt; expirado e a frequência respiratória, detecta hipoventilação, apneia e obstrução muito antes.&lt;/p&gt;&lt;p&gt;Somam-se a isso medidas gerais: estimulação, elevação da cabeceira, revisão da titulação de opioide, avaliação da curarização residual pelo estimulador de nervo periférico e analgesia multimodal poupadora de opioide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) é justamente o erro conceitual da questão: a oximetria isolada é insensível à hipoventilação sob oxigênio. (B) retirar o oxigênio para &lt;em&gt;provocar&lt;/em&gt; dessaturação como método de vigilância é conduta iatrogênica, que expõe o paciente à hipoxemia em vez de monitorizá-lo. (C) a radiografia pode auxiliar no diagnóstico de atelectasia ou derrame, mas não monitoriza ventilação nem responde à necessidade de vigilância contínua neste momento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A recuperação é dividida em fases. A &lt;strong&gt;fase I&lt;/strong&gt; abrange o despertar imediato, com vigilância intensiva de via aérea, hemodinâmica e consciência, sendo o escore de Aldrete modificado o instrumento clássico de transição. A &lt;strong&gt;fase II&lt;/strong&gt; prepara o paciente para a alta domiciliar e emprega critérios do tipo PADSS, que avaliam sinais vitais estáveis, deambulação sem tontura, controle de dor e de náusea, sangramento cirúrgico mínimo e presença de acompanhante responsável.&lt;/p&gt;&lt;p&gt;A evolução dos protocolos eliminou dois requisitos antes considerados obrigatórios. A &lt;strong&gt;micção espontânea&lt;/strong&gt; deixou de ser exigida na maioria dos pacientes, permanecendo como condição de alta apenas nos grupos de risco para retenção urinária — bloqueio do neuroeixo, cirurgia anorretal ou herniorrafia inguinal, prostatismo e história prévia de retenção. A &lt;strong&gt;ingestão oral obrigatória&lt;/strong&gt; também foi abandonada, pois retarda a alta e aumenta a incidência de náusea e vômito.&lt;/p&gt;&lt;p&gt;A paciente descrita preenche todos os critérios pertinentes e pode receber alta com acompanhante e orientações por escrito.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a micção não é requisito universal, e mantê-la como tal prolonga desnecessariamente a permanência hospitalar. (C) a tolerância a dieta sólida não é critério de alta e sua exigência aumenta náusea e vômito, sem reduzir readmissões. (D) o paciente submetido a anestesia geral não deve dirigir, operar máquinas ou tomar decisões juridicamente relevantes por pelo menos 24 horas, independentemente do escore obtido; a alta exige acompanhante adulto responsável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A recuperação é dividida em fases. A &lt;strong&gt;fase I&lt;/strong&gt; abrange o despertar imediato, com vigilância intensiva de via aérea, hemodinâmica e consciência, sendo o escore de Aldrete modificado o instrumento clássico de transição. A &lt;strong&gt;fase II&lt;/strong&gt; prepara o paciente para a alta domiciliar e emprega critérios do tipo PADSS, que avaliam sinais vitais estáveis, deambulação sem tontura, controle de dor e de náusea, sangramento cirúrgico mínimo e presença de acompanhante responsável.&lt;/p&gt;&lt;p&gt;A evolução dos protocolos eliminou dois requisitos antes considerados obrigatórios. A &lt;strong&gt;micção espontânea&lt;/strong&gt; deixou de ser exigida na maioria dos pacientes, permanecendo como condição de alta apenas nos grupos de risco para retenção urinária: bloqueio do neuroeixo, cirurgia anorretal ou herniorrafia inguinal, prostatismo e história prévia de retenção. A &lt;strong&gt;ingestão oral obrigatória&lt;/strong&gt; também foi abandonada, pois retarda a alta e aumenta a incidência de náusea e vômito.&lt;/p&gt;&lt;p&gt;A paciente descrita preenche todos os critérios pertinentes e pode receber alta com acompanhante e orientações por escrito.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a micção não é requisito universal, e mantê-la como tal prolonga desnecessariamente a permanência hospitalar. (C) a tolerância a dieta sólida não é critério de alta e sua exigência aumenta náusea e vômito, sem reduzir readmissões. (D) o paciente submetido a anestesia geral não deve dirigir, operar máquinas ou tomar decisões juridicamente relevantes por pelo menos 24 horas, independentemente do escore obtido; a alta exige acompanhante adulto responsável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Pacientes com apneia obstrutiva do sono apresentam &lt;strong&gt;colapsabilidade aumentada da via aérea superior&lt;/strong&gt; e &lt;strong&gt;sensibilidade exagerada aos efeitos depressores de opioides, benzodiazepínicos e anestésicos residuais&lt;/strong&gt;. O risco de eventos respiratórios críticos concentra-se nas primeiras 24 a 72 horas, com pico durante o sono de movimentos oculares rápidos, cuja arquitetura é distorcida no pós-operatório com fenômeno de rebote nas noites seguintes. O STOP-BANG de 6 pontos caracteriza alto risco.&lt;/p&gt;&lt;p&gt;A conduta correta reúne três eixos: &lt;strong&gt;vigilância prolongada&lt;/strong&gt; na recuperação, com oximetria contínua e observação por período estendido antes da transferência; &lt;strong&gt;analgesia multimodal poupadora de opioide&lt;/strong&gt;, com anti-inflamatórios, dipirona, paracetamol, dexmedetomidina e bloqueios de parede abdominal; e &lt;strong&gt;retomada precoce da terapia com pressão positiva&lt;/strong&gt;, orientando o paciente a trazer o próprio aparelho. Elevação da cabeceira e evitar decúbito dorsal completam as medidas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o oxigênio suplementar corrige a saturação sem tratar a obstrução e ainda retarda a detecção da hipoventilação pela oximetria, de modo que a transferência precoce sem monitorização é conduta de risco. (C) benzodiazepínicos reduzem o tônus da musculatura faríngea e deprimem a resposta ventilatória, agravando os eventos obstrutivos — devem ser evitados. (D) a naloxona em infusão contínua não tem indicação profilática de rotina, antagoniza a analgesia, provoca dor, taquicardia, hipertensão e, em casos extremos, edema pulmonar, reservando-se ao tratamento da depressão respiratória instalada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Pacientes com apneia obstrutiva do sono apresentam &lt;strong&gt;colapsabilidade aumentada da via aérea superior&lt;/strong&gt; e &lt;strong&gt;sensibilidade exagerada aos efeitos depressores de opioides, benzodiazepínicos e anestésicos residuais&lt;/strong&gt;. O risco de eventos respiratórios críticos concentra-se nas primeiras 24 a 72 horas, com pico durante o sono de movimentos oculares rápidos, cuja arquitetura é distorcida no pós-operatório com fenômeno de rebote nas noites seguintes. O STOP-BANG de 6 pontos caracteriza alto risco.&lt;/p&gt;&lt;p&gt;A conduta correta reúne três eixos: &lt;strong&gt;vigilância prolongada&lt;/strong&gt; na recuperação, com oximetria contínua e observação por período estendido antes da transferência; &lt;strong&gt;analgesia multimodal poupadora de opioide&lt;/strong&gt;, com anti-inflamatórios, dipirona, paracetamol, dexmedetomidina e bloqueios de parede abdominal; e &lt;strong&gt;retomada precoce da terapia com pressão positiva&lt;/strong&gt;, orientando o paciente a trazer o próprio aparelho. Elevação da cabeceira e evitar decúbito dorsal completam as medidas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o oxigênio suplementar corrige a saturação sem tratar a obstrução e ainda retarda a detecção da hipoventilação pela oximetria, de modo que a transferência precoce sem monitorização é conduta de risco. (C) benzodiazepínicos reduzem o tônus da musculatura faríngea e deprimem a resposta ventilatória, agravando os eventos obstrutivos; devem ser evitados. (D) a naloxona em infusão contínua não tem indicação profilática de rotina, antagoniza a analgesia, provoca dor, taquicardia, hipertensão e, em casos extremos, edema pulmonar, reservando-se ao tratamento da depressão respiratória instalada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A qualidade das compressões é o determinante isolado mais importante da sobrevida na parada cardíaca, porque delas depende a pressão de perfusão coronariana. Os parâmetros de referência no adulto são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Frequência de 100 a 120 compressões por minuto&lt;/strong&gt; — abaixo disso o fluxo é insuficiente; acima, não há tempo para o enchimento diastólico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Profundidade de 5 a 6 cm&lt;/strong&gt;, ou seja, pelo menos 5 cm e não mais que 6 cm, limite acima do qual aumentam as lesões torácicas sem ganho de perfusão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Retorno completo do tórax&lt;/strong&gt; entre as compressões, sem apoiar as mãos, permitindo pressão intratorácica negativa e retorno venoso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Minimizar interrupções&lt;/strong&gt;, mantendo cada pausa abaixo de 10 segundos e fração de compressão superior a 60%.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relação 30 compressões para 2 ventilações&lt;/strong&gt; enquanto não houver via aérea avançada, com revezamento do compressor a cada 2 minutos.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a frequência está abaixo do recomendado, a profundidade é insuficiente para gerar débito adequado e apoiar as mãos entre as compressões impede o retorno completo do tórax, reduzindo o retorno venoso. (B) frequências acima de 120 comprometem o enchimento ventricular e profundidades superiores a 6 cm aumentam a incidência de fraturas de arcos costais e de lesões viscerais. (D) pausas de 30 segundos por ciclo reduzem drasticamente a fração de compressão e a pressão de perfusão coronariana, que leva vários ciclos para ser restabelecida.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A qualidade das compressões é o determinante isolado mais importante da sobrevida na parada cardíaca, porque delas depende a pressão de perfusão coronariana. Os parâmetros de referência no adulto são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Frequência de 100 a 120 compressões por minuto&lt;/strong&gt;: abaixo disso o fluxo é insuficiente; acima, não há tempo para o enchimento diastólico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Profundidade de 5 a 6 cm&lt;/strong&gt;, ou seja, pelo menos 5 cm e não mais que 6 cm, limite acima do qual aumentam as lesões torácicas sem ganho de perfusão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Retorno completo do tórax&lt;/strong&gt; entre as compressões, sem apoiar as mãos, permitindo pressão intratorácica negativa e retorno venoso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Minimizar interrupções&lt;/strong&gt;, mantendo cada pausa abaixo de 10 segundos e fração de compressão superior a 60%.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relação 30 compressões para 2 ventilações&lt;/strong&gt; enquanto não houver via aérea avançada, com revezamento do compressor a cada 2 minutos.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a frequência está abaixo do recomendado, a profundidade é insuficiente para gerar débito adequado e apoiar as mãos entre as compressões impede o retorno completo do tórax, reduzindo o retorno venoso. (B) frequências acima de 120 comprometem o enchimento ventricular e profundidades superiores a 6 cm aumentam a incidência de fraturas de arcos costais e de lesões viscerais. (D) pausas de 30 segundos por ciclo reduzem drasticamente a fração de compressão e a pressão de perfusão coronariana, que leva vários ciclos para ser restabelecida.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A partir de aproximadamente 20 semanas, ou quando o fundo uterino atinge ou ultrapassa a cicatriz umbilical, o útero gravídico comprime a veia cava inferior e a aorta em decúbito dorsal. Essa &lt;strong&gt;compressão aortocava&lt;/strong&gt; reduz drasticamente o retorno venoso e inviabiliza o débito gerado pelas compressões torácicas — motivo pelo qual a reanimação da gestante falha se esse ponto não for corrigido.&lt;/p&gt;&lt;p&gt;A conduta atual privilegia o &lt;strong&gt;deslocamento uterino manual contínuo para a esquerda&lt;/strong&gt;, executado por um membro da equipe, mantendo a paciente em decúbito dorsal horizontal sobre superfície rígida. Assim se descomprime a cava sem perder qualidade das compressões, que são realizadas na &lt;strong&gt;posição padrão do esterno&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;cesárea perimortem&lt;/strong&gt; é medida de reanimação materna, e não apenas fetal: o esvaziamento uterino elimina a compressão aortocava e melhora substancialmente as chances de retorno da circulação. Deve ser &lt;strong&gt;iniciada por volta de 4 minutos&lt;/strong&gt; de parada sem resposta, com objetivo de extração fetal em até 5 minutos, e realizada no local do atendimento, sem transporte para outra sala.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a inclinação lateral da mesa reduz de forma significativa a força efetiva das compressões torácicas e por isso foi preterida em favor do deslocamento uterino manual. (C) manter o útero em posição neutra perpetua a compressão aortocava, e postergar o parto por 10 minutos ultrapassa amplamente a janela recomendada. (D) aguardar 20 minutos elimina a chance de sobrevida fetal e retarda justamente a intervenção que melhora o desfecho materno.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A partir de aproximadamente 20 semanas, ou quando o fundo uterino atinge ou ultrapassa a cicatriz umbilical, o útero gravídico comprime a veia cava inferior e a aorta em decúbito dorsal. Essa &lt;strong&gt;compressão aortocava&lt;/strong&gt; reduz drasticamente o retorno venoso e inviabiliza o débito gerado pelas compressões torácicas, motivo pelo qual a reanimação da gestante falha se esse ponto não for corrigido.&lt;/p&gt;&lt;p&gt;A conduta atual privilegia o &lt;strong&gt;deslocamento uterino manual contínuo para a esquerda&lt;/strong&gt;, executado por um membro da equipe, mantendo a paciente em decúbito dorsal horizontal sobre superfície rígida. Assim se descomprime a cava sem perder qualidade das compressões, que são realizadas na &lt;strong&gt;posição padrão do esterno&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;cesárea perimortem&lt;/strong&gt; é medida de reanimação materna, e não apenas fetal: o esvaziamento uterino elimina a compressão aortocava e melhora substancialmente as chances de retorno da circulação. Deve ser &lt;strong&gt;iniciada por volta de 4 minutos&lt;/strong&gt; de parada sem resposta, com objetivo de extração fetal em até 5 minutos, e realizada no local do atendimento, sem transporte para outra sala.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a inclinação lateral da mesa reduz de forma significativa a força efetiva das compressões torácicas e por isso foi preterida em favor do deslocamento uterino manual. (C) manter o útero em posição neutra perpetua a compressão aortocava, e postergar o parto por 10 minutos ultrapassa amplamente a janela recomendada. (D) aguardar 20 minutos elimina a chance de sobrevida fetal e retarda justamente a intervenção que melhora o desfecho materno.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O índice bispectral é um número adimensional derivado de variáveis do eletroencefalograma frontal — poder espectral, sincronia de fase e taxa de supressão. Ele foi construído e validado sobretudo com hipnóticos que atuam no receptor GABA-A (propofol, halogenados, benzodiazepínicos), nos quais o aprofundamento do plano cursa com lentificação progressiva do sinal. Fármacos que produzem hipnose por outro mecanismo quebram essa correlação.&lt;/p&gt;&lt;p&gt;A cetamina, antagonista de receptores NMDA, aumenta a atividade de alta frequência (beta e gama) e reduz a sincronização lenta. O algoritmo lê esse padrão como sinal de despertar e &lt;strong&gt;eleva&lt;/strong&gt; o valor exibido, mesmo com o paciente adequadamente anestesiado. O mesmo fenômeno de dissociação entre índice e plano clínico ocorre com o óxido nitroso e com o uso de efedrina.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a cetamina não é antagonista GABA-A e não reverte o efeito do propofol; não houve nenhum sinal clínico de superficialização. (C) o artefato eletromiográfico realmente eleva o índice, mas está descartado aqui pelo bloqueio neuromuscular profundo com ausência de respostas na sequência de quatro estímulos. (D) o índice bispectral é calculado exclusivamente a partir do sinal eletroencefalográfico e eletromiográfico frontal, e não incorpora frequência cardíaca ou pressão arterial; além disso, o caso descreve estabilidade hemodinâmica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O índice bispectral é um número adimensional derivado de variáveis do eletroencefalograma frontal: poder espectral, sincronia de fase e taxa de supressão. Ele foi construído e validado sobretudo com hipnóticos que atuam no receptor GABA-A (propofol, halogenados, benzodiazepínicos), nos quais o aprofundamento do plano cursa com lentificação progressiva do sinal. Fármacos que produzem hipnose por outro mecanismo quebram essa correlação.&lt;/p&gt;&lt;p&gt;A cetamina, antagonista de receptores NMDA, aumenta a atividade de alta frequência (beta e gama) e reduz a sincronização lenta. O algoritmo lê esse padrão como sinal de despertar e &lt;strong&gt;eleva&lt;/strong&gt; o valor exibido, mesmo com o paciente adequadamente anestesiado. O mesmo fenômeno de dissociação entre índice e plano clínico ocorre com o óxido nitroso e com o uso de efedrina.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a cetamina não é antagonista GABA-A e não reverte o efeito do propofol; não houve nenhum sinal clínico de superficialização. (C) o artefato eletromiográfico realmente eleva o índice, mas está descartado aqui pelo bloqueio neuromuscular profundo com ausência de respostas na sequência de quatro estímulos. (D) o índice bispectral é calculado exclusivamente a partir do sinal eletroencefalográfico e eletromiográfico frontal, e não incorpora frequência cardíaca ou pressão arterial; além disso, o caso descreve estabilidade hemodinâmica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A medida oscilométrica depende da transmissão da pulsação arterial à câmara de ar do manguito. Para que a pressão aplicada à pele corresponda à pressão transmitida à artéria braquial, a bolsa inflável precisa ter &lt;strong&gt;largura em torno de 40% da circunferência do braço&lt;/strong&gt; e comprimento suficiente para envolver cerca de 80% dessa circunferência.&lt;/p&gt;&lt;p&gt;No caso, 12 cm sobre um braço de 42 cm correspondem a menos de 30% da circunferência. Um manguito estreito precisa de pressão muito maior para ocluir a artéria sob um panículo espesso, e o resultado é &lt;strong&gt;superestimativa&lt;/strong&gt; dos valores — a explicação mais provável para a diferença em relação às medidas prévias. O erro oposto, manguito largo demais, subestima a pressão. Vale lembrar que o oscilômetro identifica com precisão apenas a &lt;em&gt;pressão arterial média&lt;/em&gt;, correspondente ao ponto de máxima amplitude das oscilações; sistólica e diastólica são estimadas por algoritmo proprietário a partir dessa curva de amplitudes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a relação: manguito largo subestima, e a correção aqui é usar um manguito mais largo, não mais estreito. (C) a oscilometria mede diretamente a média e deriva as demais; a afirmação inverte o que é medido e o que é calculado. (D) confunde os parâmetros: a proporção de 40% refere-se à largura, e o comprimento deve envolver cerca de 80% da circunferência.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A medida oscilométrica depende da transmissão da pulsação arterial à câmara de ar do manguito. Para que a pressão aplicada à pele corresponda à pressão transmitida à artéria braquial, a bolsa inflável precisa ter &lt;strong&gt;largura em torno de 40% da circunferência do braço&lt;/strong&gt; e comprimento suficiente para envolver cerca de 80% dessa circunferência.&lt;/p&gt;&lt;p&gt;No caso, 12 cm sobre um braço de 42 cm correspondem a menos de 30% da circunferência. Um manguito estreito precisa de pressão muito maior para ocluir a artéria sob um panículo espesso, e o resultado é &lt;strong&gt;superestimativa&lt;/strong&gt; dos valores, a explicação mais provável para a diferença em relação às medidas prévias. O erro oposto, manguito largo demais, subestima a pressão. Vale lembrar que o oscilômetro identifica com precisão apenas a &lt;em&gt;pressão arterial média&lt;/em&gt;, correspondente ao ponto de máxima amplitude das oscilações; sistólica e diastólica são estimadas por algoritmo proprietário a partir dessa curva de amplitudes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a relação: manguito largo subestima, e a correção aqui é usar um manguito mais largo, não mais estreito. (C) a oscilometria mede diretamente a média e deriva as demais; a afirmação inverte o que é medido e o que é calculado. (D) confunde os parâmetros: a proporção de 40% refere-se à largura, e o comprimento deve envolver cerca de 80% da circunferência.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O oxímetro de pulso convencional emite luz em dois comprimentos de onda, 660 nm (vermelho) e 940 nm (infravermelho), e calcula a saturação a partir da razão entre as absorbâncias pulsáteis. O aparelho pressupõe que existam apenas duas espécies de hemoglobina, oxi e desoxi. Qualquer terceira espécie distorce a leitura.&lt;/p&gt;&lt;p&gt;A metemoglobina tem coeficientes de absorção &lt;strong&gt;altos e semelhantes&lt;/strong&gt; nos dois comprimentos de onda. À medida que sua fração aumenta, a razão entre as absorbâncias tende a 1, valor que o algoritmo traduz em saturação de aproximadamente &lt;strong&gt;85%&lt;/strong&gt;. Por isso a SpO2 fica "travada" em torno desse número, independentemente da PaO2 e da fração inspirada de oxigênio — exatamente o quadro descrito, com PaO2 de 240 mmHg e SpO2 de 85%. O diagnóstico se confirma pela cooximetria, e o tratamento da forma sintomática é azul de metileno, 1 a 2 mg/kg por via venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) não há queda proporcional até valores próximos de zero; a leitura satura no platô em torno de 85%. (C) o comportamento de superestimar a saturação real é típico da carboxi-hemoglobina, que absorve em 660 nm de modo semelhante à oxi-hemoglobina. (D) o oxigênio suplementar eleva a PaO2 e o oxigênio dissolvido, mas não reverte a metemoglobina nem corrige a leitura do oxímetro.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O oxímetro de pulso convencional emite luz em dois comprimentos de onda, 660 nm (vermelho) e 940 nm (infravermelho), e calcula a saturação a partir da razão entre as absorbâncias pulsáteis. O aparelho pressupõe que existam apenas duas espécies de hemoglobina, oxi e desoxi. Qualquer terceira espécie distorce a leitura.&lt;/p&gt;&lt;p&gt;A metemoglobina tem coeficientes de absorção &lt;strong&gt;altos e semelhantes&lt;/strong&gt; nos dois comprimentos de onda. À medida que sua fração aumenta, a razão entre as absorbâncias tende a 1, valor que o algoritmo traduz em saturação de aproximadamente &lt;strong&gt;85%&lt;/strong&gt;. Por isso a SpO2 fica "travada" em torno desse número, independentemente da PaO2 e da fração inspirada de oxigênio, exatamente o quadro descrito, com PaO2 de 240 mmHg e SpO2 de 85%. O diagnóstico se confirma pela cooximetria, e o tratamento da forma sintomática é azul de metileno, 1 a 2 mg/kg por via venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) não há queda proporcional até valores próximos de zero; a leitura satura no platô em torno de 85%. (C) o comportamento de superestimar a saturação real é típico da carboxi-hemoglobina, que absorve em 660 nm de modo semelhante à oxi-hemoglobina. (D) o oxigênio suplementar eleva a PaO2 e o oxigênio dissolvido, mas não reverte a metemoglobina nem corrige a leitura do oxímetro.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em pulmões normais, o CO2 expirado final é 2 a 5 mmHg menor que a PaCO2, diferença atribuída ao espaço morto alveolar fisiológico. O gradiente se amplia sempre que aumenta a fração de alvéolos ventilados e mal perfundidos, pois esses alvéolos diluem o gás alveolar rico em CO2 com gás praticamente livre de CO2.&lt;/p&gt;&lt;p&gt;Aqui o gradiente passou a &lt;strong&gt;36 mmHg&lt;/strong&gt; (48 menos 12), de instalação súbita, no momento cirúrgico de maior risco de embolia — a impactação de haste femoral não cimentada, que pressuriza o canal medular e desloca gordura, medula óssea e ar para a circulação venosa. A queda do CO2 expirado final com &lt;em&gt;elevação&lt;/em&gt; da PaCO2 é a assinatura da obstrução vascular pulmonar aguda, reforçada pela hipotensão e taquicardia concomitantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipoventilação elevaria simultaneamente PaCO2 e CO2 expirado final, sem alargar o gradiente. (B) a reinalação também eleva o CO2 expirado final, com elevação da fase inspiratória; o caso mostra queda abrupta. (D) a desconexão ou o vazamento reduzem a leitura, mas costumam alterar volume corrente e pressões da via aérea e não explicam a hipotensão com taquicardia associada ao tempo cirúrgico descrito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em pulmões normais, o CO2 expirado final é 2 a 5 mmHg menor que a PaCO2, diferença atribuída ao espaço morto alveolar fisiológico. O gradiente se amplia sempre que aumenta a fração de alvéolos ventilados e mal perfundidos, pois esses alvéolos diluem o gás alveolar rico em CO2 com gás praticamente livre de CO2.&lt;/p&gt;&lt;p&gt;Aqui o gradiente passou a &lt;strong&gt;36 mmHg&lt;/strong&gt; (48 menos 12), de instalação súbita, no momento cirúrgico de maior risco de embolia: a impactação de haste femoral não cimentada, que pressuriza o canal medular e desloca gordura, medula óssea e ar para a circulação venosa. A queda do CO2 expirado final com &lt;em&gt;elevação&lt;/em&gt; da PaCO2 é a assinatura da obstrução vascular pulmonar aguda, reforçada pela hipotensão e taquicardia concomitantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipoventilação elevaria simultaneamente PaCO2 e CO2 expirado final, sem alargar o gradiente. (B) a reinalação também eleva o CO2 expirado final, com elevação da fase inspiratória; o caso mostra queda abrupta. (D) a desconexão ou o vazamento reduzem a leitura, mas costumam alterar volume corrente e pressões da via aérea e não explicam a hipotensão com taquicardia associada ao tempo cirúrgico descrito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O conjunto cateter-extensão-transdutor comporta-se como um sistema massa-mola, caracterizado por frequência natural e coeficiente de amortecimento. O teste de flush rápido avalia esses dois parâmetros: ao liberar o dispositivo de lavagem, gera-se uma onda quadrada e observa-se como o sinal retorna à linha de base.&lt;/p&gt;&lt;p&gt;Retorno &lt;strong&gt;lento e sem oscilações&lt;/strong&gt; caracteriza o sistema &lt;strong&gt;superamortecido&lt;/strong&gt;: bolhas de ar, coágulo ou dobra no cateter, extensões longas e complacentes ou torneiras mal alinhadas dissipam energia. O resultado típico é achatamento da curva, com &lt;em&gt;subestimativa da sistólica&lt;/em&gt; e &lt;em&gt;superestimativa da diastólica&lt;/em&gt;, enquanto a pressão média — que depende da área sob a curva e não do pico — permanece relativamente confiável. Diante desse achado, a conduta é procurar bolhas, aspirar e lavar o sistema, encurtar extensões e verificar conexões, e não tratar a "hipotensão" exibida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o sistema subamortecido produz múltiplas oscilações após a onda quadrada e é corrigido com dispositivos que aumentam o amortecimento, não com extensões adicionais, que pioram o problema. (B) um erro de nível do transdutor desloca todos os valores no mesmo sentido e na mesma magnitude, sem estreitar a pressão de pulso. (C) o vasoespasmo grave cursa com curva pobre e dificuldade de refluxo, o que não corresponde ao descrito, e a oscilometria não é padrão de referência.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O conjunto cateter-extensão-transdutor comporta-se como um sistema massa-mola, caracterizado por frequência natural e coeficiente de amortecimento. O teste de flush rápido avalia esses dois parâmetros: ao liberar o dispositivo de lavagem, gera-se uma onda quadrada e observa-se como o sinal retorna à linha de base.&lt;/p&gt;&lt;p&gt;Retorno &lt;strong&gt;lento e sem oscilações&lt;/strong&gt; caracteriza o sistema &lt;strong&gt;superamortecido&lt;/strong&gt;: bolhas de ar, coágulo ou dobra no cateter, extensões longas e complacentes ou torneiras mal alinhadas dissipam energia. O resultado típico é achatamento da curva, com &lt;em&gt;subestimativa da sistólica&lt;/em&gt; e &lt;em&gt;superestimativa da diastólica&lt;/em&gt;, enquanto a pressão média (que depende da área sob a curva e não do pico) permanece relativamente confiável. Diante desse achado, a conduta é procurar bolhas, aspirar e lavar o sistema, encurtar extensões e verificar conexões, e não tratar a "hipotensão" exibida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o sistema subamortecido produz múltiplas oscilações após a onda quadrada e é corrigido com dispositivos que aumentam o amortecimento, não com extensões adicionais, que pioram o problema. (B) um erro de nível do transdutor desloca todos os valores no mesmo sentido e na mesma magnitude, sem estreitar a pressão de pulso. (C) o vasoespasmo grave cursa com curva pobre e dificuldade de refluxo, o que não corresponde ao descrito, e a oscilometria não é padrão de referência.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Com o ventilador em parâmetros fixos, o CO2 expirado final varia por três grandes mecanismos: mudança na &lt;strong&gt;produção&lt;/strong&gt; de CO2, mudança no &lt;strong&gt;transporte&lt;/strong&gt; (débito cardíaco e perfusão pulmonar) e mudança na &lt;strong&gt;eliminação&lt;/strong&gt; (ventilação alveolar e espaço morto).&lt;/p&gt;&lt;p&gt;Durante a isquemia induzida pelo torniquete, o metabolismo anaeróbio do membro acumula CO2, lactato, potássio e outros metabólitos, sem que nada disso chegue ao pulmão. Ao desinsuflar, esse compartimento é lavado de uma só vez: a carga de CO2 entregue ao pulmão aumenta abruptamente e o CO2 expirado final sobe, tipicamente &lt;strong&gt;5 a 15 mmHg&lt;/strong&gt;, com pico em um a três minutos e retorno gradual ao basal em cinco a quinze minutos. A queda discreta da pressão arterial acompanha a vasodilatação do leito reperfundido e o sequestro de volume no membro. É fenômeno esperado, e não complicação — embora mereça atenção no paciente com hipertensão intracraniana, no qual a elevação da PaCO2 pode ser deletéria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) embolização significativa aumentaria o espaço morto e &lt;em&gt;reduziria&lt;/em&gt; o CO2 expirado final. (B) a produção de CO2 no membro não cai; o que muda é a sua chegada ao pulmão. (C) o paciente está anestesiado e sem tremor, e o enunciado explicita que a ventilação permaneceu inalterada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Com o ventilador em parâmetros fixos, o CO2 expirado final varia por três grandes mecanismos: mudança na &lt;strong&gt;produção&lt;/strong&gt; de CO2, mudança no &lt;strong&gt;transporte&lt;/strong&gt; (débito cardíaco e perfusão pulmonar) e mudança na &lt;strong&gt;eliminação&lt;/strong&gt; (ventilação alveolar e espaço morto).&lt;/p&gt;&lt;p&gt;Durante a isquemia induzida pelo torniquete, o metabolismo anaeróbio do membro acumula CO2, lactato, potássio e outros metabólitos, sem que nada disso chegue ao pulmão. Ao desinsuflar, esse compartimento é lavado de uma só vez: a carga de CO2 entregue ao pulmão aumenta abruptamente e o CO2 expirado final sobe, tipicamente &lt;strong&gt;5 a 15 mmHg&lt;/strong&gt;, com pico em um a três minutos e retorno gradual ao basal em cinco a quinze minutos. A queda discreta da pressão arterial acompanha a vasodilatação do leito reperfundido e o sequestro de volume no membro. É fenômeno esperado, e não complicação, embora mereça atenção no paciente com hipertensão intracraniana, no qual a elevação da PaCO2 pode ser deletéria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) embolização significativa aumentaria o espaço morto e &lt;em&gt;reduziria&lt;/em&gt; o CO2 expirado final. (B) a produção de CO2 no membro não cai; o que muda é a sua chegada ao pulmão. (C) o paciente está anestesiado e sem tremor, e o enunciado explicita que a ventilação permaneceu inalterada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As duas modalidades avaliam vias e territórios vasculares distintos, o que explica por que são complementares. Os &lt;strong&gt;potenciais somatossensitivos&lt;/strong&gt; ascendem pelas colunas dorsais e pelo lemnisco medial, irrigadas pelas artérias espinhais posteriores, e são registrados no córtex. Os &lt;strong&gt;potenciais motores&lt;/strong&gt; descem pelo trato corticoespinhal, no território da artéria espinhal anterior, e são captados como resposta muscular composta nos músculos-alvo dos membros.&lt;/p&gt;&lt;p&gt;Como o sinal motor é lido no músculo, ele depende da transmissão neuromuscular íntegra: o bloqueio neuromuscular profundo e contínuo &lt;strong&gt;abole&lt;/strong&gt; o registro. Quando o cirurgião exige relaxamento, admite-se no máximo bloqueio parcial e estável, monitorizado, com duas a três respostas na sequência de quatro estímulos. Os potenciais somatossensitivos, ao contrário, não dependem da junção neuromuscular e chegam a melhorar com o relaxamento, por redução do ruído eletromiográfico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) troca as vias — o trato corticoespinhal corresponde aos potenciais motores — e os somatossensitivos não são abolidos pelo bloqueador. (B) inverte novamente as vias e afirma o oposto quanto aos halogenados, que deprimem intensamente a amplitude dos potenciais motores. (D) os halogenados são muito mais depressores que o propofol; a anestesia venosa total é justamente a técnica de escolha nesse contexto.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As duas modalidades avaliam vias e territórios vasculares distintos, o que explica por que são complementares. Os &lt;strong&gt;potenciais somatossensitivos&lt;/strong&gt; ascendem pelas colunas dorsais e pelo lemnisco medial, irrigadas pelas artérias espinhais posteriores, e são registrados no córtex. Os &lt;strong&gt;potenciais motores&lt;/strong&gt; descem pelo trato corticoespinhal, no território da artéria espinhal anterior, e são captados como resposta muscular composta nos músculos-alvo dos membros.&lt;/p&gt;&lt;p&gt;Como o sinal motor é lido no músculo, ele depende da transmissão neuromuscular íntegra: o bloqueio neuromuscular profundo e contínuo &lt;strong&gt;abole&lt;/strong&gt; o registro. Quando o cirurgião exige relaxamento, admite-se no máximo bloqueio parcial e estável, monitorizado, com duas a três respostas na sequência de quatro estímulos. Os potenciais somatossensitivos, ao contrário, não dependem da junção neuromuscular e chegam a melhorar com o relaxamento, por redução do ruído eletromiográfico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) troca as vias: o trato corticoespinhal corresponde aos potenciais motores, e os somatossensitivos não são abolidos pelo bloqueador. (B) inverte novamente as vias e afirma o oposto quanto aos halogenados, que deprimem intensamente a amplitude dos potenciais motores. (D) os halogenados são muito mais depressores que o propofol; a anestesia venosa total é justamente a técnica de escolha nesse contexto.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O plano &lt;strong&gt;transgástrico de eixo curto na altura dos músculos papilares&lt;/strong&gt; é o corte de vigilância clássico do intraoperatório. Nele o ventrículo esquerdo aparece em secção circular, dividida em seis segmentos que pertencem, em conjunto, aos territórios da artéria descendente anterior (segmentos anterior e anterosseptal), da coronária direita (inferior e inferosseptal) e da circunflexa (lateral e posterolateral).&lt;/p&gt;&lt;p&gt;Isso permite três julgamentos ao mesmo tempo: estimativa da pré-carga pela área diastólica final da cavidade, estimativa da função sistólica global pela variação fracional de área e detecção precoce de &lt;strong&gt;alterações segmentares novas&lt;/strong&gt; — espessamento sistólico reduzido e hipocinesia —, que aparecem antes das alterações eletrocardiográficas e antes da elevação das pressões de enchimento. É também o plano usado para diferenciar hipovolemia de disfunção ventricular diante de hipotensão súbita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o corte de quatro câmaras é útil para valvas atrioventriculares e paredes septal e lateral, mas não abrange bem o território da coronária direita nem serve como janela isolada de vigilância. (C) o eixo longo esofágico médio avalia sobretudo a via de saída, a valva aórtica e a aorta ascendente proximal. (D) o plano bicaval mostra veias cavas, átrio direito e septo interatrial, e não permite avaliar contratilidade do ventrículo esquerdo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O plano &lt;strong&gt;transgástrico de eixo curto na altura dos músculos papilares&lt;/strong&gt; é o corte de vigilância clássico do intraoperatório. Nele o ventrículo esquerdo aparece em secção circular, dividida em seis segmentos que pertencem, em conjunto, aos territórios da artéria descendente anterior (segmentos anterior e anterosseptal), da coronária direita (inferior e inferosseptal) e da circunflexa (lateral e posterolateral).&lt;/p&gt;&lt;p&gt;Isso permite três julgamentos ao mesmo tempo: estimativa da pré-carga pela área diastólica final da cavidade, estimativa da função sistólica global pela variação fracional de área e detecção precoce de &lt;strong&gt;alterações segmentares novas&lt;/strong&gt; (espessamento sistólico reduzido e hipocinesia), que aparecem antes das alterações eletrocardiográficas e antes da elevação das pressões de enchimento. É também o plano usado para diferenciar hipovolemia de disfunção ventricular diante de hipotensão súbita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o corte de quatro câmaras é útil para valvas atrioventriculares e paredes septal e lateral, mas não abrange bem o território da coronária direita nem serve como janela isolada de vigilância. (C) o eixo longo esofágico médio avalia sobretudo a via de saída, a valva aórtica e a aorta ascendente proximal. (D) o plano bicaval mostra veias cavas, átrio direito e septo interatrial, e não permite avaliar contratilidade do ventrículo esquerdo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os critérios de alerta consagrados para potenciais somatossensitivos são queda de amplitude &lt;strong&gt;maior que 50%&lt;/strong&gt; ou aumento de latência &lt;strong&gt;maior que 10%&lt;/strong&gt; em relação ao valor basal. Para os potenciais motores, considera-se significativa a queda acentuada de amplitude ou a perda da resposta. O caso preenche os critérios em ambas as modalidades, e de forma lateralizada — situação que deve ser tratada como lesão medular em curso até prova em contrário.&lt;/p&gt;&lt;p&gt;A resposta correta é uma lista de verificação simultânea, executada em minutos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Causas sistêmicas:&lt;/strong&gt; elevar a PAM (alvo habitual acima de 80 a 85 mmHg para melhorar a perfusão medular), transfundir se a anemia for significativa, reaquecer o paciente e revisar o plano anestésico e a posição dos membros.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Causas cirúrgicas:&lt;/strong&gt; comunicar imediatamente a equipe para reposicionar ou retirar parafusos, reduzir a distração e reavaliar a correção; se o sinal não se recuperar, considerar o teste do despertar intraoperatório.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio neuromuscular não afeta os potenciais somatossensitivos, e aprofundá-lo aboliria ainda mais os motores. (B) os halogenados deprimem os potenciais evocados e não conferem proteção medular nesse contexto. (D) a demora é o principal determinante de déficit permanente; o tempo até a correção é crítico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os critérios de alerta consagrados para potenciais somatossensitivos são queda de amplitude &lt;strong&gt;maior que 50%&lt;/strong&gt; ou aumento de latência &lt;strong&gt;maior que 10%&lt;/strong&gt; em relação ao valor basal. Para os potenciais motores, considera-se significativa a queda acentuada de amplitude ou a perda da resposta. O caso preenche os critérios em ambas as modalidades, e de forma lateralizada, situação que deve ser tratada como lesão medular em curso até prova em contrário.&lt;/p&gt;&lt;p&gt;A resposta correta é uma lista de verificação simultânea, executada em minutos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Causas sistêmicas:&lt;/strong&gt; elevar a PAM (alvo habitual acima de 80 a 85 mmHg para melhorar a perfusão medular), transfundir se a anemia for significativa, reaquecer o paciente e revisar o plano anestésico e a posição dos membros.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Causas cirúrgicas:&lt;/strong&gt; comunicar imediatamente a equipe para reposicionar ou retirar parafusos, reduzir a distração e reavaliar a correção; se o sinal não se recuperar, considerar o teste do despertar intraoperatório.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio neuromuscular não afeta os potenciais somatossensitivos, e aprofundá-lo aboliria ainda mais os motores. (B) os halogenados deprimem os potenciais evocados e não conferem proteção medular nesse contexto. (D) a demora é o principal determinante de déficit permanente; o tempo até a correção é crítico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A variação de pressão de pulso mede a amplificação, pela ventilação com pressão positiva, da interação entre pré-carga e volume sistólico. Valores acima de 12% a 13% predizem resposta a volume, mas apenas quando um conjunto restrito de premissas é respeitado:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;ritmo &lt;strong&gt;regular&lt;/strong&gt;, pois a variabilidade do intervalo RR na fibrilação atrial altera o enchimento batimento a batimento;&lt;/li&gt;&lt;li&gt;ventilação controlada, &lt;strong&gt;sem esforço respiratório&lt;/strong&gt; do paciente;&lt;/li&gt;&lt;li&gt;volume corrente de pelo menos &lt;strong&gt;8 mL/kg&lt;/strong&gt; de peso predito, para gerar oscilação de pressão pleural suficiente;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;tórax e abdome fechados&lt;/strong&gt; e complacência toracopulmonar preservada.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A paciente descrita viola pelo menos três dessas condições: fibrilação atrial, volume corrente de 6 mL/kg e abdome aberto. O número exibido é, portanto, ininterpretável — pode coexistir com hipovolemia ou com congestão. Nessa situação, recorre-se a testes dinâmicos que independem dessas premissas, como a elevação passiva das pernas ou a prova de volume, sempre com avaliação do efeito sobre o débito cardíaco ou a integral velocidade-tempo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) toma como válido um índice cujas premissas não foram cumpridas. (B) fatores de correção para volume corrente baixo foram descritos, mas não resgatam o índice na presença de arritmia e de abdome aberto. (C) a PEEP isolada não é a limitação principal, e ventilar sem PEEP seria deletério nessa paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A variação de pressão de pulso mede a amplificação, pela ventilação com pressão positiva, da interação entre pré-carga e volume sistólico. Valores acima de 12% a 13% predizem resposta a volume, mas apenas quando um conjunto restrito de premissas é respeitado:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;ritmo &lt;strong&gt;regular&lt;/strong&gt;, pois a variabilidade do intervalo RR na fibrilação atrial altera o enchimento batimento a batimento;&lt;/li&gt;&lt;li&gt;ventilação controlada, &lt;strong&gt;sem esforço respiratório&lt;/strong&gt; do paciente;&lt;/li&gt;&lt;li&gt;volume corrente de pelo menos &lt;strong&gt;8 mL/kg&lt;/strong&gt; de peso predito, para gerar oscilação de pressão pleural suficiente;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;tórax e abdome fechados&lt;/strong&gt; e complacência toracopulmonar preservada.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A paciente descrita viola pelo menos três dessas condições: fibrilação atrial, volume corrente de 6 mL/kg e abdome aberto. O número exibido é, portanto, ininterpretável: pode coexistir com hipovolemia ou com congestão. Nessa situação, recorre-se a testes dinâmicos que independem dessas premissas, como a elevação passiva das pernas ou a prova de volume, sempre com avaliação do efeito sobre o débito cardíaco ou a integral velocidade-tempo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) toma como válido um índice cujas premissas não foram cumpridas. (B) fatores de correção para volume corrente baixo foram descritos, mas não resgatam o índice na presença de arritmia e de abdome aberto. (C) a PEEP isolada não é a limitação principal, e ventilar sem PEEP seria deletério nessa paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A curva de pressão venosa central tem três ondas positivas e dois descensos. A onda &lt;strong&gt;a&lt;/strong&gt; corresponde à contração atrial, a onda &lt;strong&gt;c&lt;/strong&gt; ao abaulamento da tricúspide no início da sístole ventricular e a onda &lt;strong&gt;v&lt;/strong&gt; ao enchimento atrial com a valva ainda fechada. O descenso &lt;strong&gt;x&lt;/strong&gt; segue a onda a e o descenso &lt;strong&gt;y&lt;/strong&gt; ocorre após a abertura da tricúspide.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;dissociação atrioventricular&lt;/strong&gt;, átrio e ventrículo despolarizam de forma independente. Quando a sístole atrial coincide com a sístole ventricular, o átrio direito contrai contra a valva tricúspide já fechada e todo o volume é ejetado retrogradamente para as veias cavas, produzindo ondas de grande amplitude — as &lt;strong&gt;ondas a em canhão&lt;/strong&gt;. São intermitentes e irregulares justamente porque a coincidência entre as duas sístoles é aleatória. O sinal clínico correspondente é a variação da intensidade da primeira bulha, também descrita no caso. Além do bloqueio atrioventricular total, o achado ocorre na taquicardia ventricular e no ritmo de marca-passo ventricular sem sincronia atrial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a onda v gigante da regurgitação tricúspide é &lt;em&gt;sistólica e presente em todos os ciclos&lt;/em&gt;, e não intermitente. (C) a perda da onda a é típica da fibrilação atrial, na qual não há contração atrial organizada. (D) a modulação ventilatória é rítmica e acompanha o ciclo respiratório, o que o enunciado exclui explicitamente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A curva de pressão venosa central tem três ondas positivas e dois descensos. A onda &lt;strong&gt;a&lt;/strong&gt; corresponde à contração atrial, a onda &lt;strong&gt;c&lt;/strong&gt; ao abaulamento da tricúspide no início da sístole ventricular e a onda &lt;strong&gt;v&lt;/strong&gt; ao enchimento atrial com a valva ainda fechada. O descenso &lt;strong&gt;x&lt;/strong&gt; segue a onda a e o descenso &lt;strong&gt;y&lt;/strong&gt; ocorre após a abertura da tricúspide.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;dissociação atrioventricular&lt;/strong&gt;, átrio e ventrículo despolarizam de forma independente. Quando a sístole atrial coincide com a sístole ventricular, o átrio direito contrai contra a valva tricúspide já fechada e todo o volume é ejetado retrogradamente para as veias cavas, produzindo ondas de grande amplitude, as &lt;strong&gt;ondas a em canhão&lt;/strong&gt;. São intermitentes e irregulares justamente porque a coincidência entre as duas sístoles é aleatória. O sinal clínico correspondente é a variação da intensidade da primeira bulha, também descrita no caso. Além do bloqueio atrioventricular total, o achado ocorre na taquicardia ventricular e no ritmo de marca-passo ventricular sem sincronia atrial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a onda v gigante da regurgitação tricúspide é &lt;em&gt;sistólica e presente em todos os ciclos&lt;/em&gt;, e não intermitente. (C) a perda da onda a é típica da fibrilação atrial, na qual não há contração atrial organizada. (D) a modulação ventilatória é rítmica e acompanha o ciclo respiratório, o que o enunciado exclui explicitamente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distinção entre macrochoque e microchoque está na &lt;strong&gt;via&lt;/strong&gt; percorrida pela corrente. No macrochoque, a corrente atravessa a pele, cuja resistência é alta (dezenas de milhares de ohms quando seca), e se dispersa por todo o corpo; apenas uma fração mínima alcança o coração. Os limiares clássicos, para corrente alternada de 60 Hz aplicada à pele, são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;1 mA&lt;/strong&gt; — limiar de percepção, sensação de formigamento;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;5 mA&lt;/strong&gt; — considerado o máximo inofensivo;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;10 a 20 mA&lt;/strong&gt; — contração tetânica sustentada, com impossibilidade de soltar o condutor;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;100 mA&lt;/strong&gt; — fibrilação ventricular.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No &lt;strong&gt;microchoque&lt;/strong&gt;, um condutor intracardíaco — fio de marca-passo, cateter venoso central preenchido com solução salina — leva a corrente diretamente ao miocárdio, eliminando a proteção da pele. Correntes de apenas &lt;strong&gt;100 µA&lt;/strong&gt;, ou seja, 0,1 mA, mil vezes menores que o limiar de macrochoque, já podem induzir fibrilação ventricular. Por isso a corrente de fuga máxima admitida em equipamentos de uso cardíaco direto é de 10 µA, e por isso se recomenda manusear esses fios com luvas e isolar suas extremidades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) superestima grosseiramente o limiar e nega o risco real do microchoque. (B) confunde os patamares: 100 mA corresponde à fibrilação, e a tetania ocorre por volta de 10 a 20 mA. (D) a pele íntegra é justamente a barreira que separa os dois cenários, com resistência muito superior à dos tecidos internos.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distinção entre macrochoque e microchoque está na &lt;strong&gt;via&lt;/strong&gt; percorrida pela corrente. No macrochoque, a corrente atravessa a pele, cuja resistência é alta (dezenas de milhares de ohms quando seca), e se dispersa por todo o corpo; apenas uma fração mínima alcança o coração. Os limiares clássicos, para corrente alternada de 60 Hz aplicada à pele, são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;1 mA&lt;/strong&gt;: limiar de percepção, sensação de formigamento;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;5 mA&lt;/strong&gt;: considerado o máximo inofensivo;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;10 a 20 mA&lt;/strong&gt;: contração tetânica sustentada, com impossibilidade de soltar o condutor;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;100 mA&lt;/strong&gt;: fibrilação ventricular.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No &lt;strong&gt;microchoque&lt;/strong&gt;, um condutor intracardíaco (fio de marca-passo, cateter venoso central preenchido com solução salina) leva a corrente diretamente ao miocárdio, eliminando a proteção da pele. Correntes de apenas &lt;strong&gt;100 µA&lt;/strong&gt;, ou seja, 0,1 mA, mil vezes menores que o limiar de macrochoque, já podem induzir fibrilação ventricular. Por isso a corrente de fuga máxima admitida em equipamentos de uso cardíaco direto é de 10 µA, e por isso se recomenda manusear esses fios com luvas e isolar suas extremidades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) superestima grosseiramente o limiar e nega o risco real do microchoque. (B) confunde os patamares: 100 mA corresponde à fibrilação, e a tetania ocorre por volta de 10 a 20 mA. (D) a pele íntegra é justamente a barreira que separa os dois cenários, com resistência muito superior à dos tecidos internos.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O sistema de força isolada emprega um &lt;strong&gt;transformador de isolamento&lt;/strong&gt;, que separa eletricamente a rede da sala do sistema aterrado do prédio. Em um circuito isolado, tocar em apenas um dos condutores não fecha circuito com a terra e, portanto, não causa choque. A finalidade não é evitar microchoque, e sim garantir que uma &lt;strong&gt;primeira falha&lt;/strong&gt; de isolamento não interrompa a energia nem eletrocute alguém.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;monitor de isolamento da linha&lt;/strong&gt; vigia continuamente esse estado. Ele calcula quanta corrente fluiria para a terra se uma pessoa tocasse um dos condutores e alarma quando esse valor ultrapassa um limiar da ordem de &lt;strong&gt;2 a 5 mA&lt;/strong&gt;. O alarme não significa que alguém está levando choque: significa que o sistema deixou de ser isolado e que uma &lt;em&gt;segunda&lt;/em&gt; falha passaria a ser perigosa. A conduta é lógica — desconectar o último aparelho ligado, que quase sempre é o defeituoso, observar se o alarme cessa e encaminhar o equipamento à engenharia clínica. Se o alarme persistir após a retirada, retiram-se sequencialmente os equipamentos não essenciais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alarme é preditivo, e desconectar a monitorização do paciente aumenta o risco em vez de reduzi-lo. (B) o aterramento do prédio não foi perdido, e transferir o paciente é desproporcional. (C) silenciar sem investigar anula a função do dispositivo e mantém o sistema sem redundância de segurança.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O sistema de força isolada emprega um &lt;strong&gt;transformador de isolamento&lt;/strong&gt;, que separa eletricamente a rede da sala do sistema aterrado do prédio. Em um circuito isolado, tocar em apenas um dos condutores não fecha circuito com a terra e, portanto, não causa choque. A finalidade não é evitar microchoque, e sim garantir que uma &lt;strong&gt;primeira falha&lt;/strong&gt; de isolamento não interrompa a energia nem eletrocute alguém.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;monitor de isolamento da linha&lt;/strong&gt; vigia continuamente esse estado. Ele calcula quanta corrente fluiria para a terra se uma pessoa tocasse um dos condutores e alarma quando esse valor ultrapassa um limiar da ordem de &lt;strong&gt;2 a 5 mA&lt;/strong&gt;. O alarme não significa que alguém está levando choque: significa que o sistema deixou de ser isolado e que uma &lt;em&gt;segunda&lt;/em&gt; falha passaria a ser perigosa. A conduta é lógica: desconectar o último aparelho ligado, que quase sempre é o defeituoso, observar se o alarme cessa e encaminhar o equipamento à engenharia clínica. Se o alarme persistir após a retirada, retiram-se sequencialmente os equipamentos não essenciais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alarme é preditivo, e desconectar a monitorização do paciente aumenta o risco em vez de reduzi-lo. (B) o aterramento do prédio não foi perdido, e transferir o paciente é desproporcional. (C) silenciar sem investigar anula a função do dispositivo e mantém o sistema sem redundância de segurança.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;temperatura crítica&lt;/strong&gt; é aquela acima da qual um gás não pode ser liquefeito por maior que seja a pressão aplicada. Para o oxigênio, ela é de −118 °C, muito abaixo da temperatura ambiente: no cilindro E, o oxigênio existe apenas como gás comprimido, e a pressão obedece à lei de Boyle, caindo proporcionalmente ao conteúdo. Um manômetro que marca metade da pressão inicial indica metade do conteúdo.&lt;/p&gt;&lt;p&gt;O óxido nitroso tem temperatura crítica de &lt;strong&gt;36,5 °C&lt;/strong&gt;, acima da temperatura ambiente. Ele é armazenado em grande parte na &lt;strong&gt;fase líquida&lt;/strong&gt;, em equilíbrio com o vapor saturado. Enquanto houver líquido, cada molécula retirada é reposta por vaporização, e a pressão do vapor permanece constante — cerca de &lt;strong&gt;745 psi (5.100 kPa) a 20 °C&lt;/strong&gt;. A pressão só começa a cair quando o líquido acaba, momento em que resta menos de um quarto do conteúdo original. Por isso o único método confiável de estimar o conteúdo é &lt;strong&gt;pesar o cilindro&lt;/strong&gt; e subtrair a tara gravada no corpo. O resfriamento da parede, descrito no caso, decorre do calor latente consumido na vaporização.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporcionalidade vale para o oxigênio, não para o óxido nitroso. (C) a temperatura crítica é &lt;em&gt;superior&lt;/em&gt; à ambiente, e é exatamente por isso que a pressão se mantém estável. (D) a pesagem é justamente o método recomendado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;temperatura crítica&lt;/strong&gt; é aquela acima da qual um gás não pode ser liquefeito por maior que seja a pressão aplicada. Para o oxigênio, ela é de −118 °C, muito abaixo da temperatura ambiente: no cilindro E, o oxigênio existe apenas como gás comprimido, e a pressão obedece à lei de Boyle, caindo proporcionalmente ao conteúdo. Um manômetro que marca metade da pressão inicial indica metade do conteúdo.&lt;/p&gt;&lt;p&gt;O óxido nitroso tem temperatura crítica de &lt;strong&gt;36,5 °C&lt;/strong&gt;, acima da temperatura ambiente. Ele é armazenado em grande parte na &lt;strong&gt;fase líquida&lt;/strong&gt;, em equilíbrio com o vapor saturado. Enquanto houver líquido, cada molécula retirada é reposta por vaporização, e a pressão do vapor permanece constante, cerca de &lt;strong&gt;745 psi (5.100 kPa) a 20 °C&lt;/strong&gt;. A pressão só começa a cair quando o líquido acaba, momento em que resta menos de um quarto do conteúdo original. Por isso o único método confiável de estimar o conteúdo é &lt;strong&gt;pesar o cilindro&lt;/strong&gt; e subtrair a tara gravada no corpo. O resfriamento da parede, descrito no caso, decorre do calor latente consumido na vaporização.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporcionalidade vale para o oxigênio, não para o óxido nitroso. (C) a temperatura crítica é &lt;em&gt;superior&lt;/em&gt; à ambiente, e é exatamente por isso que a pressão se mantém estável. (D) a pesagem é justamente o método recomendado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nos aparelhos com fluxômetros em série, os gases se misturam ao longo de um coletor comum antes de seguirem para os vaporizadores e para a saída de gases frescos. Se houver um vazamento em algum ponto desse coletor, escapa preferencialmente o gás que estiver &lt;strong&gt;a montante&lt;/strong&gt; do orifício.&lt;/p&gt;&lt;p&gt;Daí a regra de projeto: o fluxômetro de &lt;strong&gt;oxigênio deve ser o último da sequência&lt;/strong&gt;, o mais próximo da saída comum. Assim, um vazamento no tubo do óxido nitroso ou do ar faz perder esses gases, e não o oxigênio; a mistura resultante fica &lt;em&gt;enriquecida&lt;/em&gt; em oxigênio. Na disposição inversa, um vazamento no coletor drenaria oxigênio e a mistura entregue ao paciente seria hipóxica.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;sistema proporcionador&lt;/strong&gt; é um dispositivo mecânico ou pneumático que acopla os controles de oxigênio e de óxido nitroso, limitando a proporção máxima a &lt;strong&gt;3 partes de óxido nitroso para 1 de oxigênio&lt;/strong&gt; — o que assegura fração inspirada mínima de aproximadamente &lt;strong&gt;25%&lt;/strong&gt;. Vale lembrar que ele não impede mistura hipóxica quando um terceiro gás, como o ar comprimido, é usado, nem detecta erro de abastecimento na tubulação; por isso o analisador de oxigênio permanece como monitor obrigatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica do vazamento. (B) o proporcionador não atua sobre vaporizadores. (C) troca a razão e o valor: são 3:1 e 25%, não 2:1 e 40%.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Nos aparelhos com fluxômetros em série, os gases se misturam ao longo de um coletor comum antes de seguirem para os vaporizadores e para a saída de gases frescos. Se houver um vazamento em algum ponto desse coletor, escapa preferencialmente o gás que estiver &lt;strong&gt;a montante&lt;/strong&gt; do orifício.&lt;/p&gt;&lt;p&gt;Daí a regra de projeto: o fluxômetro de &lt;strong&gt;oxigênio deve ser o último da sequência&lt;/strong&gt;, o mais próximo da saída comum. Assim, um vazamento no tubo do óxido nitroso ou do ar faz perder esses gases, e não o oxigênio; a mistura resultante fica &lt;em&gt;enriquecida&lt;/em&gt; em oxigênio. Na disposição inversa, um vazamento no coletor drenaria oxigênio e a mistura entregue ao paciente seria hipóxica.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;sistema proporcionador&lt;/strong&gt; é um dispositivo mecânico ou pneumático que acopla os controles de oxigênio e de óxido nitroso, limitando a proporção máxima a &lt;strong&gt;3 partes de óxido nitroso para 1 de oxigênio&lt;/strong&gt;, o que assegura fração inspirada mínima de aproximadamente &lt;strong&gt;25%&lt;/strong&gt;. Vale lembrar que ele não impede mistura hipóxica quando um terceiro gás, como o ar comprimido, é usado, nem detecta erro de abastecimento na tubulação; por isso o analisador de oxigênio permanece como monitor obrigatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica do vazamento. (B) o proporcionador não atua sobre vaporizadores. (C) troca a razão e o valor: são 3:1 e 25%, não 2:1 e 40%.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cal sodada é constituída em cerca de 80% por &lt;strong&gt;hidróxido de cálcio&lt;/strong&gt;, com pequena proporção de &lt;strong&gt;hidróxido de sódio&lt;/strong&gt; como ativador e cerca de 15% de &lt;strong&gt;água&lt;/strong&gt;. A absorção do CO2 é uma reação química em meio aquoso: o CO2 forma ácido carbônico com a água presente, que é então neutralizado pelas bases, gerando carbonato de cálcio, mais água e &lt;strong&gt;calor&lt;/strong&gt;. A água não é impureza — é reagente indispensável.&lt;/p&gt;&lt;p&gt;O indicador colorimétrico, usualmente o etil violeta, muda de branco para violeta quando o pH dos grânulos cai abaixo de aproximadamente 10,3, sinalizando exaustão. A cor, contudo, é um indicador imperfeito: &lt;em&gt;regride&lt;/em&gt; com o repouso do absorvedor e pode ser destruída pela luz ultravioleta ou pelo ressecamento, de modo que grânulo branco não garante absorvente ativo.&lt;/p&gt;&lt;p&gt;O ressecamento é a situação perigosa descrita no caso. Absorvente seco degrada os halogenados que contêm o grupo difluormetil — &lt;strong&gt;desflurano&lt;/strong&gt;, enflurano e isoflurano — produzindo &lt;strong&gt;monóxido de carbono&lt;/strong&gt; em quantidades potencialmente tóxicas. Com o sevoflurano, o absorvente seco gera reação fortemente exotérmica, com risco de calor extremo, formação de composto A e até incêndio. Absorvedor suspeito de ressecamento deve ser trocado antes do uso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (D) subestimam o risco químico do absorvente seco. (B) a mudança de cor é reversível e não confiável isoladamente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cal sodada é constituída em cerca de 80% por &lt;strong&gt;hidróxido de cálcio&lt;/strong&gt;, com pequena proporção de &lt;strong&gt;hidróxido de sódio&lt;/strong&gt; como ativador e cerca de 15% de &lt;strong&gt;água&lt;/strong&gt;. A absorção do CO2 é uma reação química em meio aquoso: o CO2 forma ácido carbônico com a água presente, que é então neutralizado pelas bases, gerando carbonato de cálcio, mais água e &lt;strong&gt;calor&lt;/strong&gt;. A água não é impureza: é reagente indispensável.&lt;/p&gt;&lt;p&gt;O indicador colorimétrico, usualmente o etil violeta, muda de branco para violeta quando o pH dos grânulos cai abaixo de aproximadamente 10,3, sinalizando exaustão. A cor, contudo, é um indicador imperfeito: &lt;em&gt;regride&lt;/em&gt; com o repouso do absorvedor e pode ser destruída pela luz ultravioleta ou pelo ressecamento, de modo que grânulo branco não garante absorvente ativo.&lt;/p&gt;&lt;p&gt;O ressecamento é a situação perigosa descrita no caso. Absorvente seco degrada os halogenados que contêm o grupo difluormetil (&lt;strong&gt;desflurano&lt;/strong&gt;, enflurano e isoflurano), produzindo &lt;strong&gt;monóxido de carbono&lt;/strong&gt; em quantidades potencialmente tóxicas. Com o sevoflurano, o absorvente seco gera reação fortemente exotérmica, com risco de calor extremo, formação de composto A e até incêndio. Absorvedor suspeito de ressecamento deve ser trocado antes do uso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (D) subestimam o risco químico do absorvente seco. (B) a mudança de cor é reversível e não confiável isoladamente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O comportamento de um gás depende do regime de fluxo. No &lt;strong&gt;fluxo laminar&lt;/strong&gt;, descrito pela lei de Poiseuille, o fluxo é proporcional à quarta potência do raio e à diferença de pressão, e inversamente proporcional ao comprimento e à &lt;strong&gt;viscosidade&lt;/strong&gt;. A densidade não participa dessa equação.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;fluxo turbulento&lt;/strong&gt;, a relação muda: o fluxo passa a variar com a raiz quadrada da diferença de pressão e inversamente com a raiz quadrada da &lt;strong&gt;densidade&lt;/strong&gt;. A transição entre os regimes é estimada pelo número de Reynolds, que aumenta com a velocidade, com o diâmetro e com a densidade, e diminui com a viscosidade. Valores acima de aproximadamente 4.000 indicam turbulência.&lt;/p&gt;&lt;p&gt;Uma via aérea estreitada por edema força alta velocidade linear e produz fluxo turbulento — o próprio estridor é a manifestação sonora disso. Substituir o nitrogênio pelo hélio reduz drasticamente a densidade da mistura, o que diminui o número de Reynolds (favorecendo o retorno ao regime laminar) e, no componente que permanece turbulento, reduz a resistência. O resultado é menor trabalho respiratório enquanto a causa do estreitamento é tratada. A limitação prática é que o benefício exige alta proporção de hélio, o que restringe a fração inspirada de oxigênio ofertável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a viscosidade do hélio é discretamente &lt;em&gt;maior&lt;/em&gt; que a do ar. (C) a menor densidade &lt;em&gt;reduz&lt;/em&gt; o número de Reynolds. (D) o hélio é inerte e não altera o edema tecidual.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O comportamento de um gás depende do regime de fluxo. No &lt;strong&gt;fluxo laminar&lt;/strong&gt;, descrito pela lei de Poiseuille, o fluxo é proporcional à quarta potência do raio e à diferença de pressão, e inversamente proporcional ao comprimento e à &lt;strong&gt;viscosidade&lt;/strong&gt;. A densidade não participa dessa equação.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;fluxo turbulento&lt;/strong&gt;, a relação muda: o fluxo passa a variar com a raiz quadrada da diferença de pressão e inversamente com a raiz quadrada da &lt;strong&gt;densidade&lt;/strong&gt;. A transição entre os regimes é estimada pelo número de Reynolds, que aumenta com a velocidade, com o diâmetro e com a densidade, e diminui com a viscosidade. Valores acima de aproximadamente 4.000 indicam turbulência.&lt;/p&gt;&lt;p&gt;Uma via aérea estreitada por edema força alta velocidade linear e produz fluxo turbulento; o próprio estridor é a manifestação sonora disso. Substituir o nitrogênio pelo hélio reduz drasticamente a densidade da mistura, o que diminui o número de Reynolds (favorecendo o retorno ao regime laminar) e, no componente que permanece turbulento, reduz a resistência. O resultado é menor trabalho respiratório enquanto a causa do estreitamento é tratada. A limitação prática é que o benefício exige alta proporção de hélio, o que restringe a fração inspirada de oxigênio ofertável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a viscosidade do hélio é discretamente &lt;em&gt;maior&lt;/em&gt; que a do ar. (C) a menor densidade &lt;em&gt;reduz&lt;/em&gt; o número de Reynolds. (D) o hélio é inerte e não altera o edema tecidual.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A posição de litotomia concentra risco neurológico em pontos previsíveis, e a topografia do déficit permite o diagnóstico à beira do leito. O &lt;strong&gt;nervo fibular comum&lt;/strong&gt; contorna a cabeça da fíbula em posição muito superficial, com pouquíssimo tecido interposto entre o nervo e o osso. Perneiras que apoiam a lateral da perna, ou o simples peso do membro contra a borda do suporte, comprimem o nervo nesse ponto — mecanismo agravado por tempo cirúrgico prolongado e por índice de massa corporal elevado.&lt;/p&gt;&lt;p&gt;O quadro resultante é característico: &lt;strong&gt;pé caído&lt;/strong&gt; por paralisia dos dorsiflexores e eversores, com perda de sensibilidade no dorso do pé e na face lateral da perna, e preservação da flexão plantar e da sensibilidade plantar. A prevenção é acolchoar a região da cabeça da fíbula, evitar apoio lateral direto, limitar o tempo em litotomia e reduzir o grau de flexão e abdução do quadril.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão do obturatório, associada à abdução excessiva do quadril, causa fraqueza de adução e alteração sensitiva na face medial da coxa, expressamente preservadas no caso. (B) a lesão do femoral cursa com fraqueza de extensão do joelho, também preservada. (C) a lesão do ciático por estiramento produz déficit mais extenso, incluindo flexão plantar e sensibilidade plantar, o que não corresponde ao déficit localizado descrito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A posição de litotomia concentra risco neurológico em pontos previsíveis, e a topografia do déficit permite o diagnóstico à beira do leito. O &lt;strong&gt;nervo fibular comum&lt;/strong&gt; contorna a cabeça da fíbula em posição muito superficial, com pouquíssimo tecido interposto entre o nervo e o osso. Perneiras que apoiam a lateral da perna, ou o simples peso do membro contra a borda do suporte, comprimem o nervo nesse ponto, mecanismo agravado por tempo cirúrgico prolongado e por índice de massa corporal elevado.&lt;/p&gt;&lt;p&gt;O quadro resultante é característico: &lt;strong&gt;pé caído&lt;/strong&gt; por paralisia dos dorsiflexores e eversores, com perda de sensibilidade no dorso do pé e na face lateral da perna, e preservação da flexão plantar e da sensibilidade plantar. A prevenção é acolchoar a região da cabeça da fíbula, evitar apoio lateral direto, limitar o tempo em litotomia e reduzir o grau de flexão e abdução do quadril.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão do obturatório, associada à abdução excessiva do quadril, causa fraqueza de adução e alteração sensitiva na face medial da coxa, expressamente preservadas no caso. (B) a lesão do femoral cursa com fraqueza de extensão do joelho, também preservada. (C) a lesão do ciático por estiramento produz déficit mais extenso, incluindo flexão plantar e sensibilidade plantar, o que não corresponde ao déficit localizado descrito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na posição sentada, o campo cirúrgico fica acima do átrio direito e a pressão nas veias durais e diploicas pode tornar-se subatmosférica. Essas veias não colapsam por estarem aderidas ao osso e ao seio, o que permite a entrada contínua de ar — daí a incidência elevada de embolia aérea venosa em craniotomia de fossa posterior. A capnografia e o Doppler precordial são os monitores mais sensíveis disponíveis rotineiramente, e a tríade de queda súbita do CO2 expirado final, hipotensão e alteração do sinal do Doppler define o diagnóstico.&lt;/p&gt;&lt;p&gt;O tratamento tem prioridades bem estabelecidas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Interromper a entrada de ar:&lt;/strong&gt; avisar o cirurgião para inundar o campo com solução salina, aplicar cera óssea e comprimir as bordas; comprimir as jugulares aumenta a pressão venosa cerebral e ajuda a localizar o ponto de entrada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Suspender o óxido nitroso&lt;/strong&gt; e ofertar oxigênio a 100%: o óxido nitroso difunde-se para dentro da bolha e pode multiplicar seu volume, agravando a obstrução da via de saída do ventrículo direito.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Suporte hemodinâmico:&lt;/strong&gt; volume e vasopressor; aspiração pelo cateter em átrio direito; se necessário, decúbito lateral esquerdo com cabeceira baixa.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) manter o óxido nitroso é justamente o erro central. (C) a hiperventilação reduz ainda mais o CO2 expirado e o vasodilatador agrava a hipotensão e a entrada de ar. (D) descartar o Doppler nesse contexto elimina o monitor mais sensível para o evento em curso.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na posição sentada, o campo cirúrgico fica acima do átrio direito e a pressão nas veias durais e diploicas pode tornar-se subatmosférica. Essas veias não colapsam por estarem aderidas ao osso e ao seio, o que permite a entrada contínua de ar; daí a incidência elevada de embolia aérea venosa em craniotomia de fossa posterior. A capnografia e o Doppler precordial são os monitores mais sensíveis disponíveis rotineiramente, e a tríade de queda súbita do CO2 expirado final, hipotensão e alteração do sinal do Doppler define o diagnóstico.&lt;/p&gt;&lt;p&gt;O tratamento tem prioridades bem estabelecidas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Interromper a entrada de ar:&lt;/strong&gt; avisar o cirurgião para inundar o campo com solução salina, aplicar cera óssea e comprimir as bordas; comprimir as jugulares aumenta a pressão venosa cerebral e ajuda a localizar o ponto de entrada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Suspender o óxido nitroso&lt;/strong&gt; e ofertar oxigênio a 100%: o óxido nitroso difunde-se para dentro da bolha e pode multiplicar seu volume, agravando a obstrução da via de saída do ventrículo direito.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Suporte hemodinâmico:&lt;/strong&gt; volume e vasopressor; aspiração pelo cateter em átrio direito; se necessário, decúbito lateral esquerdo com cabeceira baixa.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) manter o óxido nitroso é justamente o erro central. (C) a hiperventilação reduz ainda mais o CO2 expirado e o vasodilatador agrava a hipotensão e a entrada de ar. (D) descartar o Doppler nesse contexto elimina o monitor mais sensível para o evento em curso.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O despertar intraoperatório com recordação explícita é um evento raro, mas de grande impacto: até um terço dos pacientes acometidos desenvolve sintomas persistentes de estresse pós-traumático. Estudos prospectivos de grande porte situam a incidência em torno de &lt;strong&gt;0,1% a 0,2%&lt;/strong&gt; — aproximadamente 1 a 2 casos por mil anestesias gerais. Relatos espontâneos no pós-operatório subestimam esse número, razão pela qual se recomenda a entrevista estruturada em momentos seriados.&lt;/p&gt;&lt;p&gt;Os fatores de risco distribuem-se em três categorias:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Relacionados à técnica:&lt;/strong&gt; uso de bloqueador neuromuscular, que suprime o movimento — o sinal de alarme mais confiável de plano insuficiente e o principal fator de risco isolado; anestesia venosa total sem monitorização de profundidade; dose reduzida de hipnótico; falha de equipamento ou de infusão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relacionados ao procedimento:&lt;/strong&gt; cesariana de urgência, cirurgia cardíaca e trauma, situações nas quais a instabilidade hemodinâmica limita a dose de hipnótico; a incidência nesses contextos aproxima-se de 1%.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relacionados ao paciente:&lt;/strong&gt; episódio prévio de despertar, uso crônico de opioides e outros depressores, dificuldade de via aérea prevista e classificação ASA elevada.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) superestima a incidência em cerca de vinte e cinco vezes e inverte o efeito do bloqueador neuromuscular. (B) a cesariana é reconhecidamente um cenário de &lt;em&gt;maior&lt;/em&gt; risco. (D) o índice bispectral reduz, mas não elimina, a ocorrência de despertar, e não substitui a monitorização da concentração expirada do halogenado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O despertar intraoperatório com recordação explícita é um evento raro, mas de grande impacto: até um terço dos pacientes acometidos desenvolve sintomas persistentes de estresse pós-traumático. Estudos prospectivos de grande porte situam a incidência em torno de &lt;strong&gt;0,1% a 0,2%&lt;/strong&gt;, aproximadamente 1 a 2 casos por mil anestesias gerais. Relatos espontâneos no pós-operatório subestimam esse número, razão pela qual se recomenda a entrevista estruturada em momentos seriados.&lt;/p&gt;&lt;p&gt;Os fatores de risco distribuem-se em três categorias:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Relacionados à técnica:&lt;/strong&gt; uso de bloqueador neuromuscular, que suprime o movimento (o sinal de alarme mais confiável de plano insuficiente) e é o principal fator de risco isolado; anestesia venosa total sem monitorização de profundidade; dose reduzida de hipnótico; falha de equipamento ou de infusão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relacionados ao procedimento:&lt;/strong&gt; cesariana de urgência, cirurgia cardíaca e trauma, situações nas quais a instabilidade hemodinâmica limita a dose de hipnótico; a incidência nesses contextos aproxima-se de 1%.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Relacionados ao paciente:&lt;/strong&gt; episódio prévio de despertar, uso crônico de opioides e outros depressores, dificuldade de via aérea prevista e classificação ASA elevada.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) superestima a incidência em cerca de vinte e cinco vezes e inverte o efeito do bloqueador neuromuscular. (B) a cesariana é reconhecidamente um cenário de &lt;em&gt;maior&lt;/em&gt; risco. (D) o índice bispectral reduz, mas não elimina, a ocorrência de despertar, e não substitui a monitorização da concentração expirada do halogenado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Áreas úmidas — salas com irrigação abundante, hemodinâmica, endoscopia urológica, artroscopia — exigem proteção adicional porque a umidade reduz drasticamente a resistência da pele e do piso, aumentando a corrente que atravessa uma pessoa em caso de falha. As normas admitem duas soluções: sistema de força isolada com monitor de linha ou &lt;strong&gt;interruptor de falha de aterramento&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O interruptor de falha de aterramento compara continuamente a corrente que sai pelo condutor fase com a que retorna pelo neutro. Se houver diferença — sinal de que parte da corrente está escapando para a terra, possivelmente através de uma pessoa — o dispositivo &lt;strong&gt;abre o circuito em milissegundos&lt;/strong&gt;, com limiar da ordem de &lt;strong&gt;5 mA&lt;/strong&gt;. É uma proteção eficaz contra macrochoque e barata de instalar.&lt;/p&gt;&lt;p&gt;Sua desvantagem é justamente o modo de agir: ao cortar a energia, pode desligar um equipamento em uso durante um momento crítico do procedimento. O sistema de força isolada tem lógica oposta — diante da primeira falha, o monitor apenas &lt;em&gt;alarma&lt;/em&gt; e a energia continua disponível, permitindo concluir a etapa cirúrgica em segurança antes de retirar o aparelho defeituoso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) descreve o comportamento do sistema de força isolada, não o do interruptor. (C) o limiar de 5 mA é cinquenta vezes maior que a corrente capaz de fibrilar por via intracardíaca; nenhum dos dois sistemas protege contra microchoque. (D) a conversão em rede não aterrada é obtida pelo transformador de isolamento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Áreas úmidas (salas com irrigação abundante, hemodinâmica, endoscopia urológica, artroscopia) exigem proteção adicional porque a umidade reduz drasticamente a resistência da pele e do piso, aumentando a corrente que atravessa uma pessoa em caso de falha. As normas admitem duas soluções: sistema de força isolada com monitor de linha ou &lt;strong&gt;interruptor de falha de aterramento&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O interruptor de falha de aterramento compara continuamente a corrente que sai pelo condutor fase com a que retorna pelo neutro. Se houver diferença (sinal de que parte da corrente está escapando para a terra, possivelmente através de uma pessoa), o dispositivo &lt;strong&gt;abre o circuito em milissegundos&lt;/strong&gt;, com limiar da ordem de &lt;strong&gt;5 mA&lt;/strong&gt;. É uma proteção eficaz contra macrochoque e barata de instalar.&lt;/p&gt;&lt;p&gt;Sua desvantagem é justamente o modo de agir: ao cortar a energia, pode desligar um equipamento em uso durante um momento crítico do procedimento. O sistema de força isolada tem lógica oposta: diante da primeira falha, o monitor apenas &lt;em&gt;alarma&lt;/em&gt; e a energia continua disponível, permitindo concluir a etapa cirúrgica em segurança antes de retirar o aparelho defeituoso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) descreve o comportamento do sistema de força isolada, não o do interruptor. (C) o limiar de 5 mA é cinquenta vezes maior que a corrente capaz de fibrilar por via intracardíaca; nenhum dos dois sistemas protege contra microchoque. (D) a conversão em rede não aterrada é obtida pelo transformador de isolamento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Pacotes de prevenção reúnem um número pequeno de intervenções com evidência consistente, aplicadas de forma integral e auditadas — a adesão parcial reduz muito o benefício. O &lt;strong&gt;pacote do cateter venoso central&lt;/strong&gt; apoia-se em cinco elementos: higiene das mãos; antissepsia da pele com solução alcoólica de clorexidina acima de 0,5%; &lt;strong&gt;barreira estéril máxima&lt;/strong&gt; na inserção (gorro, máscara, avental e luvas estéreis e campo de corpo inteiro); escolha criteriosa do sítio, evitando a veia femoral; e &lt;strong&gt;revisão diária&lt;/strong&gt; da necessidade do cateter, com remoção assim que ele deixar de ser indispensável.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;pacote da pneumonia associada à ventilação&lt;/strong&gt; inclui elevação da cabeceira a 30 a 45 graus, interrupção diária da sedação com avaliação da possibilidade de desmame e extubação, higiene oral regular, profilaxia de tromboembolismo venoso, profilaxia de úlcera de estresse quando indicada e aspiração de secreção subglótica em intubações prolongadas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a troca programada de cateter em intervalos fixos não reduz infecção e expõe o paciente a novas complicações mecânicas, e o antibiótico sistêmico profilático de rotina não é recomendado. (B) o decúbito horizontal favorece a aspiração de conteúdo gástrico, e a troca rotineira do circuito do ventilador aumenta a manipulação sem reduzir a incidência de pneumonia. (D) a sedação profunda contínua prolonga a ventilação e eleva o risco, sendo o oposto da interrupção diária preconizada; a traqueostomia precoce de rotina não faz parte do pacote.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Pacotes de prevenção reúnem um número pequeno de intervenções com evidência consistente, aplicadas de forma integral e auditadas, já que a adesão parcial reduz muito o benefício. O &lt;strong&gt;pacote do cateter venoso central&lt;/strong&gt; apoia-se em cinco elementos: higiene das mãos; antissepsia da pele com solução alcoólica de clorexidina acima de 0,5%; &lt;strong&gt;barreira estéril máxima&lt;/strong&gt; na inserção (gorro, máscara, avental e luvas estéreis e campo de corpo inteiro); escolha criteriosa do sítio, evitando a veia femoral; e &lt;strong&gt;revisão diária&lt;/strong&gt; da necessidade do cateter, com remoção assim que ele deixar de ser indispensável.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;pacote da pneumonia associada à ventilação&lt;/strong&gt; inclui elevação da cabeceira a 30 a 45 graus, interrupção diária da sedação com avaliação da possibilidade de desmame e extubação, higiene oral regular, profilaxia de tromboembolismo venoso, profilaxia de úlcera de estresse quando indicada e aspiração de secreção subglótica em intubações prolongadas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a troca programada de cateter em intervalos fixos não reduz infecção e expõe o paciente a novas complicações mecânicas, e o antibiótico sistêmico profilático de rotina não é recomendado. (B) o decúbito horizontal favorece a aspiração de conteúdo gástrico, e a troca rotineira do circuito do ventilador aumenta a manipulação sem reduzir a incidência de pneumonia. (D) a sedação profunda contínua prolonga a ventilação e eleva o risco, sendo o oposto da interrupção diária preconizada; a traqueostomia precoce de rotina não faz parte do pacote.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A creatinina sérica resulta do equilíbrio entre a &lt;strong&gt;produção&lt;/strong&gt;, proporcional à massa muscular, e a &lt;strong&gt;depuração renal&lt;/strong&gt;. No idoso, esses dois termos caem em paralelo.&lt;/p&gt;&lt;p&gt;A filtração glomerular declina cerca de 1 mL/min por ano, ou aproximadamente 1 por cento ao ano, a partir da quarta década, acompanhada de perda de massa renal, esclerose glomerular e redução do fluxo plasmático renal. Simultaneamente, a sarcopenia reduz a geração diária de creatinina. O resultado é uma creatinina sérica que permanece dentro da faixa de referência mesmo com &lt;strong&gt;perda substancial de função renal&lt;/strong&gt; — em uma paciente como a do caso, uma creatinina de 0,9 mg/dL pode corresponder a uma depuração bem inferior a 60 mL/min.&lt;/p&gt;&lt;p&gt;Por isso, a avaliação deve usar equações de estimativa que incorporem idade, sexo e peso, ou a depuração medida, e não a creatinina isolada. As implicações anestésicas são diretas: cautela com fármacos de eliminação renal e seus metabólitos ativos, evitação de anti-inflamatórios não esteroides, atenção ao contraste iodado e à hipovolemia, e maior risco de retenção hídrica e de distúrbios eletrolíticos, já que a capacidade de concentrar e diluir a urina também está reduzida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) é exatamente a armadilha da questão, pois a creatinina isolada não afasta disfunção renal no idoso; (B) a filtração glomerular diminui com a idade, não aumenta; (C) a produção muscular de creatinina está reduzida na sarcopenia, e não aumentada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A creatinina sérica resulta do equilíbrio entre a &lt;strong&gt;produção&lt;/strong&gt;, proporcional à massa muscular, e a &lt;strong&gt;depuração renal&lt;/strong&gt;. No idoso, esses dois termos caem em paralelo.&lt;/p&gt;&lt;p&gt;A filtração glomerular declina cerca de 1 mL/min por ano, ou aproximadamente 1 por cento ao ano, a partir da quarta década, acompanhada de perda de massa renal, esclerose glomerular e redução do fluxo plasmático renal. Simultaneamente, a sarcopenia reduz a geração diária de creatinina. O resultado é uma creatinina sérica que permanece dentro da faixa de referência mesmo com &lt;strong&gt;perda substancial de função renal&lt;/strong&gt;: em uma paciente como a do caso, uma creatinina de 0,9 mg/dL pode corresponder a uma depuração bem inferior a 60 mL/min.&lt;/p&gt;&lt;p&gt;Por isso, a avaliação deve usar equações de estimativa que incorporem idade, sexo e peso, ou a depuração medida, e não a creatinina isolada. As implicações anestésicas são diretas: cautela com fármacos de eliminação renal e seus metabólitos ativos, evitação de anti-inflamatórios não esteroides, atenção ao contraste iodado e à hipovolemia, e maior risco de retenção hídrica e de distúrbios eletrolíticos, já que a capacidade de concentrar e diluir a urina também está reduzida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) é exatamente a armadilha da questão, pois a creatinina isolada não afasta disfunção renal no idoso; (B) a filtração glomerular diminui com a idade, não aumenta; (C) a produção muscular de creatinina está reduzida na sarcopenia, e não aumentada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A percepção dolorosa após um estímulo nocivo intenso costuma ser &lt;strong&gt;bifásica&lt;/strong&gt;, e essa dupla sensação reflete a diferença de velocidade de condução entre duas populações de aferentes primários. A &lt;em&gt;primeira dor&lt;/em&gt; é rápida, em pontada e bem localizada; a &lt;em&gt;segunda dor&lt;/em&gt; é tardia, em queimação, difusa e persistente.&lt;/p&gt;&lt;p&gt;As fibras &lt;strong&gt;A-delta&lt;/strong&gt; são finamente mielinizadas, conduzem a cerca de 5 a 30 m/s, têm campos receptivos pequenos e respondem sobretudo a estímulos mecânicos de alto limiar e térmicos: são as responsáveis pela primeira dor. As fibras &lt;strong&gt;C&lt;/strong&gt; são amielínicas, conduzem lentamente (aproximadamente 0,5 a 2 m/s), são polimodais (respondem a estímulos mecânicos, térmicos e químicos) e possuem campos receptivos amplos e sobrepostos, o que explica a má localização da segunda dor. São também as fibras cuja estimulação repetitiva gera &lt;em&gt;wind-up&lt;/em&gt; no corno dorsal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as fibras A-beta são de grosso calibre, conduzem tato e propriocepção e, pela teoria da comporta, inibem a transmissão nociceptiva — não veiculam dor em condições normais. (C) descreve corretamente as fibras A-delta, mas estas medeiam a primeira dor, e não a fase tardia em queimação. (D) atribui às fibras C uma velocidade de condução que corresponde às fibras mielinizadas finas, além de campos receptivos restritos, o oposto do que se observa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A percepção dolorosa após um estímulo nocivo intenso costuma ser &lt;strong&gt;bifásica&lt;/strong&gt;, e essa dupla sensação reflete a diferença de velocidade de condução entre duas populações de aferentes primários. A &lt;em&gt;primeira dor&lt;/em&gt; é rápida, em pontada e bem localizada; a &lt;em&gt;segunda dor&lt;/em&gt; é tardia, em queimação, difusa e persistente.&lt;/p&gt;&lt;p&gt;As fibras &lt;strong&gt;A-delta&lt;/strong&gt; são finamente mielinizadas, conduzem a cerca de 5 a 30 m/s, têm campos receptivos pequenos e respondem sobretudo a estímulos mecânicos de alto limiar e térmicos: são as responsáveis pela primeira dor. As fibras &lt;strong&gt;C&lt;/strong&gt; são amielínicas, conduzem lentamente (aproximadamente 0,5 a 2 m/s), são polimodais (respondem a estímulos mecânicos, térmicos e químicos) e possuem campos receptivos amplos e sobrepostos, o que explica a má localização da segunda dor. São também as fibras cuja estimulação repetitiva gera &lt;em&gt;wind-up&lt;/em&gt; no corno dorsal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as fibras A-beta são de grosso calibre, conduzem tato e propriocepção e, pela teoria da comporta, inibem a transmissão nociceptiva; não veiculam dor em condições normais. (C) descreve corretamente as fibras A-delta, mas estas medeiam a primeira dor, e não a fase tardia em queimação. (D) atribui às fibras C uma velocidade de condução que corresponde às fibras mielinizadas finas, além de campos receptivos restritos, o oposto do que se observa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cetamina é um &lt;strong&gt;antagonista não competitivo&lt;/strong&gt; do receptor NMDA: liga-se a um sítio no interior do poro do canal (o mesmo sítio da fenciclidina), acessível apenas quando o canal está aberto. Ao impedir o influxo de cálcio mediado pelo NMDA, ela interrompe a cascata que sustenta o &lt;em&gt;wind-up&lt;/em&gt;, a sensibilização central e a hiperalgesia induzida por opioides.&lt;/p&gt;&lt;p&gt;Esse perfil explica o benefício particular em pacientes &lt;strong&gt;tolerantes a opioides&lt;/strong&gt;, como a do caso, e em cirurgias de grande porte com dor esperada intensa. As doses usadas para esse fim são subanestésicas — tipicamente um bolus da ordem de 0,15 a 0,5 mg/kg seguido de infusão em torno de 0,1 a 0,3 mg/kg/h —, faixa em que os efeitos psicomiméticos são pouco frequentes. A cetamina tem ainda ações acessórias em receptores monoaminérgicos, colinérgicos e canais de sódio, mas o efeito antinociceptivo central é atribuído ao bloqueio NMDA.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cetamina tem afinidade fraca por receptores opioides, insuficiente para explicar o efeito clínico, e o mecanismo proposto não reduziria tolerância. (C) o sítio da glicina é um sítio modulatório do NMDA, mas a cetamina não age nele nem por antagonismo competitivo. (D) o bloqueio de canais de cálcio do tipo N descreve a ziconotida, fármaco de uso intratecal, e não a cetamina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cetamina é um &lt;strong&gt;antagonista não competitivo&lt;/strong&gt; do receptor NMDA: liga-se a um sítio no interior do poro do canal (o mesmo sítio da fenciclidina), acessível apenas quando o canal está aberto. Ao impedir o influxo de cálcio mediado pelo NMDA, ela interrompe a cascata que sustenta o &lt;em&gt;wind-up&lt;/em&gt;, a sensibilização central e a hiperalgesia induzida por opioides.&lt;/p&gt;&lt;p&gt;Esse perfil explica o benefício particular em pacientes &lt;strong&gt;tolerantes a opioides&lt;/strong&gt;, como a do caso, e em cirurgias de grande porte com dor esperada intensa. As doses usadas para esse fim são subanestésicas (tipicamente um bolus da ordem de 0,15 a 0,5 mg/kg seguido de infusão em torno de 0,1 a 0,3 mg/kg/h), faixa em que os efeitos psicomiméticos são pouco frequentes. A cetamina tem ainda ações acessórias em receptores monoaminérgicos, colinérgicos e canais de sódio, mas o efeito antinociceptivo central é atribuído ao bloqueio NMDA.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cetamina tem afinidade fraca por receptores opioides, insuficiente para explicar o efeito clínico, e o mecanismo proposto não reduziria tolerância. (C) o sítio da glicina é um sítio modulatório do NMDA, mas a cetamina não age nele nem por antagonismo competitivo. (D) o bloqueio de canais de cálcio do tipo N descreve a ziconotida, fármaco de uso intratecal, e não a cetamina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A síndrome dolorosa regional complexa (SDRC) caracteriza-se por dor &lt;strong&gt;desproporcional&lt;/strong&gt; ao evento desencadeante, acompanhada de manifestações sensoriais, vasomotoras, sudomotoras e motoras/tróficas, geralmente distais e sem respeitar territórios de nervo ou raiz. A distinção entre os tipos é puramente etiológica: no &lt;strong&gt;tipo I&lt;/strong&gt; (antiga distrofia simpático-reflexa) não há lesão nervosa identificável, sendo o trauma de extremidade — sobretudo fratura do punho — o gatilho mais comum; no &lt;strong&gt;tipo II&lt;/strong&gt; (antiga causalgia) existe lesão de nervo periférico documentada.&lt;/p&gt;&lt;p&gt;Os critérios de Budapeste organizam o diagnóstico, que é clínico e de exclusão: exige-se dor contínua desproporcional, &lt;em&gt;sintomas&lt;/em&gt; relatados em pelo menos três das quatro categorias (sensorial, vasomotora, sudomotora/edema, motora/trófica), &lt;em&gt;sinais&lt;/em&gt; observados em pelo menos duas delas e ausência de outro diagnóstico que explique melhor o quadro. O paciente descrito preenche todas as categorias e tem eletroneuromiografia sem lesão troncular, o que o classifica como tipo I.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o tipo II pressupõe lesão nervosa demonstrada, ausente aqui; além disso, a dor da SDRC caracteristicamente extrapola o território do nervo. (B) a síndrome do túnel do carpo cursa com parestesia nos três primeiros dedos e alterações neurofisiológicas, sem as alterações vasomotoras e tróficas descritas. (D) a dor miofascial produz dor referida à palpação de bandas tensas, sem edema, discromia ou assimetria térmica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A síndrome dolorosa regional complexa (SDRC) caracteriza-se por dor &lt;strong&gt;desproporcional&lt;/strong&gt; ao evento desencadeante, acompanhada de manifestações sensoriais, vasomotoras, sudomotoras e motoras/tróficas, geralmente distais e sem respeitar territórios de nervo ou raiz. A distinção entre os tipos é puramente etiológica: no &lt;strong&gt;tipo I&lt;/strong&gt; (antiga distrofia simpático-reflexa) não há lesão nervosa identificável, sendo o trauma de extremidade (sobretudo fratura do punho) o gatilho mais comum; no &lt;strong&gt;tipo II&lt;/strong&gt; (antiga causalgia) existe lesão de nervo periférico documentada.&lt;/p&gt;&lt;p&gt;Os critérios de Budapeste organizam o diagnóstico, que é clínico e de exclusão: exige-se dor contínua desproporcional, &lt;em&gt;sintomas&lt;/em&gt; relatados em pelo menos três das quatro categorias (sensorial, vasomotora, sudomotora/edema, motora/trófica), &lt;em&gt;sinais&lt;/em&gt; observados em pelo menos duas delas e ausência de outro diagnóstico que explique melhor o quadro. O paciente descrito preenche todas as categorias e tem eletroneuromiografia sem lesão troncular, o que o classifica como tipo I.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o tipo II pressupõe lesão nervosa demonstrada, ausente aqui; além disso, a dor da SDRC caracteristicamente extrapola o território do nervo. (B) a síndrome do túnel do carpo cursa com parestesia nos três primeiros dedos e alterações neurofisiológicas, sem as alterações vasomotoras e tróficas descritas. (D) a dor miofascial produz dor referida à palpação de bandas tensas, sem edema, discromia ou assimetria térmica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os dois agentes destroem o tecido nervoso, mas por vias físico-químicas distintas — o álcool por extração de lipídios e precipitação de proteínas, o fenol por desnaturação proteica — e suas diferenças práticas determinam a técnica.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Álcool&lt;/strong&gt; (concentrações de cerca de 50% a 100%): é &lt;em&gt;hipobárico&lt;/em&gt; em relação ao líquor, de modo que, em neurólise subaracnóidea, o paciente é posicionado com o lado a ser tratado para cima. A injeção é intensamente &lt;strong&gt;dolorosa&lt;/strong&gt;, em queimação, o que muitas vezes exige anestésico local prévio. O efeito neurolítico se instala em 12 a 24 horas e tende a ser mais duradouro.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fenol&lt;/strong&gt; (cerca de 6% a 12%, em glicerina ou água): é &lt;em&gt;hiperbárico&lt;/em&gt;, e o lado a tratar fica para baixo. Tem efeito anestésico local inicial, tornando a injeção praticamente &lt;strong&gt;indolor&lt;/strong&gt;, e sua ação neurolítica é geralmente de menor duração.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambos, o risco maior é a difusão para raízes motoras ou esfincterianas e a neurite pós-neurolítica com dor por desaferentação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as duas propriedades do álcool, que é doloroso e hipobárico. (C) a baricidade dos dois é oposta e é justamente ela que define o posicionamento, não a disponibilidade institucional. (D) inverte a duração: o bloqueio com álcool tende a ser mais prolongado que o com fenol.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os dois agentes destroem o tecido nervoso, mas por vias físico-químicas distintas (o álcool por extração de lipídios e precipitação de proteínas, o fenol por desnaturação proteica), e suas diferenças práticas determinam a técnica.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Álcool&lt;/strong&gt; (concentrações de cerca de 50% a 100%): é &lt;em&gt;hipobárico&lt;/em&gt; em relação ao líquor, de modo que, em neurólise subaracnóidea, o paciente é posicionado com o lado a ser tratado para cima. A injeção é intensamente &lt;strong&gt;dolorosa&lt;/strong&gt;, em queimação, o que muitas vezes exige anestésico local prévio. O efeito neurolítico se instala em 12 a 24 horas e tende a ser mais duradouro.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fenol&lt;/strong&gt; (cerca de 6% a 12%, em glicerina ou água): é &lt;em&gt;hiperbárico&lt;/em&gt;, e o lado a tratar fica para baixo. Tem efeito anestésico local inicial, tornando a injeção praticamente &lt;strong&gt;indolor&lt;/strong&gt;, e sua ação neurolítica é geralmente de menor duração.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambos, o risco maior é a difusão para raízes motoras ou esfincterianas e a neurite pós-neurolítica com dor por desaferentação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as duas propriedades do álcool, que é doloroso e hipobárico. (C) a baricidade dos dois é oposta e é justamente ela que define o posicionamento, não a disponibilidade institucional. (D) inverte a duração: o bloqueio com álcool tende a ser mais prolongado que o com fenol.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Agonistas parciais e agonistas-antagonistas — buprenorfina, nalbufina, butorfanol, pentazocina — combinam &lt;strong&gt;alta afinidade&lt;/strong&gt; pelo receptor mu com &lt;strong&gt;atividade intrínseca reduzida ou nula&lt;/strong&gt; nesse mesmo receptor. Em paciente virgem de opioides, produzem analgesia com teto de efeito. Em paciente &lt;strong&gt;fisicamente dependente&lt;/strong&gt; de um agonista pleno, porém, competem pelo receptor e deslocam o agonista ocupante, reduzindo abruptamente a estimulação mu e desencadeando &lt;strong&gt;abstinência precipitada&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O quadro descrito é típico: início em minutos a poucas dezenas de minutos, com hiperatividade autonômica e do sistema nervoso central — midríase, lacrimejamento, rinorreia, bocejos, piloereção, sudorese, cólicas, diarreia, agitação e, de forma marcante para o paciente oncológico, retorno intenso da dor. O tratamento é de suporte, com reintrodução do agonista pleno em doses tituladas; o antagonismo de alta afinidade pode exigir doses maiores que as habituais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade opioide cursaria com miose, sedação e bradipneia, o oposto do observado. (B) a nalbufina não inibe de modo relevante a glicuronidação da morfina, e o acúmulo de morfina-3-glicuronídeo produz mioclonias e hiperalgesia em dias, não em minutos. (C) reação anafilactoide cursaria com eritema, prurido, hipotensão e broncoespasmo, e não explica midríase, bocejos e retorno da dor de base.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Agonistas parciais e agonistas-antagonistas (buprenorfina, nalbufina, butorfanol, pentazocina) combinam &lt;strong&gt;alta afinidade&lt;/strong&gt; pelo receptor mu com &lt;strong&gt;atividade intrínseca reduzida ou nula&lt;/strong&gt; nesse mesmo receptor. Em paciente virgem de opioides, produzem analgesia com teto de efeito. Em paciente &lt;strong&gt;fisicamente dependente&lt;/strong&gt; de um agonista pleno, porém, competem pelo receptor e deslocam o agonista ocupante, reduzindo abruptamente a estimulação mu e desencadeando &lt;strong&gt;abstinência precipitada&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O quadro descrito é típico: início em minutos a poucas dezenas de minutos, com hiperatividade autonômica e do sistema nervoso central que se traduz em midríase, lacrimejamento, rinorreia, bocejos, piloereção, sudorese, cólicas, diarreia, agitação e, de forma marcante para o paciente oncológico, retorno intenso da dor. O tratamento é de suporte, com reintrodução do agonista pleno em doses tituladas; o antagonismo de alta afinidade pode exigir doses maiores que as habituais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade opioide cursaria com miose, sedação e bradipneia, o oposto do observado. (B) a nalbufina não inibe de modo relevante a glicuronidação da morfina, e o acúmulo de morfina-3-glicuronídeo produz mioclonias e hiperalgesia em dias, não em minutos. (C) reação anafilactoide cursaria com eritema, prurido, hipotensão e broncoespasmo, e não explica midríase, bocejos e retorno da dor de base.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O gânglio estrelado, ou cervicotorácico, resulta da fusão do gânglio cervical inferior com o primeiro torácico e situa-se em geral à frente do colo da primeira costela, entre C7 e T1. Por segurança, a punção é habitualmente realizada mais alta, no processo transverso de &lt;strong&gt;C6&lt;/strong&gt; (tubérculo de Chassaignac), contando com a difusão caudal do anestésico local.&lt;/p&gt;&lt;p&gt;É justamente aí que está a armadilha clínica: a &lt;strong&gt;síndrome de Horner&lt;/strong&gt; confirma apenas que a solução atingiu as fibras simpáticas destinadas à cabeça e ao pescoço, que se originam em nível mais alto. A inervação simpática do membro superior provém sobretudo de T2 a T8 e depende da difusão caudal do bloqueio. O indicador confiável de simpatólise do braço e da mão é, portanto, o &lt;strong&gt;aumento da temperatura cutânea&lt;/strong&gt; da extremidade — em geral 1 a 2 °C ou mais em relação ao lado oposto —, acompanhado de vasodilatação, redução da sudorese e perda da resposta vasoconstritora.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Horner é sinal de bloqueio simpático cefálico e pode ocorrer sem qualquer bloqueio do membro; é sinal de difusão, não de sucesso terapêutico. (B) a rouquidão indica bloqueio do laríngeo recorrente, uma &lt;em&gt;complicação&lt;/em&gt; por difusão anterior, sem relação com a eficácia simpática. (D) alterações motoras e parestesias sugerem bloqueio de raízes do plexo braquial, também complicação indesejada, já que fibras simpáticas pós-ganglionares não conduzem função motora somática.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O gânglio estrelado, ou cervicotorácico, resulta da fusão do gânglio cervical inferior com o primeiro torácico e situa-se em geral à frente do colo da primeira costela, entre C7 e T1. Por segurança, a punção é habitualmente realizada mais alta, no processo transverso de &lt;strong&gt;C6&lt;/strong&gt; (tubérculo de Chassaignac), contando com a difusão caudal do anestésico local.&lt;/p&gt;&lt;p&gt;É justamente aí que está a armadilha clínica: a &lt;strong&gt;síndrome de Horner&lt;/strong&gt; confirma apenas que a solução atingiu as fibras simpáticas destinadas à cabeça e ao pescoço, que se originam em nível mais alto. A inervação simpática do membro superior provém sobretudo de T2 a T8 e depende da difusão caudal do bloqueio. O indicador confiável de simpatólise do braço e da mão é, portanto, o &lt;strong&gt;aumento da temperatura cutânea&lt;/strong&gt; da extremidade (em geral 1 a 2 °C ou mais em relação ao lado oposto), acompanhado de vasodilatação, redução da sudorese e perda da resposta vasoconstritora.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Horner é sinal de bloqueio simpático cefálico e pode ocorrer sem qualquer bloqueio do membro; é sinal de difusão, não de sucesso terapêutico. (B) a rouquidão indica bloqueio do laríngeo recorrente, uma &lt;em&gt;complicação&lt;/em&gt; por difusão anterior, sem relação com a eficácia simpática. (D) alterações motoras e parestesias sugerem bloqueio de raízes do plexo braquial, também complicação indesejada, já que fibras simpáticas pós-ganglionares não conduzem função motora somática.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Apesar de o nome sugerir parentesco com o ácido gama-aminobutírico, a gabapentina &lt;strong&gt;não&lt;/strong&gt; age em receptores GABA nem é convertida em GABA. Seu alvo é a &lt;strong&gt;subunidade auxiliar alfa-2-delta&lt;/strong&gt; dos canais de cálcio voltagem-dependentes, cuja expressão aumenta nos terminais pré-sinápticos de aferentes primários após lesão neural. Ao se ligar a essa subunidade, o fármaco reduz o tráfego do canal para a membrana e diminui o influxo de cálcio dependente de despolarização, com consequente queda na liberação de neurotransmissores excitatórios como glutamato, substância P e peptídeo relacionado ao gene da calcitonina. O resultado é atenuação da sensibilização central. A pregabalina compartilha o mesmo mecanismo, com absorção mais previsível.&lt;/p&gt;&lt;p&gt;Do ponto de vista prático, a gabapentina é eliminada praticamente inalterada pelos &lt;strong&gt;rins&lt;/strong&gt;, exigindo ajuste conforme a depuração de creatinina — cuidado relevante na paciente diabética. A titulação deve ser lenta, pelos efeitos adversos de sedação, tontura, ataxia e edema periférico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o agonismo GABA-B corresponde ao baclofeno, não à gabapentina, cujo nome apenas ecoa o do neurotransmissor. (C) o bloqueio de canais de sódio em estado inativado descreve carbamazepina, oxcarbazepina e lamotrigina. (D) a inibição da recaptação de monoaminas com reforço das vias descendentes descreve duloxetina, venlafaxina e antidepressivos tricíclicos.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Apesar de o nome sugerir parentesco com o ácido gama-aminobutírico, a gabapentina &lt;strong&gt;não&lt;/strong&gt; age em receptores GABA nem é convertida em GABA. Seu alvo é a &lt;strong&gt;subunidade auxiliar alfa-2-delta&lt;/strong&gt; dos canais de cálcio voltagem-dependentes, cuja expressão aumenta nos terminais pré-sinápticos de aferentes primários após lesão neural. Ao se ligar a essa subunidade, o fármaco reduz o tráfego do canal para a membrana e diminui o influxo de cálcio dependente de despolarização, com consequente queda na liberação de neurotransmissores excitatórios como glutamato, substância P e peptídeo relacionado ao gene da calcitonina. O resultado é atenuação da sensibilização central. A pregabalina compartilha o mesmo mecanismo, com absorção mais previsível.&lt;/p&gt;&lt;p&gt;Do ponto de vista prático, a gabapentina é eliminada praticamente inalterada pelos &lt;strong&gt;rins&lt;/strong&gt;, exigindo ajuste conforme a depuração de creatinina, cuidado relevante na paciente diabética. A titulação deve ser lenta, pelos efeitos adversos de sedação, tontura, ataxia e edema periférico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o agonismo GABA-B corresponde ao baclofeno, não à gabapentina, cujo nome apenas ecoa o do neurotransmissor. (C) o bloqueio de canais de sódio em estado inativado descreve carbamazepina, oxcarbazepina e lamotrigina. (D) a inibição da recaptação de monoaminas com reforço das vias descendentes descreve duloxetina, venlafaxina e antidepressivos tricíclicos.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A metadona tem um perfil cinético peculiar, com curva de decaimento &lt;strong&gt;bifásica&lt;/strong&gt;. A fase inicial, de distribuição (alfa), dura aproximadamente 8 a 12 horas e é a que mantém concentrações acima do limiar analgésico. A fase terminal de eliminação (beta) é muito prolongada e variável entre indivíduos, situando-se com frequência entre 30 e 60 horas; ela mantém concentrações suficientes para &lt;strong&gt;suprimir a abstinência&lt;/strong&gt;, mas insuficientes para produzir analgesia.&lt;/p&gt;&lt;p&gt;Daí a regra prática que confunde muitos residentes: para &lt;em&gt;manutenção na dependência&lt;/em&gt;, dose única diária basta; para &lt;em&gt;analgesia&lt;/em&gt;, o intervalo precisa ser de 6 a 8 horas. A dissociação entre meia-vida longa e duração analgésica curta é também a razão do risco de acúmulo e depressão respiratória tardia quando a dose é escalonada rapidamente nos primeiros dias — o estado de equilíbrio pode levar de 5 a 7 dias.&lt;/p&gt;&lt;p&gt;A metadona ainda soma antagonismo NMDA e inibição da recaptação de monoaminas, o que a torna útil na dor neuropática, e prolonga o intervalo QT de modo dose-dependente. Sua razão de conversão com a morfina não é linear: quanto maior a dose prévia de morfina, maior a potência relativa da metadona.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a biodisponibilidade oral da metadona é alta, em torno de 70% a 90%. (B) a meia-vida terminal é longa e bastante variável, e a metadona não depende de metabólitos ativos. (C) a ligação ao receptor mu é reversível e competitiva, sem qualquer dependência de síntese de novos receptores.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A metadona tem um perfil cinético peculiar, com curva de decaimento &lt;strong&gt;bifásica&lt;/strong&gt;. A fase inicial, de distribuição (alfa), dura aproximadamente 8 a 12 horas e é a que mantém concentrações acima do limiar analgésico. A fase terminal de eliminação (beta) é muito prolongada e variável entre indivíduos, situando-se com frequência entre 30 e 60 horas; ela mantém concentrações suficientes para &lt;strong&gt;suprimir a abstinência&lt;/strong&gt;, mas insuficientes para produzir analgesia.&lt;/p&gt;&lt;p&gt;Daí a regra prática que confunde muitos residentes: para &lt;em&gt;manutenção na dependência&lt;/em&gt;, dose única diária basta; para &lt;em&gt;analgesia&lt;/em&gt;, o intervalo precisa ser de 6 a 8 horas. A dissociação entre meia-vida longa e duração analgésica curta é também a razão do risco de acúmulo e depressão respiratória tardia quando a dose é escalonada rapidamente nos primeiros dias; o estado de equilíbrio pode levar de 5 a 7 dias.&lt;/p&gt;&lt;p&gt;A metadona ainda soma antagonismo NMDA e inibição da recaptação de monoaminas, o que a torna útil na dor neuropática, e prolonga o intervalo QT de modo dose-dependente. Sua razão de conversão com a morfina não é linear: quanto maior a dose prévia de morfina, maior a potência relativa da metadona.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a biodisponibilidade oral da metadona é alta, em torno de 70% a 90%. (B) a meia-vida terminal é longa e bastante variável, e a metadona não depende de metabólitos ativos. (C) a ligação ao receptor mu é reversível e competitiva, sem qualquer dependência de síntese de novos receptores.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A morfina sofre extenso metabolismo de primeira passagem hepática, com biodisponibilidade oral em torno de 30%. Por isso, no uso &lt;strong&gt;crônico&lt;/strong&gt;, a razão equianalgésica consagrada entre a via oral e a venosa é de aproximadamente &lt;strong&gt;3:1&lt;/strong&gt; — 30 mg por via oral equivalem a cerca de 10 mg por via parenteral. Em dose única em paciente virgem de opioide, essa razão se aproxima de 6:1, mas a regra de 3:1 é a que se aplica ao paciente já em uso regular, como o do caso.&lt;/p&gt;&lt;p&gt;Aplicando a conversão: 30 mg por via venosa em 24 horas correspondem a cerca de &lt;strong&gt;90 mg por via oral&lt;/strong&gt; ao dia. Fracionando a morfina de liberação imediata a cada 4 horas, chega-se a 15 mg por dose. Na prática, prescreve-se ainda uma dose de resgate equivalente a cerca de 10% a 15% da dose diária total, disponível a cada 1 a 2 horas conforme a necessidade.&lt;/p&gt;&lt;p&gt;Vale lembrar que a redução de 25% a 50% por &lt;em&gt;tolerância cruzada incompleta&lt;/em&gt; se aplica quando se troca de molécula (rotação de opioide), e não quando apenas se muda a via de administração do mesmo fármaco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) mantém a mesma dose numérica ao mudar de via, ignorando a primeira passagem hepática e subdosando gravemente a paciente. (B) usa razão 2:1, insuficiente para a morfina em uso crônico. (D) usa razão 6:1, apropriada apenas para dose única em paciente sem exposição prévia, e resultaria em risco de sedação e depressão respiratória.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A morfina sofre extenso metabolismo de primeira passagem hepática, com biodisponibilidade oral em torno de 30%. Por isso, no uso &lt;strong&gt;crônico&lt;/strong&gt;, a razão equianalgésica consagrada entre a via oral e a venosa é de aproximadamente &lt;strong&gt;3:1&lt;/strong&gt;, ou seja, 30 mg por via oral equivalem a cerca de 10 mg por via parenteral. Em dose única em paciente virgem de opioide, essa razão se aproxima de 6:1, mas a regra de 3:1 é a que se aplica ao paciente já em uso regular, como o do caso.&lt;/p&gt;&lt;p&gt;Aplicando a conversão: 30 mg por via venosa em 24 horas correspondem a cerca de &lt;strong&gt;90 mg por via oral&lt;/strong&gt; ao dia. Fracionando a morfina de liberação imediata a cada 4 horas, chega-se a 15 mg por dose. Na prática, prescreve-se ainda uma dose de resgate equivalente a cerca de 10% a 15% da dose diária total, disponível a cada 1 a 2 horas conforme a necessidade.&lt;/p&gt;&lt;p&gt;Vale lembrar que a redução de 25% a 50% por &lt;em&gt;tolerância cruzada incompleta&lt;/em&gt; se aplica quando se troca de molécula (rotação de opioide), e não quando apenas se muda a via de administração do mesmo fármaco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) mantém a mesma dose numérica ao mudar de via, ignorando a primeira passagem hepática e subdosando gravemente a paciente. (B) usa razão 2:1, insuficiente para a morfina em uso crônico. (D) usa razão 6:1, apropriada apenas para dose única em paciente sem exposição prévia, e resultaria em risco de sedação e depressão respiratória.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A doutrina de Monro-Kellie estabelece que o crânio é uma caixa rígida cujo conteúdo — parênquima (cerca de 80% do volume), sangue (cerca de 10%) e líquor (cerca de 10%) — é praticamente incompressível. Qualquer aumento no volume de um componente, ou o acréscimo de um quarto compartimento como um tumor, um hematoma ou edema, precisa ser compensado pela redução de outro.&lt;/p&gt;&lt;p&gt;Os mecanismos compensatórios disponíveis são a &lt;strong&gt;translocação de líquor&lt;/strong&gt; para o espaço subaracnóideo espinhal com aumento da absorção, e a &lt;strong&gt;redução do volume sanguíneo cerebral&lt;/strong&gt;, sobretudo venoso. Enquanto estão operantes, o volume cresce com pouca variação de pressão — é a porção horizontal da curva, que explica por que o paciente conviveu meses com pressão intracraniana de 12 mmHg apesar de uma lesão volumosa.&lt;/p&gt;&lt;p&gt;Quando esses mecanismos se esgotam, a curva torna-se &lt;strong&gt;exponencial&lt;/strong&gt;: a complacência despenca e incrementos mínimos de volume produzem elevações abruptas de pressão, como ocorreu na indução. A tríade de Cushing — hipertensão, bradicardia e alteração respiratória — sinaliza descompensação iminente e risco de herniação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a relação é claramente não linear, e supor linearidade leva a subestimar o risco em pacientes aparentemente compensados. (C) o parênquima é o compartimento menos deslocável; a compensação inicial cabe ao líquor e ao sangue venoso. (D) a complacência &lt;em&gt;diminui&lt;/em&gt; progressivamente com o crescimento da lesão, e é justamente essa queda que caracteriza o joelho da curva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A doutrina de Monro-Kellie estabelece que o crânio é uma caixa rígida cujo conteúdo, formado por parênquima (cerca de 80% do volume), sangue (cerca de 10%) e líquor (cerca de 10%), é praticamente incompressível. Qualquer aumento no volume de um componente, ou o acréscimo de um quarto compartimento como um tumor, um hematoma ou edema, precisa ser compensado pela redução de outro.&lt;/p&gt;&lt;p&gt;Os mecanismos compensatórios disponíveis são a &lt;strong&gt;translocação de líquor&lt;/strong&gt; para o espaço subaracnóideo espinhal com aumento da absorção, e a &lt;strong&gt;redução do volume sanguíneo cerebral&lt;/strong&gt;, sobretudo venoso. Enquanto estão operantes, o volume cresce com pouca variação de pressão; é a porção horizontal da curva, que explica por que o paciente conviveu meses com pressão intracraniana de 12 mmHg apesar de uma lesão volumosa.&lt;/p&gt;&lt;p&gt;Quando esses mecanismos se esgotam, a curva torna-se &lt;strong&gt;exponencial&lt;/strong&gt;: a complacência despenca e incrementos mínimos de volume produzem elevações abruptas de pressão, como ocorreu na indução. A tríade de Cushing (hipertensão, bradicardia e alteração respiratória) sinaliza descompensação iminente e risco de herniação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a relação é claramente não linear, e supor linearidade leva a subestimar o risco em pacientes aparentemente compensados. (C) o parênquima é o compartimento menos deslocável; a compensação inicial cabe ao líquor e ao sangue venoso. (D) a complacência &lt;em&gt;diminui&lt;/em&gt; progressivamente com o crescimento da lesão, e é justamente essa queda que caracteriza o joelho da curva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A vasculatura cerebral é intensamente sensível à PaCO2: dentro da faixa aproximada de 20 a 80 mmHg, o fluxo sanguíneo cerebral varia cerca de &lt;strong&gt;1 a 2 mL/100 g/min para cada mmHg&lt;/strong&gt; de variação da PaCO2. A hipocapnia produz alcalose no líquido extracelular perivascular, vasoconstrição arteriolar, queda do &lt;strong&gt;volume sanguíneo cerebral&lt;/strong&gt; e, por consequência, redução da pressão intracraniana — efeito que se instala em minutos.&lt;/p&gt;&lt;p&gt;Esse benefício, porém, é &lt;strong&gt;temporário e arriscado&lt;/strong&gt;. Em 6 a 24 horas o bicarbonato liquórico se ajusta e o efeito se dissipa. Mais grave: como o cérebro traumatizado pode ter fluxo já reduzido, a vasoconstrição adicional pode precipitar isquemia. Por isso a hiperventilação é hoje reservada como &lt;strong&gt;medida de resgate&lt;/strong&gt; para deterioração aguda ou sinais de herniação, com alvo de PaCO2 entre 30 e 35 mmHg, pelo menor tempo possível e, quando prolongada, sob monitorização da oxigenação cerebral. Deve-se evitar hipocapnia profunda, sobretudo nas primeiras 24 horas do trauma.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipercapnia é vasodilatadora e &lt;em&gt;elevaria&lt;/em&gt; ainda mais a pressão intracraniana, sendo deletéria neste cenário. (C) PaCO2 próxima de 20 mmHg provoca vasoconstrição intensa com risco real de isquemia, e a manutenção por 48 horas não se sustenta pela adaptação liquórica. (D) a hiperóxia tem efeito vasoconstritor cerebral apenas discreto e não substitui o controle da PaCO2 como manobra para reduzir a pressão intracraniana.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A vasculatura cerebral é intensamente sensível à PaCO2: dentro da faixa aproximada de 20 a 80 mmHg, o fluxo sanguíneo cerebral varia cerca de &lt;strong&gt;1 a 2 mL/100 g/min para cada mmHg&lt;/strong&gt; de variação da PaCO2. A hipocapnia produz alcalose no líquido extracelular perivascular, vasoconstrição arteriolar, queda do &lt;strong&gt;volume sanguíneo cerebral&lt;/strong&gt; e, por consequência, redução da pressão intracraniana, efeito que se instala em minutos.&lt;/p&gt;&lt;p&gt;Esse benefício, porém, é &lt;strong&gt;temporário e arriscado&lt;/strong&gt;. Em 6 a 24 horas o bicarbonato liquórico se ajusta e o efeito se dissipa. Mais grave: como o cérebro traumatizado pode ter fluxo já reduzido, a vasoconstrição adicional pode precipitar isquemia. Por isso a hiperventilação é hoje reservada como &lt;strong&gt;medida de resgate&lt;/strong&gt; para deterioração aguda ou sinais de herniação, com alvo de PaCO2 entre 30 e 35 mmHg, pelo menor tempo possível e, quando prolongada, sob monitorização da oxigenação cerebral. Deve-se evitar hipocapnia profunda, sobretudo nas primeiras 24 horas do trauma.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipercapnia é vasodilatadora e &lt;em&gt;elevaria&lt;/em&gt; ainda mais a pressão intracraniana, sendo deletéria neste cenário. (C) PaCO2 próxima de 20 mmHg provoca vasoconstrição intensa com risco real de isquemia, e a manutenção por 48 horas não se sustenta pela adaptação liquórica. (D) a hiperóxia tem efeito vasoconstritor cerebral apenas discreto e não substitui o controle da PaCO2 como manobra para reduzir a pressão intracraniana.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pressão de perfusão cerebral é calculada como &lt;strong&gt;PPC = PAM − PIC&lt;/strong&gt; (ou menos a pressão venosa central, quando esta for maior que a pressão intracraniana). A pressão arterial média estimada é PAM = (PAS + 2 × PAD) / 3, ou seja, (110 + 130) / 3 = &lt;strong&gt;80 mmHg&lt;/strong&gt;. Logo, PPC = 80 − 25 = &lt;strong&gt;55 mmHg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Esse valor está &lt;strong&gt;abaixo&lt;/strong&gt; do alvo habitualmente perseguido, situado em torno de 60 a 70 mmHg, faixa que evita tanto a isquemia por hipoperfusão quanto a hiperemia e a sobrecarga hídrica associadas a alvos exageradamente altos. Em paciente com hemorragia subaracnóidea no quinto dia — plena janela de vasoespasmo —, tolerar PPC baixa é particularmente perigoso.&lt;/p&gt;&lt;p&gt;A correção atua nos dois termos da equação:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Elevar a PAM&lt;/strong&gt; com volume adequado e vasopressor, tipicamente noradrenalina.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reduzir a PIC&lt;/strong&gt; — nesta paciente, a drenagem de líquor pela ventriculostomia já disponível é a manobra mais rápida e eficaz, somando-se a cabeceira elevada, sedação adequada e controle de temperatura.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Vale lembrar que o transdutor arterial deve ser zerado no nível do meato acústico externo, como descrito, para que a PPC não seja superestimada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o cálculo está errado e a conduta expectante é inaceitável com PPC abaixo do alvo. (B) o valor de 85 mmHg resultaria de usar a pressão sistólica no lugar da média, erro frequente. (D) acerta o cálculo mas inverte a conduta: reduzir a PAM agravaria a hipoperfusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pressão de perfusão cerebral é calculada como &lt;strong&gt;PPC = PAM − PIC&lt;/strong&gt; (ou menos a pressão venosa central, quando esta for maior que a pressão intracraniana). A pressão arterial média estimada é PAM = (PAS + 2 × PAD) / 3, ou seja, (110 + 130) / 3 = &lt;strong&gt;80 mmHg&lt;/strong&gt;. Logo, PPC = 80 − 25 = &lt;strong&gt;55 mmHg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Esse valor está &lt;strong&gt;abaixo&lt;/strong&gt; do alvo habitualmente perseguido, situado em torno de 60 a 70 mmHg, faixa que evita tanto a isquemia por hipoperfusão quanto a hiperemia e a sobrecarga hídrica associadas a alvos exageradamente altos. Em paciente com hemorragia subaracnóidea no quinto dia (plena janela de vasoespasmo), tolerar PPC baixa é particularmente perigoso.&lt;/p&gt;&lt;p&gt;A correção atua nos dois termos da equação:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Elevar a PAM&lt;/strong&gt; com volume adequado e vasopressor, tipicamente noradrenalina.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reduzir a PIC&lt;/strong&gt;: nesta paciente, a drenagem de líquor pela ventriculostomia já disponível é a manobra mais rápida e eficaz, somando-se a cabeceira elevada, sedação adequada e controle de temperatura.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Vale lembrar que o transdutor arterial deve ser zerado no nível do meato acústico externo, como descrito, para que a PPC não seja superestimada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o cálculo está errado e a conduta expectante é inaceitável com PPC abaixo do alvo. (B) o valor de 85 mmHg resultaria de usar a pressão sistólica no lugar da média, erro frequente. (D) acerta o cálculo mas inverte a conduta: reduzir a PAM agravaria a hipoperfusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Manitol e salina hipertônica reduzem a pressão intracraniana pelo mesmo princípio: criam um gradiente osmótico através de uma barreira hematoencefálica íntegra e retiram água do parênquima. A diferença decisiva está no &lt;strong&gt;efeito volêmico&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;manitol&lt;/strong&gt; (0,25 a 1 g/kg) provoca expansão plasmática transitória seguida de &lt;strong&gt;diurese osmótica&lt;/strong&gt; intensa, que pode agravar a hipovolemia e a hipotensão. Em um politraumatizado em choque hemorrágico, como o do caso, isso significa risco de queda adicional da pressão arterial média e, portanto, da pressão de perfusão cerebral — exatamente o que se quer evitar diante de sinais de herniação. Exige ainda vigilância da osmolaridade sérica, mantida abaixo de cerca de 320 mOsm/L, e da função renal.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;salina hipertônica&lt;/strong&gt; reduz a pressão intracraniana e simultaneamente &lt;strong&gt;expande o intravascular&lt;/strong&gt;, sustentando a pressão arterial. É por isso a escolha preferencial no paciente hipotenso ou hipovolêmico. Requer controle seriado do sódio e da osmolaridade e, em concentrações altas, acesso venoso central.&lt;/p&gt;&lt;p&gt;Nenhuma das duas substitui o tratamento definitivo: drenagem cirúrgica imediata do hematoma.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o manitol pode ser útil, mas neste paciente hipotenso a diurese osmótica compromete a perfusão cerebral. (B) a furosemida isolada é adjuvante fraca e piora a hipovolemia. (C) restringir volume em paciente em choque é deletério e contraria o objetivo de manter pressão de perfusão adequada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Manitol e salina hipertônica reduzem a pressão intracraniana pelo mesmo princípio: criam um gradiente osmótico através de uma barreira hematoencefálica íntegra e retiram água do parênquima. A diferença decisiva está no &lt;strong&gt;efeito volêmico&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;manitol&lt;/strong&gt; (0,25 a 1 g/kg) provoca expansão plasmática transitória seguida de &lt;strong&gt;diurese osmótica&lt;/strong&gt; intensa, que pode agravar a hipovolemia e a hipotensão. Em um politraumatizado em choque hemorrágico, como o do caso, isso significa risco de queda adicional da pressão arterial média e, portanto, da pressão de perfusão cerebral, exatamente o que se quer evitar diante de sinais de herniação. Exige ainda vigilância da osmolaridade sérica, mantida abaixo de cerca de 320 mOsm/L, e da função renal.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;salina hipertônica&lt;/strong&gt; reduz a pressão intracraniana e simultaneamente &lt;strong&gt;expande o intravascular&lt;/strong&gt;, sustentando a pressão arterial. É por isso a escolha preferencial no paciente hipotenso ou hipovolêmico. Requer controle seriado do sódio e da osmolaridade e, em concentrações altas, acesso venoso central.&lt;/p&gt;&lt;p&gt;Nenhuma das duas substitui o tratamento definitivo: drenagem cirúrgica imediata do hematoma.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o manitol pode ser útil, mas neste paciente hipotenso a diurese osmótica compromete a perfusão cerebral. (B) a furosemida isolada é adjuvante fraca e piora a hipovolemia. (C) restringir volume em paciente em choque é deletério e contraria o objetivo de manter pressão de perfusão adequada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O óxido nitroso é cerca de 34 vezes mais solúvel no sangue que o nitrogênio. Por isso, difunde-se para dentro de qualquer &lt;strong&gt;cavidade aérea fechada&lt;/strong&gt; muito mais rápido do que o nitrogênio consegue sair, aumentando seu volume — ou, quando as paredes são rígidas, sua pressão.&lt;/p&gt;&lt;p&gt;Em craniotomia, sobretudo em posição sentada ou semissentada, o líquor drenado é substituído por ar, e uma coleção intracraniana de ar é a regra ao final do procedimento. Enquanto a dura está aberta, esse ar tem para onde escapar. Uma vez &lt;strong&gt;fechada a dura-máter&lt;/strong&gt;, a cavidade torna-se fechada e a manutenção do óxido nitroso converte um pneumoencéfalo simples em &lt;strong&gt;pneumoencéfalo hipertensivo&lt;/strong&gt;, com efeito de massa, elevação da pressão intracraniana e a resposta de Cushing descrita — hipertensão e bradicardia — além de despertar tardio e déficit neurológico no pós-operatório.&lt;/p&gt;&lt;p&gt;A conduta preventiva consiste em &lt;strong&gt;suspender o óxido nitroso antes do fechamento dural&lt;/strong&gt;, com margem de tempo para sua eliminação, e ventilar com oxigênio e ar. Instalado o quadro, a suspensão imediata é o primeiro passo, podendo ser necessária a descompressão cirúrgica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) manter o óxido nitroso perpetua a causa, e o sevoflurano em concentração alta é vasodilatador cerebral, o que piora a situação. (C) a hipertensão é aqui um sinal &lt;em&gt;reflexo&lt;/em&gt; de hipertensão intracraniana, e reduzi-la farmacologicamente compromete a pressão de perfusão cerebral. (D) tratar a bradicardia isoladamente mascara a resposta de Cushing sem corrigir o mecanismo subjacente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O óxido nitroso é cerca de 34 vezes mais solúvel no sangue que o nitrogênio. Por isso, difunde-se para dentro de qualquer &lt;strong&gt;cavidade aérea fechada&lt;/strong&gt; muito mais rápido do que o nitrogênio consegue sair, aumentando seu volume ou, quando as paredes são rígidas, sua pressão.&lt;/p&gt;&lt;p&gt;Em craniotomia, sobretudo em posição sentada ou semissentada, o líquor drenado é substituído por ar, e uma coleção intracraniana de ar é a regra ao final do procedimento. Enquanto a dura está aberta, esse ar tem para onde escapar. Uma vez &lt;strong&gt;fechada a dura-máter&lt;/strong&gt;, a cavidade torna-se fechada e a manutenção do óxido nitroso converte um pneumoencéfalo simples em &lt;strong&gt;pneumoencéfalo hipertensivo&lt;/strong&gt;, com efeito de massa, elevação da pressão intracraniana e a resposta de Cushing descrita (hipertensão e bradicardia), além de despertar tardio e déficit neurológico no pós-operatório.&lt;/p&gt;&lt;p&gt;A conduta preventiva consiste em &lt;strong&gt;suspender o óxido nitroso antes do fechamento dural&lt;/strong&gt;, com margem de tempo para sua eliminação, e ventilar com oxigênio e ar. Instalado o quadro, a suspensão imediata é o primeiro passo, podendo ser necessária a descompressão cirúrgica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) manter o óxido nitroso perpetua a causa, e o sevoflurano em concentração alta é vasodilatador cerebral, o que piora a situação. (C) a hipertensão é aqui um sinal &lt;em&gt;reflexo&lt;/em&gt; de hipertensão intracraniana, e reduzi-la farmacologicamente compromete a pressão de perfusão cerebral. (D) tratar a bradicardia isoladamente mascara a resposta de Cushing sem corrigir o mecanismo subjacente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O vasoespasmo cerebral é a principal causa de morbidade tardia após hemorragia subaracnóidea aneurismática e a hipótese obrigatória diante de déficit neurológico novo dentro de sua janela temporal. Essa janela vai aproximadamente do &lt;strong&gt;quarto ao décimo quarto dia&lt;/strong&gt;, com pico entre o sexto e o oitavo — exatamente onde se encontra a paciente. O risco correlaciona-se com a quantidade de sangue cisternal.&lt;/p&gt;&lt;p&gt;O quadro clínico é de deterioração subaguda, com rebaixamento e déficit focal, após exclusão de ressangramento, hidrocefalia, crise convulsiva, hiponatremia, hipóxia e infecção. O Doppler transcraniano auxilia no rastreamento, e a angiotomografia ou a angiografia confirmam.&lt;/p&gt;&lt;p&gt;O manejo se organiza em camadas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Nimodipino&lt;/strong&gt; por via oral, 60 mg a cada 4 horas por 21 dias, iniciado precocemente — melhora o desfecho neurológico e não deve ser suspenso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Euvolemia&lt;/strong&gt; e &lt;strong&gt;hipertensão induzida&lt;/strong&gt; com vasopressor, uma vez que o aneurisma já está tratado. A antiga tríade com hemodiluição foi abandonada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Terapia endovascular&lt;/strong&gt; nos casos refratários: angioplastia com balão no vasoespasmo proximal e vasodilatador intra-arterial no distal.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o ressangramento tem pico nas primeiras 24 a 48 horas, cursa com piora súbita e sangue novo na tomografia, ausente aqui. (B) a hidrocefalia foi descartada pela imagem, e suspender o nimodipino é sempre inadequado. (D) o quadro não sugere estado epiléptico, e a retirada do nimodipino agravaria o risco de isquemia tardia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O vasoespasmo cerebral é a principal causa de morbidade tardia após hemorragia subaracnóidea aneurismática e a hipótese obrigatória diante de déficit neurológico novo dentro de sua janela temporal. Essa janela vai aproximadamente do &lt;strong&gt;quarto ao décimo quarto dia&lt;/strong&gt;, com pico entre o sexto e o oitavo, exatamente onde se encontra a paciente. O risco correlaciona-se com a quantidade de sangue cisternal.&lt;/p&gt;&lt;p&gt;O quadro clínico é de deterioração subaguda, com rebaixamento e déficit focal, após exclusão de ressangramento, hidrocefalia, crise convulsiva, hiponatremia, hipóxia e infecção. O Doppler transcraniano auxilia no rastreamento, e a angiotomografia ou a angiografia confirmam.&lt;/p&gt;&lt;p&gt;O manejo se organiza em camadas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Nimodipino&lt;/strong&gt; por via oral, 60 mg a cada 4 horas por 21 dias, iniciado precocemente; melhora o desfecho neurológico e não deve ser suspenso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Euvolemia&lt;/strong&gt; e &lt;strong&gt;hipertensão induzida&lt;/strong&gt; com vasopressor, uma vez que o aneurisma já está tratado. A antiga tríade com hemodiluição foi abandonada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Terapia endovascular&lt;/strong&gt; nos casos refratários: angioplastia com balão no vasoespasmo proximal e vasodilatador intra-arterial no distal.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o ressangramento tem pico nas primeiras 24 a 48 horas, cursa com piora súbita e sangue novo na tomografia, ausente aqui. (B) a hidrocefalia foi descartada pela imagem, e suspender o nimodipino é sempre inadequado. (D) o quadro não sugere estado epiléptico, e a retirada do nimodipino agravaria o risco de isquemia tardia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hiponatremia é frequente após hemorragia subaracnóidea e sua interpretação correta é decisiva, porque as duas causas principais exigem condutas &lt;strong&gt;opostas&lt;/strong&gt;. A chave para distingui-las é o &lt;strong&gt;estado volêmico&lt;/strong&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Na &lt;strong&gt;síndrome cerebral perdedora de sal&lt;/strong&gt;, há natriurese primária, provavelmente mediada por peptídeos natriuréticos, com perda obrigatória de água. O paciente fica &lt;strong&gt;hipovolêmico&lt;/strong&gt;: balanço negativo, perda de peso, poliúria, pressão venosa central baixa, mucosas secas, taquicardia — o quadro descrito.&lt;/li&gt;&lt;li&gt;Na &lt;strong&gt;secreção inapropriada de hormônio antidiurético&lt;/strong&gt;, há retenção de água livre e o paciente está &lt;strong&gt;euvolêmico ou levemente hipervolêmico&lt;/strong&gt;, sem sinais de depleção.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambos o sódio urinário e a osmolalidade urinária estão altos, o que torna esses exames pouco discriminativos isoladamente.&lt;/p&gt;&lt;p&gt;Neste paciente, a conduta é &lt;strong&gt;reposição de volume e de sódio&lt;/strong&gt;, com solução isotônica ou hipertônica conforme a gravidade, e correção gradual para evitar desmielinização osmótica. A fludrocortisona pode ser adjuvante. A restrição hídrica é formalmente indesejável na hemorragia subaracnóidea, pois a hipovolemia aumenta o risco de isquemia cerebral tardia associada ao vasoespasmo, especialmente no sexto dia de evolução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o diagnóstico exige euvolemia, ausente aqui, e a restrição seria perigosa. (B) o diabetes insípido cursa com hipernatremia e urina diluída, o oposto do encontrado. (C) a hiponatremia dilucional não explica a hipovolemia nem a natriurese, e a conduta expectante deixaria o sódio em nível de risco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hiponatremia é frequente após hemorragia subaracnóidea e sua interpretação correta é decisiva, porque as duas causas principais exigem condutas &lt;strong&gt;opostas&lt;/strong&gt;. A chave para distingui-las é o &lt;strong&gt;estado volêmico&lt;/strong&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Na &lt;strong&gt;síndrome cerebral perdedora de sal&lt;/strong&gt;, há natriurese primária, provavelmente mediada por peptídeos natriuréticos, com perda obrigatória de água. O paciente fica &lt;strong&gt;hipovolêmico&lt;/strong&gt;: balanço negativo, perda de peso, poliúria, pressão venosa central baixa, mucosas secas, taquicardia; exatamente o quadro descrito.&lt;/li&gt;&lt;li&gt;Na &lt;strong&gt;secreção inapropriada de hormônio antidiurético&lt;/strong&gt;, há retenção de água livre e o paciente está &lt;strong&gt;euvolêmico ou levemente hipervolêmico&lt;/strong&gt;, sem sinais de depleção.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambos o sódio urinário e a osmolalidade urinária estão altos, o que torna esses exames pouco discriminativos isoladamente.&lt;/p&gt;&lt;p&gt;Neste paciente, a conduta é &lt;strong&gt;reposição de volume e de sódio&lt;/strong&gt;, com solução isotônica ou hipertônica conforme a gravidade, e correção gradual para evitar desmielinização osmótica. A fludrocortisona pode ser adjuvante. A restrição hídrica é formalmente indesejável na hemorragia subaracnóidea, pois a hipovolemia aumenta o risco de isquemia cerebral tardia associada ao vasoespasmo, especialmente no sexto dia de evolução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o diagnóstico exige euvolemia, ausente aqui, e a restrição seria perigosa. (B) o diabetes insípido cursa com hipernatremia e urina diluída, o oposto do encontrado. (C) a hiponatremia dilucional não explica a hipovolemia nem a natriurese, e a conduta expectante deixaria o sódio em nível de risco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os receptores adrenérgicos e muscarínicos pertencem à família acoplada a proteína G, e cada subtipo tem uma via de sinalização característica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Alfa-1&lt;/strong&gt;: proteína Gq, ativação da fosfolipase C, geração de inositol trifosfato e diacilglicerol, liberação de cálcio do retículo sarcoplasmático — vasoconstrição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Alfa-2&lt;/strong&gt;: proteína Gi, inibição da adenilato ciclase e queda do AMP cíclico. Nos terminais pré-sinápticos noradrenérgicos, funciona como autorreceptor inibitório, reduzindo a liberação de noradrenalina; no locus ceruleus, medeia sedação, e na medula, analgesia. É o mecanismo da clonidina e da dexmedetomidina, e explica a bradicardia e a hipotensão observadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Beta-1 e beta-2&lt;/strong&gt;: proteína Gs, aumento do AMP cíclico e ativação da proteinoquinase A.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;M2&lt;/strong&gt; (nó sinusal e átrio): proteína Gi, com redução do AMP cíclico e abertura de canais de potássio, produzindo bradicardia; &lt;strong&gt;M3&lt;/strong&gt; usa via Gq.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A ação da noradrenalina liberada é encerrada principalmente pela &lt;strong&gt;recaptação neuronal&lt;/strong&gt;, responsável por cerca de 80% do término do efeito; a degradação por monoaminoxidase e catecol-O-metiltransferase é quantitativamente secundária e gera metabólitos como as metanefrinas e o ácido vanilmandélico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alfa-1 é acoplado a Gq, não a Gs. (C) o beta-1 sinaliza via Gs e AMP cíclico, não pela fosfolipase C. (D) o M2 acopla-se a Gi e &lt;em&gt;reduz&lt;/em&gt; o AMP cíclico; a proteína citada está trocada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os receptores adrenérgicos e muscarínicos pertencem à família acoplada a proteína G, e cada subtipo tem uma via de sinalização característica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Alfa-1&lt;/strong&gt;: proteína Gq, ativação da fosfolipase C, geração de inositol trifosfato e diacilglicerol, liberação de cálcio do retículo sarcoplasmático e, ao final, vasoconstrição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Alfa-2&lt;/strong&gt;: proteína Gi, inibição da adenilato ciclase e queda do AMP cíclico. Nos terminais pré-sinápticos noradrenérgicos, funciona como autorreceptor inibitório, reduzindo a liberação de noradrenalina; no locus ceruleus, medeia sedação, e na medula, analgesia. É o mecanismo da clonidina e da dexmedetomidina, e explica a bradicardia e a hipotensão observadas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Beta-1 e beta-2&lt;/strong&gt;: proteína Gs, aumento do AMP cíclico e ativação da proteinoquinase A.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;M2&lt;/strong&gt; (nó sinusal e átrio): proteína Gi, com redução do AMP cíclico e abertura de canais de potássio, produzindo bradicardia; &lt;strong&gt;M3&lt;/strong&gt; usa via Gq.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A ação da noradrenalina liberada é encerrada principalmente pela &lt;strong&gt;recaptação neuronal&lt;/strong&gt;, responsável por cerca de 80% do término do efeito; a degradação por monoaminoxidase e catecol-O-metiltransferase é quantitativamente secundária e gera metabólitos como as metanefrinas e o ácido vanilmandélico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alfa-1 é acoplado a Gq, não a Gs. (C) o beta-1 sinaliza via Gs e AMP cíclico, não pela fosfolipase C. (D) o M2 acopla-se a Gi e &lt;em&gt;reduz&lt;/em&gt; o AMP cíclico; a proteína citada está trocada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O líquido cefalorraquidiano é produzido sobretudo pelos &lt;strong&gt;plexos coroides&lt;/strong&gt; dos ventrículos, com contribuição menor do epêndima e do espaço extracelular cerebral. A taxa de formação é de aproximadamente &lt;strong&gt;0,3 a 0,4 mL/min&lt;/strong&gt;, ou seja, cerca de 500 mL por dia — cerca de 21 mL por hora. Como o volume total circulante é de apenas &lt;strong&gt;100 a 150 mL&lt;/strong&gt; no adulto (dos quais em torno de 25 a 35 mL no espaço subaracnóideo espinhal), o líquor é integralmente renovado três a quatro vezes ao dia.&lt;/p&gt;&lt;p&gt;A circulação segue dos ventrículos laterais pelos forames interventriculares ao terceiro ventrículo, pelo aqueduto cerebral ao quarto ventrículo, e daí ao espaço subaracnóideo pelos forames de Luschka e Magendie. A absorção ocorre principalmente nas &lt;strong&gt;granulações aracnóideas&lt;/strong&gt; dos seios venosos durais, por um mecanismo dependente do gradiente de pressão entre o líquor e o seio venoso.&lt;/p&gt;&lt;p&gt;A produção é relativamente insensível à pressão intracraniana, ao passo que a absorção aumenta com ela — assimetria que explica por que a hipertensão intracraniana não se resolve espontaneamente e por que a drenagem por ventriculostomia é medida tão eficaz. Acetazolamida e furosemida reduzem discretamente a produção.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde valores: 1,5 mL/min e 500 mL de volume superestimam grosseiramente ambos os parâmetros. (B) inverte os papéis do plexo coroide, que produz, e das granulações aracnóideas, que absorvem. (D) a produção é praticamente independente da pressão intracraniana, e é justamente essa característica que agrava a hidrocefalia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O líquido cefalorraquidiano é produzido sobretudo pelos &lt;strong&gt;plexos coroides&lt;/strong&gt; dos ventrículos, com contribuição menor do epêndima e do espaço extracelular cerebral. A taxa de formação é de aproximadamente &lt;strong&gt;0,3 a 0,4 mL/min&lt;/strong&gt;, ou seja, cerca de 500 mL por dia, o que corresponde a cerca de 21 mL por hora. Como o volume total circulante é de apenas &lt;strong&gt;100 a 150 mL&lt;/strong&gt; no adulto (dos quais em torno de 25 a 35 mL no espaço subaracnóideo espinhal), o líquor é integralmente renovado três a quatro vezes ao dia.&lt;/p&gt;&lt;p&gt;A circulação segue dos ventrículos laterais pelos forames interventriculares ao terceiro ventrículo, pelo aqueduto cerebral ao quarto ventrículo, e daí ao espaço subaracnóideo pelos forames de Luschka e Magendie. A absorção ocorre principalmente nas &lt;strong&gt;granulações aracnóideas&lt;/strong&gt; dos seios venosos durais, por um mecanismo dependente do gradiente de pressão entre o líquor e o seio venoso.&lt;/p&gt;&lt;p&gt;A produção é relativamente insensível à pressão intracraniana, ao passo que a absorção aumenta com ela. Essa assimetria explica por que a hipertensão intracraniana não se resolve espontaneamente e por que a drenagem por ventriculostomia é medida tão eficaz. Acetazolamida e furosemida reduzem discretamente a produção.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde valores: 1,5 mL/min e 500 mL de volume superestimam grosseiramente ambos os parâmetros. (B) inverte os papéis do plexo coroide, que produz, e das granulações aracnóideas, que absorvem. (D) a produção é praticamente independente da pressão intracraniana, e é justamente essa característica que agrava a hidrocefalia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A síndrome anticolinérgica central decorre do bloqueio de receptores muscarínicos no sistema nervoso central por fármacos que atravessam a barreira hematoencefálica. Entre os anticolinérgicos usados em anestesia, atropina e sobretudo &lt;strong&gt;escopolamina&lt;/strong&gt; são &lt;strong&gt;aminas terciárias&lt;/strong&gt;, lipossolúveis e capazes de atingir o encéfalo; o &lt;strong&gt;glicopirrolato&lt;/strong&gt; é uma amina quaternária, carregada, que praticamente não atravessa a barreira e por isso não causa a síndrome. Idosos são particularmente suscetíveis.&lt;/p&gt;&lt;p&gt;O quadro combina manifestações centrais — agitação, desorientação, alucinações, delirium, podendo chegar a sedação e coma — com sinais periféricos de bloqueio muscarínico: midríase, pele seca e quente, taquicardia, retenção urinária e íleo. O diagnóstico é de exclusão, feito depois de afastar hipoxemia, hipercapnia, hipoglicemia, distúrbio eletrolítico, dor e sedativos residuais, como no caso descrito.&lt;/p&gt;&lt;p&gt;O tratamento específico é a &lt;strong&gt;fisostigmina&lt;/strong&gt;, único anticolinesterásico de uso clínico que é amina terciária e portanto age no sistema nervoso central, em doses tituladas da ordem de 0,01 a 0,03 mg/kg. Deve-se ter atropina disponível, pelo risco de bradicardia, broncoespasmo e convulsões.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neostigmina é amina quaternária e não atinge o sistema nervoso central, sendo inútil para o componente central. (B) o glicopirrolato é anticolinérgico, não anticolinesterásico, e agravaria o quadro. (C) o flumazenil só faz sentido diante de exposição a benzodiazepínico, ausente nesta paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A síndrome anticolinérgica central decorre do bloqueio de receptores muscarínicos no sistema nervoso central por fármacos que atravessam a barreira hematoencefálica. Entre os anticolinérgicos usados em anestesia, atropina e sobretudo &lt;strong&gt;escopolamina&lt;/strong&gt; são &lt;strong&gt;aminas terciárias&lt;/strong&gt;, lipossolúveis e capazes de atingir o encéfalo; o &lt;strong&gt;glicopirrolato&lt;/strong&gt; é uma amina quaternária, carregada, que praticamente não atravessa a barreira e por isso não causa a síndrome. Idosos são particularmente suscetíveis.&lt;/p&gt;&lt;p&gt;O quadro combina manifestações centrais (agitação, desorientação, alucinações, delirium, podendo chegar a sedação e coma) com sinais periféricos de bloqueio muscarínico: midríase, pele seca e quente, taquicardia, retenção urinária e íleo. O diagnóstico é de exclusão, feito depois de afastar hipoxemia, hipercapnia, hipoglicemia, distúrbio eletrolítico, dor e sedativos residuais, como no caso descrito.&lt;/p&gt;&lt;p&gt;O tratamento específico é a &lt;strong&gt;fisostigmina&lt;/strong&gt;, único anticolinesterásico de uso clínico que é amina terciária e portanto age no sistema nervoso central, em doses tituladas da ordem de 0,01 a 0,03 mg/kg. Deve-se ter atropina disponível, pelo risco de bradicardia, broncoespasmo e convulsões.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neostigmina é amina quaternária e não atinge o sistema nervoso central, sendo inútil para o componente central. (B) o glicopirrolato é anticolinérgico, não anticolinesterásico, e agravaria o quadro. (C) o flumazenil só faz sentido diante de exposição a benzodiazepínico, ausente nesta paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As complicações pulmonares pós-operatórias — atelectasia, pneumonia, insuficiência respiratória e broncoespasmo — são tão frequentes quanto as cardíacas e pesam de forma semelhante na morbimortalidade. Seus preditores dividem-se em &lt;strong&gt;relacionados ao paciente&lt;/strong&gt; e &lt;strong&gt;relacionados ao procedimento&lt;/strong&gt;, e são estes últimos que mostram a maior força de associação.&lt;/p&gt;&lt;p&gt;Entre os fatores cirúrgicos, destacam-se o &lt;strong&gt;sítio operatório&lt;/strong&gt; (quanto mais próximo do diafragma, maior o risco: torácica e abdominal alta lideram, seguidas de aorta e neurocirurgia) e a &lt;strong&gt;duração superior a três horas&lt;/strong&gt;. Ambos atuam pelo mesmo mecanismo: disfunção diafragmática, queda da capacidade residual funcional e tosse ineficaz. Do lado do paciente, contam idade avançada, doença pulmonar obstrutiva crônica, ASA maior que II, dependência funcional, insuficiência cardíaca, tabagismo ativo e hipoalbuminemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a obesidade, mesmo mórbida, é preditor fraco e inconsistente de complicação pulmonar, ao contrário do que a intuição sugere; (C) a hipertensão arterial controlada não figura como fator de risco pulmonar independente; (D) a idade é fator real, mas de magnitude modesta e claramente inferior à do sítio e da duração cirúrgica, sendo erro comum superestimá-la e usá-la para contraindicar procedimentos.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As complicações pulmonares pós-operatórias (atelectasia, pneumonia, insuficiência respiratória e broncoespasmo) são tão frequentes quanto as cardíacas e pesam de forma semelhante na morbimortalidade. Seus preditores dividem-se em &lt;strong&gt;relacionados ao paciente&lt;/strong&gt; e &lt;strong&gt;relacionados ao procedimento&lt;/strong&gt;, e são estes últimos que mostram a maior força de associação.&lt;/p&gt;&lt;p&gt;Entre os fatores cirúrgicos, destacam-se o &lt;strong&gt;sítio operatório&lt;/strong&gt; (quanto mais próximo do diafragma, maior o risco: torácica e abdominal alta lideram, seguidas de aorta e neurocirurgia) e a &lt;strong&gt;duração superior a três horas&lt;/strong&gt;. Ambos atuam pelo mesmo mecanismo: disfunção diafragmática, queda da capacidade residual funcional e tosse ineficaz. Do lado do paciente, contam idade avançada, doença pulmonar obstrutiva crônica, ASA maior que II, dependência funcional, insuficiência cardíaca, tabagismo ativo e hipoalbuminemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a obesidade, mesmo mórbida, é preditor fraco e inconsistente de complicação pulmonar, ao contrário do que a intuição sugere; (C) a hipertensão arterial controlada não figura como fator de risco pulmonar independente; (D) a idade é fator real, mas de magnitude modesta e claramente inferior à do sítio e da duração cirúrgica, sendo erro comum superestimá-la e usá-la para contraindicar procedimentos.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A gravidade da pneumonite química de aspiração depende sobretudo do &lt;strong&gt;pH&lt;/strong&gt; e do &lt;strong&gt;volume&lt;/strong&gt; aspirados, com risco maior quando o pH é inferior a 2,5. A profilaxia farmacológica ataca esses dois alvos por vias distintas, e a escolha depende do tempo disponível.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;antiácido não particulado&lt;/strong&gt;, como o citrato de sódio 0,3 M, é o único que neutraliza quimicamente o ácido &lt;em&gt;já secretado&lt;/em&gt;, com efeito em poucos minutos — por isso é o agente indicado quando a indução é iminente. Deve ser não particulado, pois antiácidos particulados como o hidróxido de alumínio produzem lesão pulmonar própria se aspirados. Antagonistas H&lt;sub&gt;2&lt;/sub&gt; e inibidores de bomba de prótons agem sobre a secreção futura e exigem antecedência, e a metoclopramida acelera o esvaziamento gástrico e eleva o tônus do esfíncter esofágico inferior sem alterar o pH.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ranitidina intravenosa precisa de aproximadamente 30 a 60 minutos para elevar o pH e nada faz com o ácido já presente; (B) os inibidores de bomba de prótons têm início ainda mais lento e efeito máximo em horas; (C) a metoclopramida não possui qualquer ação neutralizante, e sua utilidade é reduzir o volume gástrico residual, não a acidez.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A gravidade da pneumonite química de aspiração depende sobretudo do &lt;strong&gt;pH&lt;/strong&gt; e do &lt;strong&gt;volume&lt;/strong&gt; aspirados, com risco maior quando o pH é inferior a 2,5. A profilaxia farmacológica ataca esses dois alvos por vias distintas, e a escolha depende do tempo disponível.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;antiácido não particulado&lt;/strong&gt;, como o citrato de sódio 0,3 M, é o único que neutraliza quimicamente o ácido &lt;em&gt;já secretado&lt;/em&gt;, com efeito em poucos minutos; por isso é o agente indicado quando a indução é iminente. Deve ser não particulado, pois antiácidos particulados como o hidróxido de alumínio produzem lesão pulmonar própria se aspirados. Antagonistas H&lt;sub&gt;2&lt;/sub&gt; e inibidores de bomba de prótons agem sobre a secreção futura e exigem antecedência, e a metoclopramida acelera o esvaziamento gástrico e eleva o tônus do esfíncter esofágico inferior sem alterar o pH.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ranitidina intravenosa precisa de aproximadamente 30 a 60 minutos para elevar o pH e nada faz com o ácido já presente; (B) os inibidores de bomba de prótons têm início ainda mais lento e efeito máximo em horas; (C) a metoclopramida não possui qualquer ação neutralizante, e sua utilidade é reduzir o volume gástrico residual, não a acidez.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os tempos de jejum pediátrico são graduados pela &lt;strong&gt;velocidade de esvaziamento gástrico&lt;/strong&gt; de cada alimento, e não por um prazo único. Líquidos claros — água, chá sem leite, sucos coados sem polpa, soluções de carboidrato — deixam o estômago com meia-vida de cerca de 15 minutos, o que justifica o intervalo curto.&lt;/p&gt;&lt;p&gt;A regra consagrada, do menor para o maior tempo, é: &lt;strong&gt;líquidos claros 2 horas&lt;/strong&gt;; &lt;strong&gt;leite materno 4 horas&lt;/strong&gt;; &lt;strong&gt;fórmula infantil, leite não humano e refeição leve 6 horas&lt;/strong&gt;; refeição gordurosa ou frita, 8 horas. O leite materno esvazia mais rápido que a fórmula por seu menor teor de gordura e caseína. Prolongar desnecessariamente o jejum em lactentes é prejudicial: gera irritabilidade, desidratação e hipoglicemia, sem qualquer ganho de segurança — daí a tendência atual de liberar líquidos claros até 1 hora em serviços selecionados.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) atribui ao leite materno o tempo da fórmula e à fórmula o tempo da refeição gordurosa, prolongando o jejum sem benefício; (C) impõe 4 horas a líquidos claros, retrocesso conceitual já abandonado; (D) encurta indevidamente o intervalo do leite materno e da fórmula, que não esvaziam como líquidos claros por formarem coágulos no meio ácido gástrico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os tempos de jejum pediátrico são graduados pela &lt;strong&gt;velocidade de esvaziamento gástrico&lt;/strong&gt; de cada alimento, e não por um prazo único. Líquidos claros (água, chá sem leite, sucos coados sem polpa, soluções de carboidrato) deixam o estômago com meia-vida de cerca de 15 minutos, o que justifica o intervalo curto.&lt;/p&gt;&lt;p&gt;A regra consagrada, do menor para o maior tempo, é: &lt;strong&gt;líquidos claros 2 horas&lt;/strong&gt;; &lt;strong&gt;leite materno 4 horas&lt;/strong&gt;; &lt;strong&gt;fórmula infantil, leite não humano e refeição leve 6 horas&lt;/strong&gt;; refeição gordurosa ou frita, 8 horas. O leite materno esvazia mais rápido que a fórmula por seu menor teor de gordura e caseína. Prolongar desnecessariamente o jejum em lactentes é prejudicial: gera irritabilidade, desidratação e hipoglicemia, sem qualquer ganho de segurança; daí a tendência atual de liberar líquidos claros até 1 hora em serviços selecionados.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) atribui ao leite materno o tempo da fórmula e à fórmula o tempo da refeição gordurosa, prolongando o jejum sem benefício; (C) impõe 4 horas a líquidos claros, retrocesso conceitual já abandonado; (D) encurta indevidamente o intervalo do leite materno e da fórmula, que não esvaziam como líquidos claros por formarem coágulos no meio ácido gástrico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O manejo de medicações crônicas segue uma lógica simples: mantém-se o que protege e cuja retirada gera efeito rebote; suspende-se o que traz risco perioperatório específico.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;inibidores do cotransportador sódio-glicose tipo 2&lt;/strong&gt; (empagliflozina, dapagliflozina, canagliflozina) provocam glicosúria e depleção de volume e, no jejum e no estresse cirúrgico, favorecem &lt;strong&gt;cetoacidose euglicêmica&lt;/strong&gt; — quadro traiçoeiro, com acidose de ânion-gap elevado e glicemia normal ou pouco alterada, o que retarda o diagnóstico. Recomenda-se suspendê-los de três a quatro dias antes de cirurgias de médio e grande porte. A metformina é habitualmente suspensa no dia do procedimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) betabloqueadores de uso crônico devem ser &lt;em&gt;mantidos&lt;/em&gt;, inclusive na manhã da cirurgia, pois a retirada abrupta causa rebote adrenérgico, taquicardia, isquemia e arritmia; (B) as estatinas também devem ser mantidas, pelo efeito pleiotrópico de estabilização de placa, e não há risco relevante de rabdomiólise ligado ao jejum perioperatório; (D) o antagonista do receptor de angiotensina, quando usado como anti-hipertensivo, costuma ser &lt;em&gt;omitido&lt;/em&gt; na manhã da cirurgia, justamente porque sua manutenção se associa a hipotensão refratária a vasopressores na indução, por bloqueio do eixo renina-angiotensina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O manejo de medicações crônicas segue uma lógica simples: mantém-se o que protege e cuja retirada gera efeito rebote; suspende-se o que traz risco perioperatório específico.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;inibidores do cotransportador sódio-glicose tipo 2&lt;/strong&gt; (empagliflozina, dapagliflozina, canagliflozina) provocam glicosúria e depleção de volume e, no jejum e no estresse cirúrgico, favorecem &lt;strong&gt;cetoacidose euglicêmica&lt;/strong&gt;, quadro traiçoeiro, com acidose de ânion-gap elevado e glicemia normal ou pouco alterada, o que retarda o diagnóstico. Recomenda-se suspendê-los de três a quatro dias antes de cirurgias de médio e grande porte. A metformina é habitualmente suspensa no dia do procedimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) betabloqueadores de uso crônico devem ser &lt;em&gt;mantidos&lt;/em&gt;, inclusive na manhã da cirurgia, pois a retirada abrupta causa rebote adrenérgico, taquicardia, isquemia e arritmia; (B) as estatinas também devem ser mantidas, pelo efeito pleiotrópico de estabilização de placa, e não há risco relevante de rabdomiólise ligado ao jejum perioperatório; (D) o antagonista do receptor de angiotensina, quando usado como anti-hipertensivo, costuma ser &lt;em&gt;omitido&lt;/em&gt; na manhã da cirurgia, justamente porque sua manutenção se associa a hipotensão refratária a vasopressores na indução, por bloqueio do eixo renina-angiotensina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;disreflexia autonômica&lt;/strong&gt; ocorre em lesões medulares acima de &lt;strong&gt;T6&lt;/strong&gt;, após a resolução do choque medular (semanas a meses do trauma). Um estímulo nociceptivo abaixo do nível da lesão — distensão vesical ou retal é o gatilho clássico — deflagra descarga simpática maciça pelos neurônios pré-ganglionares da cadeia toracolombar, que já não recebem a inibição descendente supraespinal interrompida pela secção.&lt;/p&gt;&lt;p&gt;O resultado é vasoconstrição intensa &lt;em&gt;abaixo&lt;/em&gt; da lesão (palidez, piloereção, hipertensão grave) com vasodilatação compensatória &lt;em&gt;acima&lt;/em&gt; dela (rubor, sudorese, congestão nasal, cefaleia), mediada pelos barorreceptores carotídeos. A mesma via barorreflexa produz &lt;strong&gt;bradicardia&lt;/strong&gt;, e é essa combinação de hipertensão com frequência baixa que fecha o diagnóstico. O tratamento é remover o estímulo, aprofundar o plano anestésico e usar vasodilatador de meia-vida curta, como nitroprussiato ou nitroglicerina, pois a crise cede tão rapidamente quanto surge. A prevenção é anestesia adequada, geral ou espinal, mesmo em paciente sem sensibilidade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) rotular como hipertensão essencial ignora a topografia dos sinais, e o betabloqueio isolado deixa a vasoconstrição alfa sem oposição; (C) o choque medular cursa com hipotensão e não se instala dois anos após o trauma; (D) a bradicardia é reflexa à hipertensão, e tratá-la com atropina mantendo o estímulo agrava a crise e expõe a hemorragia intracraniana e edema pulmonar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;disreflexia autonômica&lt;/strong&gt; ocorre em lesões medulares acima de &lt;strong&gt;T6&lt;/strong&gt;, após a resolução do choque medular (semanas a meses do trauma). Um estímulo nociceptivo abaixo do nível da lesão (distensão vesical ou retal é o gatilho clássico) deflagra descarga simpática maciça pelos neurônios pré-ganglionares da cadeia toracolombar, que já não recebem a inibição descendente supraespinal interrompida pela secção.&lt;/p&gt;&lt;p&gt;O resultado é vasoconstrição intensa &lt;em&gt;abaixo&lt;/em&gt; da lesão (palidez, piloereção, hipertensão grave) com vasodilatação compensatória &lt;em&gt;acima&lt;/em&gt; dela (rubor, sudorese, congestão nasal, cefaleia), mediada pelos barorreceptores carotídeos. A mesma via barorreflexa produz &lt;strong&gt;bradicardia&lt;/strong&gt;, e é essa combinação de hipertensão com frequência baixa que fecha o diagnóstico. O tratamento é remover o estímulo, aprofundar o plano anestésico e usar vasodilatador de meia-vida curta, como nitroprussiato ou nitroglicerina, pois a crise cede tão rapidamente quanto surge. A prevenção é anestesia adequada, geral ou espinal, mesmo em paciente sem sensibilidade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) rotular como hipertensão essencial ignora a topografia dos sinais, e o betabloqueio isolado deixa a vasoconstrição alfa sem oposição; (C) o choque medular cursa com hipotensão e não se instala dois anos após o trauma; (D) a bradicardia é reflexa à hipertensão, e tratá-la com atropina mantendo o estímulo agrava a crise e expõe a hemorragia intracraniana e edema pulmonar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O traumatismo cranioencefálico grave, sobretudo com lesão frontobasal, de linha média ou de haste hipofisária, pode romper a via hipotálamo-neuro-hipofisária e abolir a liberação de &lt;strong&gt;vasopressina&lt;/strong&gt;. Sem hormônio antidiurético, o túbulo coletor perde a capacidade de reabsorver água, e o resultado é poliúria de urina diluída com desidratação hipertônica.&lt;/p&gt;&lt;p&gt;A assinatura laboratorial do &lt;strong&gt;diabetes insípido central&lt;/strong&gt; é a dissociação entre um plasma concentrado (sódio acima de 145 mEq/L, osmolalidade plasmática elevada) e uma urina inadequadamente diluída (osmolalidade urinária baixa, tipicamente inferior à do plasma e frequentemente abaixo de 300 mOsm/kg), com débito urinário desproporcional. O tratamento associa reposição do déficit de água livre — corrigindo o sódio de forma gradual, para evitar edema cerebral — e desmopressina, análogo com ação preferencial em receptores V&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a síndrome perdedora de sal cerebral cursa com &lt;em&gt;hiponatremia&lt;/em&gt; e hipovolemia, e não com sódio de 158 mEq/L; (C) a secreção inapropriada de hormônio antidiurético também produz hiponatremia, com urina concentrada e volume urinário baixo, exatamente o oposto do quadro; (D) a diurese osmótica é hipótese razoável em quem recebeu manitol, mas foi explicitamente afastada, e ela elevaria a osmolalidade urinária em vez de reduzi-la.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O traumatismo cranioencefálico grave, sobretudo com lesão frontobasal, de linha média ou de haste hipofisária, pode romper a via hipotálamo-neuro-hipofisária e abolir a liberação de &lt;strong&gt;vasopressina&lt;/strong&gt;. Sem hormônio antidiurético, o túbulo coletor perde a capacidade de reabsorver água, e o resultado é poliúria de urina diluída com desidratação hipertônica.&lt;/p&gt;&lt;p&gt;A assinatura laboratorial do &lt;strong&gt;diabetes insípido central&lt;/strong&gt; é a dissociação entre um plasma concentrado (sódio acima de 145 mEq/L, osmolalidade plasmática elevada) e uma urina inadequadamente diluída (osmolalidade urinária baixa, tipicamente inferior à do plasma e frequentemente abaixo de 300 mOsm/kg), com débito urinário desproporcional. O tratamento associa reposição do déficit de água livre (corrigindo o sódio de forma gradual, para evitar edema cerebral) e desmopressina, análogo com ação preferencial em receptores V&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a síndrome perdedora de sal cerebral cursa com &lt;em&gt;hiponatremia&lt;/em&gt; e hipovolemia, e não com sódio de 158 mEq/L; (C) a secreção inapropriada de hormônio antidiurético também produz hiponatremia, com urina concentrada e volume urinário baixo, exatamente o oposto do quadro; (D) a diurese osmótica é hipótese razoável em quem recebeu manitol, mas foi explicitamente afastada, e ela elevaria a osmolalidade urinária em vez de reduzi-la.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome da embolia gordurosa&lt;/strong&gt; decorre da liberação de gotículas de gordura medular para a circulação venosa após fratura de ossos longos ou da pelve, com dois mecanismos somados: obstrução mecânica de capilares pulmonares e lesão bioquímica pelos ácidos graxos livres gerados pela lipase, que danificam o endotélio e o pneumócito.&lt;/p&gt;&lt;p&gt;O intervalo livre de &lt;strong&gt;12 a 72 horas&lt;/strong&gt; entre o trauma e o quadro é característico e ajuda a separá-la da contusão pulmonar, que é precoce. A tríade clássica reúne &lt;strong&gt;hipoxemia&lt;/strong&gt;, &lt;strong&gt;alteração neurológica&lt;/strong&gt; (confusão, agitação, rebaixamento) e &lt;strong&gt;petéquias&lt;/strong&gt; em tórax superior, axilas, pescoço e conjuntivas — o sinal mais específico, presente em cerca de metade dos casos, atribuído à embolização de arteríolas cutâneas frágeis. Completam o quadro febre, taquicardia, plaquetopenia e queda do hematócrito. O tratamento é de suporte, e a melhor prevenção é a fixação precoce da fratura.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o tromboembolismo pulmonar é improvável tão precocemente e não explica petéquias, febre nem plaquetopenia com anemia; (C) a contusão pulmonar manifesta-se nas primeiras horas e não cursa com exantema petequial nem com confusão mental; (D) a sepse cutânea exigiria porta de entrada e evolução mais arrastada, e o padrão temporal com fratura de ossos longos aponta para embolia gordurosa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome da embolia gordurosa&lt;/strong&gt; decorre da liberação de gotículas de gordura medular para a circulação venosa após fratura de ossos longos ou da pelve, com dois mecanismos somados: obstrução mecânica de capilares pulmonares e lesão bioquímica pelos ácidos graxos livres gerados pela lipase, que danificam o endotélio e o pneumócito.&lt;/p&gt;&lt;p&gt;O intervalo livre de &lt;strong&gt;12 a 72 horas&lt;/strong&gt; entre o trauma e o quadro é característico e ajuda a separá-la da contusão pulmonar, que é precoce. A tríade clássica reúne &lt;strong&gt;hipoxemia&lt;/strong&gt;, &lt;strong&gt;alteração neurológica&lt;/strong&gt; (confusão, agitação, rebaixamento) e &lt;strong&gt;petéquias&lt;/strong&gt; em tórax superior, axilas, pescoço e conjuntivas; este é o sinal mais específico, presente em cerca de metade dos casos, atribuído à embolização de arteríolas cutâneas frágeis. Completam o quadro febre, taquicardia, plaquetopenia e queda do hematócrito. O tratamento é de suporte, e a melhor prevenção é a fixação precoce da fratura.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o tromboembolismo pulmonar é improvável tão precocemente e não explica petéquias, febre nem plaquetopenia com anemia; (C) a contusão pulmonar manifesta-se nas primeiras horas e não cursa com exantema petequial nem com confusão mental; (D) a sepse cutânea exigiria porta de entrada e evolução mais arrastada, e o padrão temporal com fratura de ossos longos aponta para embolia gordurosa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;dor do torniquete&lt;/strong&gt; aparece tipicamente entre 45 e 60 minutos de isquemia e caracteriza-se por sensação difusa de queimação e opressão, acompanhada de hipertensão progressiva, mesmo quando o nível sensitivo do bloqueio parece adequado e a função motora está abolida.&lt;/p&gt;&lt;p&gt;A explicação aceita é a condução por &lt;strong&gt;fibras C amielínicas&lt;/strong&gt;, que transmitem dor lenta, difusa e mal localizada. Essas fibras são bloqueadas de maneira incompleta e menos duradoura pelos anestésicos locais na concentração residual encontrada ao fim de uma raquianestesia, enquanto fibras A-delta e motoras permanecem bloqueadas. A dor escapa ao teste de sensibilidade convencional, feito com picada ou frio, que avalia sobretudo fibras A-delta — daí a discordância entre exame aparentemente satisfatório e paciente com dor. O manejo inclui analgesia sistêmica, aprofundamento da sedação e, sobretudo, limitar o tempo de isquemia, com desinsuflação periódica quando possível.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há regressão, pois o nível sensitivo permanece em T10 e o bloqueio motor está mantido; (B) a isquemia muscular contribui para o desconforto, mas o mecanismo determinante da dor referida é a condução por fibras C, e não a estimulação quimiorreceptora; (C) a lesão neural por compressão existe como complicação, porém manifesta-se como déficit motor e sensitivo &lt;em&gt;após&lt;/em&gt; a desinsuflação, e não como dor durante a isquemia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;dor do torniquete&lt;/strong&gt; aparece tipicamente entre 45 e 60 minutos de isquemia e caracteriza-se por sensação difusa de queimação e opressão, acompanhada de hipertensão progressiva, mesmo quando o nível sensitivo do bloqueio parece adequado e a função motora está abolida.&lt;/p&gt;&lt;p&gt;A explicação aceita é a condução por &lt;strong&gt;fibras C amielínicas&lt;/strong&gt;, que transmitem dor lenta, difusa e mal localizada. Essas fibras são bloqueadas de maneira incompleta e menos duradoura pelos anestésicos locais na concentração residual encontrada ao fim de uma raquianestesia, enquanto fibras A-delta e motoras permanecem bloqueadas. A dor escapa ao teste de sensibilidade convencional, feito com picada ou frio, que avalia sobretudo fibras A-delta; daí a discordância entre exame aparentemente satisfatório e paciente com dor. O manejo inclui analgesia sistêmica, aprofundamento da sedação e, sobretudo, limitar o tempo de isquemia, com desinsuflação periódica quando possível.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há regressão, pois o nível sensitivo permanece em T10 e o bloqueio motor está mantido; (B) a isquemia muscular contribui para o desconforto, mas o mecanismo determinante da dor referida é a condução por fibras C, e não a estimulação quimiorreceptora; (C) a lesão neural por compressão existe como complicação, porém manifesta-se como déficit motor e sensitivo &lt;em&gt;após&lt;/em&gt; a desinsuflação, e não como dor durante a isquemia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome pós-reperfusão&lt;/strong&gt; é definida por queda superior a 30 % da pressão arterial média nos primeiros cinco minutos após o desclampeamento, com duração de ao menos um minuto. Ao ser reperfundido, o enxerto devolve à circulação sistêmica um bolo de sangue frio, ácido e rico em potássio, acumulado na solução de preservação e no leito esplâncnico congesto, além de mediadores vasodilatadores e substâncias cardiodepressoras.&lt;/p&gt;&lt;p&gt;Diante de hipercalemia com repercussão eletrocardiográfica e instabilidade, a prioridade absoluta é &lt;strong&gt;estabilizar a membrana do miócito&lt;/strong&gt; com sal de cálcio. O cálcio não reduz a caleimia, mas restaura o gradiente do potencial de repouso em segundos e previne fibrilação ventricular e assistolia — e, nesse caso, há ainda hipocalcemia iônica real, secundária ao citrato transfundido e ao fígado não funcionante, o que reforça a indicação. Só depois entram as medidas que deslocam ou eliminam potássio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) insulina com glicose é medida correta, porém de segunda linha, com início em 10 a 20 minutos, tempo incompatível com a instabilidade descrita; (C) a furosemida depende de função renal preservada e de volemia adequada, ambas incertas nesse cenário, e tem efeito tardio; (D) o beta-2 agonista inalatório é pouco confiável no paciente ventilado e instável, com início lento e resposta variável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome pós-reperfusão&lt;/strong&gt; é definida por queda superior a 30 % da pressão arterial média nos primeiros cinco minutos após o desclampeamento, com duração de ao menos um minuto. Ao ser reperfundido, o enxerto devolve à circulação sistêmica um bolo de sangue frio, ácido e rico em potássio, acumulado na solução de preservação e no leito esplâncnico congesto, além de mediadores vasodilatadores e substâncias cardiodepressoras.&lt;/p&gt;&lt;p&gt;Diante de hipercalemia com repercussão eletrocardiográfica e instabilidade, a prioridade absoluta é &lt;strong&gt;estabilizar a membrana do miócito&lt;/strong&gt; com sal de cálcio. O cálcio não reduz a caleimia, mas restaura o gradiente do potencial de repouso em segundos e previne fibrilação ventricular e assistolia. Nesse caso, há ainda hipocalcemia iônica real, secundária ao citrato transfundido e ao fígado não funcionante, o que reforça a indicação. Só depois entram as medidas que deslocam ou eliminam potássio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) insulina com glicose é medida correta, porém de segunda linha, com início em 10 a 20 minutos, tempo incompatível com a instabilidade descrita; (C) a furosemida depende de função renal preservada e de volemia adequada, ambas incertas nesse cenário, e tem efeito tardio; (D) o beta-2 agonista inalatório é pouco confiável no paciente ventilado e instável, com início lento e resposta variável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No transplante cardíaco ortotópico, a secção das conexões autonômicas deixa o enxerto &lt;strong&gt;desnervado&lt;/strong&gt;. A reinervação simpática pode ocorrer de forma parcial e tardia em alguns pacientes, mas a parassimpática é inconsistente e, na prática, deve-se assumir ausência de tônus vagal sobre o nó sinusal do doador.&lt;/p&gt;&lt;p&gt;Duas consequências dominam a conduta. Primeiro, fármacos de &lt;strong&gt;ação indireta&lt;/strong&gt; — atropina, efedrina, glicopirrolônio e manobras reflexas como o massagem do seio carotídeo — são &lt;strong&gt;ineficazes&lt;/strong&gt;, pois dependem de terminações nervosas íntegras. Segundo, apenas &lt;strong&gt;agonistas de ação direta&lt;/strong&gt; funcionam: isoprenalina, adrenalina, dobutamina e dopamina em doses adequadas, sendo a isoprenalina a escolha clássica para cronotropismo. Como o débito cardíaco do enxerto é fortemente &lt;strong&gt;pré-carga dependente&lt;/strong&gt;, a manutenção da volemia é igualmente essencial, e o pneumoperitônio, ao reduzir o retorno venoso, é gatilho frequente de instabilidade. A frequência basal costuma ser mais alta, entre 90 e 110 bpm, pelo ritmo intrínseco sem freio vagal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o problema não é dose: nenhuma quantidade de atropina age sobre um nó sinusal sem inervação vagal; (B) admitir inervação parassimpática residual e escolher efedrina repete o mesmo erro do mecanismo indireto; (D) rejeição é diagnóstico possível a longo prazo, mas o ritmo sinusal preservado e o contexto de pneumoperitônio afastam bloqueio atrioventricular total.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No transplante cardíaco ortotópico, a secção das conexões autonômicas deixa o enxerto &lt;strong&gt;desnervado&lt;/strong&gt;. A reinervação simpática pode ocorrer de forma parcial e tardia em alguns pacientes, mas a parassimpática é inconsistente e, na prática, deve-se assumir ausência de tônus vagal sobre o nó sinusal do doador.&lt;/p&gt;&lt;p&gt;Duas consequências dominam a conduta. Primeiro, fármacos de &lt;strong&gt;ação indireta&lt;/strong&gt; (atropina, efedrina, glicopirrolônio e manobras reflexas como a massagem do seio carotídeo) são &lt;strong&gt;ineficazes&lt;/strong&gt;, pois dependem de terminações nervosas íntegras. Segundo, apenas &lt;strong&gt;agonistas de ação direta&lt;/strong&gt; funcionam: isoprenalina, adrenalina, dobutamina e dopamina em doses adequadas, sendo a isoprenalina a escolha clássica para cronotropismo. Como o débito cardíaco do enxerto é fortemente &lt;strong&gt;pré-carga dependente&lt;/strong&gt;, a manutenção da volemia é igualmente essencial, e o pneumoperitônio, ao reduzir o retorno venoso, é gatilho frequente de instabilidade. A frequência basal costuma ser mais alta, entre 90 e 110 bpm, pelo ritmo intrínseco sem freio vagal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o problema não é dose: nenhuma quantidade de atropina age sobre um nó sinusal sem inervação vagal; (B) admitir inervação parassimpática residual e escolher efedrina repete o mesmo erro do mecanismo indireto; (D) rejeição é diagnóstico possível a longo prazo, mas o ritmo sinusal preservado e o contexto de pneumoperitônio afastam bloqueio atrioventricular total.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;embolia de dióxido de carbono&lt;/strong&gt; ocorre quando o gás insuflado entra em vaso aberto — mais provável quando há dissecção de leito venoso e gradiente favorável entre a pressão intra-abdominal e a pressão venosa. O gás acumula-se no ventrículo direito e na via de saída, formando um &lt;em&gt;air lock&lt;/em&gt; que bloqueia a ejeção e derruba abruptamente o débito cardíaco.&lt;/p&gt;&lt;p&gt;A assinatura é a &lt;strong&gt;queda súbita e acentuada da capnografia&lt;/strong&gt;, reflexo do colapso do débito e do aumento do espaço morto, acompanhada de hipotensão, dessaturação, arritmia e, quando o volume é grande, sopro em roda de moinho. Pressões de via aérea inalteradas ajudam a afastar broncoespasmo. A conduta imediata reúne: cessar a insuflação e desfazer o pneumoperitônio, ventilar com oxigênio a 100 %, suspender o óxido nitroso, colocar a paciente em decúbito lateral esquerdo com cefalodeclive (posição de Durant) para deslocar o gás do infundíbulo pulmonar, expandir volume e usar vasopressor; havendo cateter central, aspirar o gás.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) hiperventilar trata o número, não a causa, e mantém o gatilho ativo enquanto a paciente está em choque obstrutivo; (C) o broncoespasmo elevaria as pressões de via aérea e prolongaria a expiração, com capnografia em rampa ascendente, e não queda abrupta; (D) aumentar a pressão do pneumoperitônio amplia o gradiente e agrava a entrada de gás.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;embolia de dióxido de carbono&lt;/strong&gt; ocorre quando o gás insuflado entra em vaso aberto, mais provável quando há dissecção de leito venoso e gradiente favorável entre a pressão intra-abdominal e a pressão venosa. O gás acumula-se no ventrículo direito e na via de saída, formando um &lt;em&gt;air lock&lt;/em&gt; que bloqueia a ejeção e derruba abruptamente o débito cardíaco.&lt;/p&gt;&lt;p&gt;A assinatura é a &lt;strong&gt;queda súbita e acentuada da capnografia&lt;/strong&gt;, reflexo do colapso do débito e do aumento do espaço morto, acompanhada de hipotensão, dessaturação, arritmia e, quando o volume é grande, sopro em roda de moinho. Pressões de via aérea inalteradas ajudam a afastar broncoespasmo. A conduta imediata reúne: cessar a insuflação e desfazer o pneumoperitônio, ventilar com oxigênio a 100 %, suspender o óxido nitroso, colocar a paciente em decúbito lateral esquerdo com cefalodeclive (posição de Durant) para deslocar o gás do infundíbulo pulmonar, expandir volume e usar vasopressor; havendo cateter central, aspirar o gás.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) hiperventilar trata o número, não a causa, e mantém o gatilho ativo enquanto a paciente está em choque obstrutivo; (C) o broncoespasmo elevaria as pressões de via aérea e prolongaria a expiração, com capnografia em rampa ascendente, e não queda abrupta; (D) aumentar a pressão do pneumoperitônio amplia o gradiente e agrava a entrada de gás.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A bexiga funciona como membrana passiva que transmite a pressão da cavidade peritoneal, o que faz da via vesical o padrão para estimar a &lt;strong&gt;pressão intra-abdominal&lt;/strong&gt;. Para ser reprodutível, a técnica exige padronização rigorosa: paciente em &lt;strong&gt;decúbito dorsal horizontal&lt;/strong&gt;, medida ao &lt;strong&gt;final da expiração&lt;/strong&gt;, sem contração da musculatura abdominal, com instilação de no máximo &lt;strong&gt;25 mL&lt;/strong&gt; de solução salina e o transdutor zerado na &lt;strong&gt;linha axilar média, na altura da crista ilíaca&lt;/strong&gt;. Volumes maiores de instilação superestimam o valor por distenderem o detrusor.&lt;/p&gt;&lt;p&gt;A pressão intra-abdominal normal no doente crítico gira em torno de 5 a 7 mmHg. Hipertensão intra-abdominal é definida por valores sustentados iguais ou superiores a 12 mmHg, graduada de I a IV (12-15, 16-20, 21-25 e acima de 25 mmHg). A &lt;strong&gt;síndrome compartimental abdominal&lt;/strong&gt; exige pressão acima de 20 mmHg associada a nova disfunção orgânica — exatamente o caso, que reúne oligúria, elevação da pressão de platô e choque, e impõe descompressão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 26 mmHg corresponde a grau IV, e a presença de disfunção orgânica torna a conduta expectante inaceitável; (B) confunde valor patológico com fisiológico; (C) inverte a fórmula — a pressão de perfusão abdominal é a pressão arterial média menos a pressão intra-abdominal, aqui apenas 36 mmHg.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A bexiga funciona como membrana passiva que transmite a pressão da cavidade peritoneal, o que faz da via vesical o padrão para estimar a &lt;strong&gt;pressão intra-abdominal&lt;/strong&gt;. Para ser reprodutível, a técnica exige padronização rigorosa: paciente em &lt;strong&gt;decúbito dorsal horizontal&lt;/strong&gt;, medida ao &lt;strong&gt;final da expiração&lt;/strong&gt;, sem contração da musculatura abdominal, com instilação de no máximo &lt;strong&gt;25 mL&lt;/strong&gt; de solução salina e o transdutor zerado na &lt;strong&gt;linha axilar média, na altura da crista ilíaca&lt;/strong&gt;. Volumes maiores de instilação superestimam o valor por distenderem o detrusor.&lt;/p&gt;&lt;p&gt;A pressão intra-abdominal normal no doente crítico gira em torno de 5 a 7 mmHg. Hipertensão intra-abdominal é definida por valores sustentados iguais ou superiores a 12 mmHg, graduada de I a IV (12-15, 16-20, 21-25 e acima de 25 mmHg). A &lt;strong&gt;síndrome compartimental abdominal&lt;/strong&gt; exige pressão acima de 20 mmHg associada a nova disfunção orgânica, exatamente o caso, que reúne oligúria, elevação da pressão de platô e choque, e impõe descompressão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 26 mmHg corresponde a grau IV, e a presença de disfunção orgânica torna a conduta expectante inaceitável; (B) confunde valor patológico com fisiológico; (C) inverte a fórmula: a pressão de perfusão abdominal é a pressão arterial média menos a pressão intra-abdominal, aqui apenas 36 mmHg.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;óxido nitroso&lt;/strong&gt; é cerca de 34 vezes mais solúvel no sangue que o nitrogênio e muito mais que os gases perfluorocarbonados. Diante de uma cavidade gasosa fechada, ele entra mais rápido do que o gás interno consegue sair, e o resultado é &lt;strong&gt;expansão de volume&lt;/strong&gt; em espaço não complacente — princípio que também explica seu efeito em pneumotórax, alça intestinal distendida e balonete de tubo traqueal.&lt;/p&gt;&lt;p&gt;Após vitrectomia com tamponamento gasoso, a bolha ocupa a câmara vítrea de um globo rígido. A expansão eleva de forma abrupta a &lt;strong&gt;pressão intraocular&lt;/strong&gt;, podendo ultrapassar a pressão de perfusão da artéria central da retina e causar isquemia e perda visual irreversível. Recomenda-se evitar o óxido nitroso por cerca de &lt;strong&gt;10 dias&lt;/strong&gt; após hexafluoreto de enxofre e por &lt;strong&gt;até 30 dias ou mais&lt;/strong&gt; após perfluoropropano, que persiste por muito mais tempo. Ao suspender o óxido nitroso, o movimento inverso também é danoso, com contração rápida da bolha e perda do tamponamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o hexafluoreto de enxofre permanece na cavidade vítrea por cerca de dez dias, e cinco dias é intervalo claramente insuficiente; (C) qualquer concentração clinicamente útil expande a bolha, apenas com velocidade menor; (D) a acetazolamida reduz a produção de humor aquoso e não compensa o aumento volumétrico de uma bolha em expansão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;óxido nitroso&lt;/strong&gt; é cerca de 34 vezes mais solúvel no sangue que o nitrogênio e muito mais que os gases perfluorocarbonados. Diante de uma cavidade gasosa fechada, ele entra mais rápido do que o gás interno consegue sair, e o resultado é &lt;strong&gt;expansão de volume&lt;/strong&gt; em espaço não complacente, princípio que também explica seu efeito em pneumotórax, alça intestinal distendida e balonete de tubo traqueal.&lt;/p&gt;&lt;p&gt;Após vitrectomia com tamponamento gasoso, a bolha ocupa a câmara vítrea de um globo rígido. A expansão eleva de forma abrupta a &lt;strong&gt;pressão intraocular&lt;/strong&gt;, podendo ultrapassar a pressão de perfusão da artéria central da retina e causar isquemia e perda visual irreversível. Recomenda-se evitar o óxido nitroso por cerca de &lt;strong&gt;10 dias&lt;/strong&gt; após hexafluoreto de enxofre e por &lt;strong&gt;até 30 dias ou mais&lt;/strong&gt; após perfluoropropano, que persiste por muito mais tempo. Ao suspender o óxido nitroso, o movimento inverso também é danoso, com contração rápida da bolha e perda do tamponamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o hexafluoreto de enxofre permanece na cavidade vítrea por cerca de dez dias, e cinco dias é intervalo claramente insuficiente; (C) qualquer concentração clinicamente útil expande a bolha, apenas com velocidade menor; (D) a acetazolamida reduz a produção de humor aquoso e não compensa o aumento volumétrico de uma bolha em expansão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;nervo laríngeo recorrente&lt;/strong&gt; inerva todos os músculos intrínsecos da laringe, exceto o cricotireóideo. O único abdutor das cordas vocais é o &lt;strong&gt;cricoaritenóideo posterior&lt;/strong&gt;, também dependente do recorrente. Quando ambos os recorrentes são lesados, perde-se a abdução, enquanto o cricotireóideo — inervado pelo ramo externo do laríngeo superior — mantém a tensão e a adução, e as cordas assumem posição próxima à linha média.&lt;/p&gt;&lt;p&gt;Daí o quadro típico: &lt;strong&gt;estridor inspiratório e obstrução respiratória&lt;/strong&gt; logo após a extubação, com voz relativamente preservada em intensidade, porque a fenda glótica estreita ainda permite fonação. É emergência de via aérea, com necessidade de reintubação imediata e, se a lesão for definitiva, traqueostomia. A lesão &lt;em&gt;unilateral&lt;/em&gt;, ao contrário, produz &lt;strong&gt;rouquidão e voz soprosa&lt;/strong&gt; sem obstrução, pois a corda contralateral compensa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão unilateral cursa com disfonia como sinal dominante e raramente causa estridor, o que contraria o exame descrito; (B) a lesão do ramo externo do laríngeo superior afeta a projeção e as notas agudas da voz, com fadiga vocal, sem comprometer a permeabilidade glótica; (D) o laringoespasmo é diagnóstico diferencial legítimo, mas cursa com afonia ou choro abafado e tende a ceder com pressão positiva, aprofundamento anestésico ou suxametônio, o que não explica a voz normal com obstrução progressiva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;nervo laríngeo recorrente&lt;/strong&gt; inerva todos os músculos intrínsecos da laringe, exceto o cricotireóideo. O único abdutor das cordas vocais é o &lt;strong&gt;cricoaritenóideo posterior&lt;/strong&gt;, também dependente do recorrente. Quando ambos os recorrentes são lesados, perde-se a abdução, enquanto o cricotireóideo (inervado pelo ramo externo do laríngeo superior) mantém a tensão e a adução, e as cordas assumem posição próxima à linha média.&lt;/p&gt;&lt;p&gt;Daí o quadro típico: &lt;strong&gt;estridor inspiratório e obstrução respiratória&lt;/strong&gt; logo após a extubação, com voz relativamente preservada em intensidade, porque a fenda glótica estreita ainda permite fonação. É emergência de via aérea, com necessidade de reintubação imediata e, se a lesão for definitiva, traqueostomia. A lesão &lt;em&gt;unilateral&lt;/em&gt;, ao contrário, produz &lt;strong&gt;rouquidão e voz soprosa&lt;/strong&gt; sem obstrução, pois a corda contralateral compensa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão unilateral cursa com disfonia como sinal dominante e raramente causa estridor, o que contraria o exame descrito; (B) a lesão do ramo externo do laríngeo superior afeta a projeção e as notas agudas da voz, com fadiga vocal, sem comprometer a permeabilidade glótica; (D) o laringoespasmo é diagnóstico diferencial legítimo, mas cursa com afonia ou choro abafado e tende a ceder com pressão positiva, aprofundamento anestésico ou suxametônio, o que não explica a voz normal com obstrução progressiva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O campo magnético estático da ressonância é &lt;strong&gt;permanente&lt;/strong&gt;: só é desfeito no &lt;em&gt;quench&lt;/em&gt;, perda controlada ou acidental do hélio líquido, procedimento de emergência caro e potencialmente perigoso pelo deslocamento de oxigênio na sala. Por isso, todas as precauções valem 24 horas por dia, mesmo fora do horário de exames.&lt;/p&gt;&lt;p&gt;A grandeza que determina a atração não é o campo em si, mas o &lt;strong&gt;gradiente espacial do campo&lt;/strong&gt;, que aumenta acentuadamente perto da abertura do magneto. Consequentemente, um objeto ferromagnético que parecia manejável a alguns metros é arrancado das mãos ao aproximar-se, atingindo velocidades capazes de matar — é o &lt;strong&gt;efeito projétil&lt;/strong&gt;, causa clássica de óbito nesse ambiente. O acesso é organizado em quatro zonas, sendo a &lt;strong&gt;zona IV&lt;/strong&gt; a sala do magneto, onde só entram equipamentos comprovadamente seguros. Monitor, bombas e ventilador devem ser específicos para ressonância, e o paciente é acompanhado por observação direta e por monitorização à distância, com prolongadores.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o magneto supercondutor não é desligado entre exames; (B) o rótulo "condicional" significa segurança apenas dentro de condições declaradas de intensidade de campo, gradiente e taxa de absorção específica, não liberação irrestrita; (D) equipamento convencional simplesmente não pode permanecer na zona IV, pois distância fixa não anula o risco de projétil nem a interferência sobre a imagem e sobre o próprio aparelho.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O campo magnético estático da ressonância é &lt;strong&gt;permanente&lt;/strong&gt;: só é desfeito no &lt;em&gt;quench&lt;/em&gt;, perda controlada ou acidental do hélio líquido, procedimento de emergência caro e potencialmente perigoso pelo deslocamento de oxigênio na sala. Por isso, todas as precauções valem 24 horas por dia, mesmo fora do horário de exames.&lt;/p&gt;&lt;p&gt;A grandeza que determina a atração não é o campo em si, mas o &lt;strong&gt;gradiente espacial do campo&lt;/strong&gt;, que aumenta acentuadamente perto da abertura do magneto. Consequentemente, um objeto ferromagnético que parecia manejável a alguns metros é arrancado das mãos ao aproximar-se, atingindo velocidades capazes de matar. É o &lt;strong&gt;efeito projétil&lt;/strong&gt;, causa clássica de óbito nesse ambiente. O acesso é organizado em quatro zonas, sendo a &lt;strong&gt;zona IV&lt;/strong&gt; a sala do magneto, onde só entram equipamentos comprovadamente seguros. Monitor, bombas e ventilador devem ser específicos para ressonância, e o paciente é acompanhado por observação direta e por monitorização à distância, com prolongadores.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o magneto supercondutor não é desligado entre exames; (B) o rótulo "condicional" significa segurança apenas dentro de condições declaradas de intensidade de campo, gradiente e taxa de absorção específica, não liberação irrestrita; (D) equipamento convencional simplesmente não pode permanecer na zona IV, pois distância fixa não anula o risco de projétil nem a interferência sobre a imagem e sobre o próprio aparelho.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Cada molécula de nitroprussiato libera óxido nítrico e &lt;strong&gt;cinco íons cianeto&lt;/strong&gt; ao interagir com a oxiemoglobina. O cianeto é normalmente destoxificado pela rodanase hepática, que o converte em tiocianato usando tiossulfato como doador de enxofre. Quando a velocidade de infusão supera essa capacidade — habitualmente acima de &lt;strong&gt;2 mcg/kg/min de forma sustentada&lt;/strong&gt;, ou em doses altas por curto período —, o cianeto se acumula.&lt;/p&gt;&lt;p&gt;O cianeto liga-se ao ferro férrico da &lt;strong&gt;citocromo c oxidase&lt;/strong&gt; e bloqueia a fosforilação oxidativa. As células deixam de extrair oxigênio, mesmo com oferta adequada: instala-se &lt;strong&gt;acidose láctica&lt;/strong&gt; com &lt;strong&gt;saturação venosa mista ou central elevada&lt;/strong&gt; — a combinação paradoxal que fecha o raciocínio. Somam-se &lt;strong&gt;taquifilaxia&lt;/strong&gt;, com necessidade crescente de dose, e, em paciente acordado, confusão e cefaleia. A conduta é suspender o fármaco, ventilar com oxigênio a 100 % e administrar antídoto, como hidroxocobalamina ou tiossulfato de sódio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a hipoperfusão global produz acidose láctica com saturação venosa &lt;em&gt;baixa&lt;/em&gt;, pois a extração periférica de oxigênio aumenta; (C) a metemoglobinemia é complicação possível, porém rara, e cursa com cianose refratária e discrepância entre oximetria e gasometria, não com saturação venosa alta; (D) a acidose hiperclorêmica não eleva o lactato nem explica a escalada de dose do fármaco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Cada molécula de nitroprussiato libera óxido nítrico e &lt;strong&gt;cinco íons cianeto&lt;/strong&gt; ao interagir com a oxiemoglobina. O cianeto é normalmente destoxificado pela rodanase hepática, que o converte em tiocianato usando tiossulfato como doador de enxofre. Quando a velocidade de infusão supera essa capacidade (habitualmente acima de &lt;strong&gt;2 mcg/kg/min de forma sustentada&lt;/strong&gt;, ou em doses altas por curto período), o cianeto se acumula.&lt;/p&gt;&lt;p&gt;O cianeto liga-se ao ferro férrico da &lt;strong&gt;citocromo c oxidase&lt;/strong&gt; e bloqueia a fosforilação oxidativa. As células deixam de extrair oxigênio, mesmo com oferta adequada: instala-se &lt;strong&gt;acidose láctica&lt;/strong&gt; com &lt;strong&gt;saturação venosa mista ou central elevada&lt;/strong&gt;, a combinação paradoxal que fecha o raciocínio. Somam-se &lt;strong&gt;taquifilaxia&lt;/strong&gt;, com necessidade crescente de dose, e, em paciente acordado, confusão e cefaleia. A conduta é suspender o fármaco, ventilar com oxigênio a 100 % e administrar antídoto, como hidroxocobalamina ou tiossulfato de sódio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a hipoperfusão global produz acidose láctica com saturação venosa &lt;em&gt;baixa&lt;/em&gt;, pois a extração periférica de oxigênio aumenta; (C) a metemoglobinemia é complicação possível, porém rara, e cursa com cianose refratária e discrepância entre oximetria e gasometria, não com saturação venosa alta; (D) a acidose hiperclorêmica não eleva o lactato nem explica a escalada de dose do fármaco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipotermia sob anestesia geral tem três fases bem definidas. A &lt;strong&gt;primeira hora&lt;/strong&gt; é dominada pela &lt;strong&gt;redistribuição&lt;/strong&gt;: os anestésicos abolem a vasoconstrição tônica que mantém o gradiente entre o compartimento central e o periférico, o sangue quente do tronco se distribui para pele e extremidades e a temperatura central cai &lt;strong&gt;0,5 a 1,5 °C&lt;/strong&gt;, sem que o conteúdo total de calor do organismo tenha diminuído na mesma proporção. Por isso, mesmo com aquecimento ativo bem conduzido, essa queda inicial é difícil de evitar — o que se previne com pré-aquecimento cutâneo antes da indução.&lt;/p&gt;&lt;p&gt;Nas duas a três horas seguintes vem a &lt;strong&gt;fase linear&lt;/strong&gt;, em que a perda supera a produção metabólica, com a &lt;strong&gt;radiação&lt;/strong&gt; respondendo pela maior fração, seguida de convecção; evaporação e condução contribuem pouco em cirurgia convencional. Por fim, instala-se o &lt;strong&gt;platô&lt;/strong&gt;, quando a vasoconstrição termorreguladora, agora deflagrada, reduz a perda periférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a evaporação tem peso modesto, ganhando relevância apenas em grandes cavidades abertas e queimados; (B) a anestesia geral &lt;em&gt;reduz&lt;/em&gt; o limiar de vasoconstrição e alarga a faixa interlimiar de cerca de 0,2 para 2 a 4 °C, atrasando a defesa termorreguladora; (C) a condução para a mesa é pequena, pois o colchão é isolante e rapidamente se equilibra com a temperatura do paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipotermia sob anestesia geral tem três fases bem definidas. A &lt;strong&gt;primeira hora&lt;/strong&gt; é dominada pela &lt;strong&gt;redistribuição&lt;/strong&gt;: os anestésicos abolem a vasoconstrição tônica que mantém o gradiente entre o compartimento central e o periférico, o sangue quente do tronco se distribui para pele e extremidades e a temperatura central cai &lt;strong&gt;0,5 a 1,5 °C&lt;/strong&gt;, sem que o conteúdo total de calor do organismo tenha diminuído na mesma proporção. Por isso, mesmo com aquecimento ativo bem conduzido, essa queda inicial é difícil de evitar, e sua prevenção se faz com pré-aquecimento cutâneo antes da indução.&lt;/p&gt;&lt;p&gt;Nas duas a três horas seguintes vem a &lt;strong&gt;fase linear&lt;/strong&gt;, em que a perda supera a produção metabólica, com a &lt;strong&gt;radiação&lt;/strong&gt; respondendo pela maior fração, seguida de convecção; evaporação e condução contribuem pouco em cirurgia convencional. Por fim, instala-se o &lt;strong&gt;platô&lt;/strong&gt;, quando a vasoconstrição termorreguladora, agora deflagrada, reduz a perda periférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a evaporação tem peso modesto, ganhando relevância apenas em grandes cavidades abertas e queimados; (B) a anestesia geral &lt;em&gt;reduz&lt;/em&gt; o limiar de vasoconstrição e alarga a faixa interlimiar de cerca de 0,2 para 2 a 4 °C, atrasando a defesa termorreguladora; (C) a condução para a mesa é pequena, pois o colchão é isolante e rapidamente se equilibra com a temperatura do paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Sensibilidade e especificidade são propriedades intrínsecas do teste e independem da prevalência. Já os &lt;strong&gt;valores preditivos&lt;/strong&gt; respondem à pergunta que interessa ao clínico — dado o resultado, qual a chance de a doença existir — e dependem fortemente da &lt;strong&gt;probabilidade pré-teste&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Montando a tabela de contingência com 1.000 pacientes e prevalência de 10 %: há &lt;strong&gt;100 doentes&lt;/strong&gt; e &lt;strong&gt;900 sadios&lt;/strong&gt;. Com sensibilidade de 90 %, obtêm-se &lt;strong&gt;90 verdadeiros positivos&lt;/strong&gt; e 10 falso-negativos. Com especificidade de 90 %, obtêm-se 810 verdadeiros negativos e &lt;strong&gt;90 falso-positivos&lt;/strong&gt;. O total de testes positivos é 90 + 90 = 180, e o valor preditivo positivo é 90/180 = &lt;strong&gt;50 %&lt;/strong&gt;. Ou seja, mesmo com um teste de desempenho aparentemente bom, metade dos positivos é falso-positivo — a razão pela qual rastreamento de doenças raras gera tantos alarmes falsos. No mesmo cenário, o valor preditivo negativo é 810/820, cerca de 99 %.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde valor preditivo com sensibilidade, que se calcula entre os doentes e não entre os testes positivos; (C) superestima o efeito da especificidade, ignorando que 10 % de 900 sadios geram tantos falso-positivos quanto o número de verdadeiros positivos; (D) a prevalência influencia o valor preditivo, mas não o define sozinha, e 10 % é simplesmente a prevalência copiada do enunciado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Sensibilidade e especificidade são propriedades intrínsecas do teste e independem da prevalência. Já os &lt;strong&gt;valores preditivos&lt;/strong&gt; respondem à pergunta que interessa ao clínico (dado o resultado, qual a chance de a doença existir) e dependem fortemente da &lt;strong&gt;probabilidade pré-teste&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Montando a tabela de contingência com 1.000 pacientes e prevalência de 10 %: há &lt;strong&gt;100 doentes&lt;/strong&gt; e &lt;strong&gt;900 sadios&lt;/strong&gt;. Com sensibilidade de 90 %, obtêm-se &lt;strong&gt;90 verdadeiros positivos&lt;/strong&gt; e 10 falso-negativos. Com especificidade de 90 %, obtêm-se 810 verdadeiros negativos e &lt;strong&gt;90 falso-positivos&lt;/strong&gt;. O total de testes positivos é 90 + 90 = 180, e o valor preditivo positivo é 90/180 = &lt;strong&gt;50 %&lt;/strong&gt;. Ou seja, mesmo com um teste de desempenho aparentemente bom, metade dos positivos é falso-positivo, a razão pela qual rastreamento de doenças raras gera tantos alarmes falsos. No mesmo cenário, o valor preditivo negativo é 810/820, cerca de 99 %.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde valor preditivo com sensibilidade, que se calcula entre os doentes e não entre os testes positivos; (C) superestima o efeito da especificidade, ignorando que 10 % de 900 sadios geram tantos falso-positivos quanto o número de verdadeiros positivos; (D) a prevalência influencia o valor preditivo, mas não o define sozinha, e 10 % é simplesmente a prevalência copiada do enunciado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Todo teste de hipótese admite dois erros. O &lt;strong&gt;erro tipo I&lt;/strong&gt; (alfa) é rejeitar a hipótese nula quando ela é verdadeira — afirmar diferença inexistente; é o próprio nível de significância, fixado em 5 % por convenção. O &lt;strong&gt;erro tipo II&lt;/strong&gt; (beta) é não rejeitar a hipótese nula quando ela é falsa — deixar passar uma diferença real. O &lt;strong&gt;poder&lt;/strong&gt; do estudo é 1 − beta, habitualmente estipulado em 80 % ou 90 %.&lt;/p&gt;&lt;p&gt;O poder depende do tamanho do efeito, da variabilidade dos dados, do alfa escolhido e, sobretudo, do &lt;strong&gt;tamanho amostral&lt;/strong&gt;. Reduzir a amostra pela metade não altera o alfa, mas derruba o poder e, portanto, &lt;strong&gt;eleva o risco de erro tipo II&lt;/strong&gt;. O resultado descrito é típico de estudo subdimensionado: efeito na direção esperada, porém intervalo de confiança largo e valor de p acima do limiar. A leitura correta é que o estudo foi incapaz de responder à pergunta, não que a intervenção seja inútil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o risco de erro tipo I é determinado pelo alfa, mantido em 5 %, e não aumenta por redução amostral; (B) ausência de significância não é prova de equivalência — demonstrar equivalência exige delineamento próprio, com margem previamente definida; (D) o poder de 80 % era uma projeção condicionada aos 120 participantes por grupo, e o poder real do estudo concluído é substancialmente menor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Todo teste de hipótese admite dois erros. O &lt;strong&gt;erro tipo I&lt;/strong&gt; (alfa) é rejeitar a hipótese nula quando ela é verdadeira, ou seja, afirmar diferença inexistente; é o próprio nível de significância, fixado em 5 % por convenção. O &lt;strong&gt;erro tipo II&lt;/strong&gt; (beta) é não rejeitar a hipótese nula quando ela é falsa, ou seja, deixar passar uma diferença real. O &lt;strong&gt;poder&lt;/strong&gt; do estudo é 1 − beta, habitualmente estipulado em 80 % ou 90 %.&lt;/p&gt;&lt;p&gt;O poder depende do tamanho do efeito, da variabilidade dos dados, do alfa escolhido e, sobretudo, do &lt;strong&gt;tamanho amostral&lt;/strong&gt;. Reduzir a amostra pela metade não altera o alfa, mas derruba o poder e, portanto, &lt;strong&gt;eleva o risco de erro tipo II&lt;/strong&gt;. O resultado descrito é típico de estudo subdimensionado: efeito na direção esperada, porém intervalo de confiança largo e valor de p acima do limiar. A leitura correta é que o estudo foi incapaz de responder à pergunta, não que a intervenção seja inútil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o risco de erro tipo I é determinado pelo alfa, mantido em 5 %, e não aumenta por redução amostral; (B) ausência de significância não é prova de equivalência: demonstrar equivalência exige delineamento próprio, com margem previamente definida; (D) o poder de 80 % era uma projeção condicionada aos 120 participantes por grupo, e o poder real do estudo concluído é substancialmente menor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No Brasil, a responsabilidade civil do médico que atua como &lt;strong&gt;profissional liberal&lt;/strong&gt; é &lt;strong&gt;subjetiva&lt;/strong&gt;, tanto pelo Código Civil quanto pela ressalva expressa do Código de Defesa do Consumidor, que afasta a responsabilidade objetiva nesse caso específico. Para haver dever de indenizar, exige-se a presença simultânea de quatro elementos: &lt;strong&gt;conduta&lt;/strong&gt;, &lt;strong&gt;culpa&lt;/strong&gt;, &lt;strong&gt;dano&lt;/strong&gt; e &lt;strong&gt;nexo causal&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A culpa manifesta-se em três modalidades clássicas: &lt;strong&gt;imprudência&lt;/strong&gt; (agir sem a cautela devida), &lt;strong&gt;negligência&lt;/strong&gt; (deixar de fazer o que era devido) e &lt;strong&gt;imperícia&lt;/strong&gt; (falta de aptidão técnica para o ato praticado). Como regra, a atividade médica configura &lt;strong&gt;obrigação de meio&lt;/strong&gt; — compromete-se o profissional a empregar diligência, técnica e recursos disponíveis, não a garantir cura ou resultado. A cirurgia estética com finalidade embelezadora é a exceção habitualmente apontada como obrigação de resultado. Daí a importância probatória do &lt;strong&gt;registro em prontuário&lt;/strong&gt;, que documenta a diligência empregada, e do consentimento livre e esclarecido, que evidencia a informação prestada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a responsabilidade objetiva aplica-se ao hospital ou à clínica como prestadores de serviço, mas não ao médico profissional liberal; (C) a anestesia é obrigação de meio, e mero resultado adverso não gera dever de indenizar sem culpa demonstrada; (D) o consentimento informado documenta a informação e a autonomia, porém não funciona como salvo-conduto nem exclui responsabilidade por erro técnico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No Brasil, a responsabilidade civil do médico que atua como &lt;strong&gt;profissional liberal&lt;/strong&gt; é &lt;strong&gt;subjetiva&lt;/strong&gt;, tanto pelo Código Civil quanto pela ressalva expressa do Código de Defesa do Consumidor, que afasta a responsabilidade objetiva nesse caso específico. Para haver dever de indenizar, exige-se a presença simultânea de quatro elementos: &lt;strong&gt;conduta&lt;/strong&gt;, &lt;strong&gt;culpa&lt;/strong&gt;, &lt;strong&gt;dano&lt;/strong&gt; e &lt;strong&gt;nexo causal&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A culpa manifesta-se em três modalidades clássicas: &lt;strong&gt;imprudência&lt;/strong&gt; (agir sem a cautela devida), &lt;strong&gt;negligência&lt;/strong&gt; (deixar de fazer o que era devido) e &lt;strong&gt;imperícia&lt;/strong&gt; (falta de aptidão técnica para o ato praticado). Como regra, a atividade médica configura &lt;strong&gt;obrigação de meio&lt;/strong&gt;: compromete-se o profissional a empregar diligência, técnica e recursos disponíveis, não a garantir cura ou resultado. A cirurgia estética com finalidade embelezadora é a exceção habitualmente apontada como obrigação de resultado. Daí a importância probatória do &lt;strong&gt;registro em prontuário&lt;/strong&gt;, que documenta a diligência empregada, e do consentimento livre e esclarecido, que evidencia a informação prestada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a responsabilidade objetiva aplica-se ao hospital ou à clínica como prestadores de serviço, mas não ao médico profissional liberal; (C) a anestesia é obrigação de meio, e mero resultado adverso não gera dever de indenizar sem culpa demonstrada; (D) o consentimento informado documenta a informação e a autonomia, porém não funciona como salvo-conduto nem exclui responsabilidade por erro técnico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
